--- a/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74FE6F35-E49D-46A7-9994-DD80B2A1CAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575E30EA-9A14-4D3C-A37C-BCE36693EABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="275">
   <si>
     <t>Component list</t>
   </si>
@@ -242,15 +242,9 @@
     <t>Clamshell 22 Double-sided contacts/up and down connection Surface Mount 0.5mm SMD,P=0.5mm FFC/FPC Connectors ROHS</t>
   </si>
   <si>
-    <t>2A Surface Mount Square Pins 2mm 4mm -40℃~+105℃ 1 8 2mm 1x8P SMD,P=2mm Pin Headers ROHS</t>
-  </si>
-  <si>
     <t>CONN FPC/FFC 12POS .5MM</t>
   </si>
   <si>
-    <t>4 POS 2.54mm Pin Header Male single row Right Angle SMD</t>
-  </si>
-  <si>
     <t>FIXED IND 2.2UH 1.5A 160MOHM SMD</t>
   </si>
   <si>
@@ -461,9 +455,6 @@
     <t>GJM1555C1HR80WB01D</t>
   </si>
   <si>
-    <t>1220-1108G0Z090CR02</t>
-  </si>
-  <si>
     <t>MGFL2012F100MT-LF</t>
   </si>
   <si>
@@ -536,12 +527,6 @@
     <t>XFCN</t>
   </si>
   <si>
-    <t>Wcon</t>
-  </si>
-  <si>
-    <t>RTLECS</t>
-  </si>
-  <si>
     <t>TDK</t>
   </si>
   <si>
@@ -761,9 +746,6 @@
     <t>C285870</t>
   </si>
   <si>
-    <t>C920922</t>
-  </si>
-  <si>
     <t>C521237</t>
   </si>
   <si>
@@ -851,13 +833,28 @@
     <t>--------</t>
   </si>
   <si>
-    <t>1220-1104G0Z090CR02</t>
-  </si>
-  <si>
     <t>-------</t>
   </si>
   <si>
-    <t>C920925</t>
+    <t>CONN HEADER VERT 8POS 2.54MM</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 4POS 2.54MM</t>
+  </si>
+  <si>
+    <t>61300811121</t>
+  </si>
+  <si>
+    <t>61300411121</t>
+  </si>
+  <si>
+    <t>Wurth Electronics</t>
+  </si>
+  <si>
+    <t>C2935914</t>
+  </si>
+  <si>
+    <t>C2935910</t>
   </si>
 </sst>
 </file>
@@ -2065,25 +2062,25 @@
         <v>57</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H9" s="61" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J9" s="62" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
@@ -2099,19 +2096,19 @@
         <v>58</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="I10" s="43" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="J10" s="46">
         <v>3</v>
@@ -2133,19 +2130,19 @@
         <v>59</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H11" s="53" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J11" s="47">
         <v>24</v>
@@ -2167,19 +2164,19 @@
         <v>60</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G12" s="45" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H12" s="54" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I12" s="45" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="J12" s="48">
         <v>1</v>
@@ -2201,19 +2198,19 @@
         <v>61</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H13" s="53" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="J13" s="47">
         <v>8</v>
@@ -2235,19 +2232,19 @@
         <v>62</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F14" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G14" s="45" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H14" s="54" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I14" s="45" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="J14" s="48">
         <v>3</v>
@@ -2269,19 +2266,19 @@
         <v>63</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H15" s="53" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="J15" s="47">
         <v>8</v>
@@ -2303,19 +2300,19 @@
         <v>64</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F16" s="45" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H16" s="54" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I16" s="45" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="J16" s="48">
         <v>1</v>
@@ -2334,22 +2331,22 @@
         <v>18</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H17" s="53" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="J17" s="47">
         <v>2</v>
@@ -2371,19 +2368,19 @@
         <v>65</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F18" s="45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G18" s="45" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H18" s="54" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="I18" s="45" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="J18" s="48">
         <v>1</v>
@@ -2405,19 +2402,19 @@
         <v>66</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F19" s="44" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H19" s="53" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J19" s="47">
         <v>1</v>
@@ -2439,19 +2436,19 @@
         <v>67</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F20" s="45" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G20" s="45" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H20" s="54" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I20" s="51" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J20" s="48">
         <v>1</v>
@@ -2473,19 +2470,19 @@
         <v>68</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F21" s="44" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H21" s="53" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I21" s="50" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J21" s="47">
         <v>1</v>
@@ -2507,19 +2504,19 @@
         <v>69</v>
       </c>
       <c r="E22" s="45" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G22" s="45" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H22" s="54" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I22" s="51" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J22" s="48">
         <v>1</v>
@@ -2528,7 +2525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="64">
         <f t="shared" si="0"/>
@@ -2537,29 +2534,29 @@
       <c r="C23" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="53" t="s">
-        <v>70</v>
+      <c r="D23" s="44" t="s">
+        <v>268</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>110</v>
-      </c>
-      <c r="F23" s="44" t="s">
-        <v>143</v>
+        <v>108</v>
+      </c>
+      <c r="F23" s="50" t="s">
+        <v>270</v>
       </c>
       <c r="G23" s="44" t="s">
-        <v>168</v>
+        <v>272</v>
       </c>
       <c r="H23" s="53" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J23" s="47">
         <v>1</v>
       </c>
       <c r="K23" s="29">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -2572,22 +2569,22 @@
         <v>25</v>
       </c>
       <c r="D24" s="54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F24" s="45" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G24" s="45" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H24" s="54" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="I24" s="51" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J24" s="48">
         <v>1</v>
@@ -2596,7 +2593,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="64">
         <f t="shared" si="0"/>
@@ -2605,29 +2602,29 @@
       <c r="C25" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="53" t="s">
-        <v>72</v>
+      <c r="D25" s="55" t="s">
+        <v>269</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="F25" s="44" t="s">
-        <v>273</v>
+        <v>110</v>
+      </c>
+      <c r="F25" s="50" t="s">
+        <v>271</v>
       </c>
       <c r="G25" s="44" t="s">
-        <v>169</v>
+        <v>272</v>
       </c>
       <c r="H25" s="53" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J25" s="47">
         <v>1</v>
       </c>
       <c r="K25" s="29">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -2640,22 +2637,22 @@
         <v>27</v>
       </c>
       <c r="D26" s="54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F26" s="45" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G26" s="45" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H26" s="57" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="I26" s="45" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="J26" s="48">
         <v>1</v>
@@ -2674,22 +2671,22 @@
         <v>28</v>
       </c>
       <c r="D27" s="53" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F27" s="44" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G27" s="44" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H27" s="53" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I27" s="44" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="J27" s="47">
         <v>1</v>
@@ -2708,22 +2705,22 @@
         <v>29</v>
       </c>
       <c r="D28" s="54" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E28" s="45" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F28" s="45" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G28" s="45" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H28" s="54" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I28" s="45" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="J28" s="48">
         <v>1</v>
@@ -2742,22 +2739,22 @@
         <v>30</v>
       </c>
       <c r="D29" s="53" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F29" s="44" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G29" s="44" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="H29" s="53" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="I29" s="44" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="J29" s="47">
         <v>1</v>
@@ -2776,22 +2773,22 @@
         <v>31</v>
       </c>
       <c r="D30" s="54" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F30" s="45" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G30" s="45" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H30" s="54" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="I30" s="45" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="J30" s="48">
         <v>1</v>
@@ -2810,22 +2807,22 @@
         <v>32</v>
       </c>
       <c r="D31" s="53" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F31" s="44" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G31" s="44" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H31" s="53" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="I31" s="50" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J31" s="47">
         <v>1</v>
@@ -2844,22 +2841,22 @@
         <v>33</v>
       </c>
       <c r="D32" s="54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E32" s="45" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F32" s="45" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G32" s="45" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H32" s="54" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="I32" s="45" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="J32" s="48">
         <v>1</v>
@@ -2878,22 +2875,22 @@
         <v>34</v>
       </c>
       <c r="D33" s="53" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F33" s="53" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="G33" s="44" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="H33" s="53" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I33" s="50" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J33" s="47">
         <v>2</v>
@@ -2912,22 +2909,22 @@
         <v>35</v>
       </c>
       <c r="D34" s="54" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E34" s="45" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G34" s="45" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="H34" s="54" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="I34" s="51" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J34" s="48">
         <v>1</v>
@@ -2946,22 +2943,22 @@
         <v>36</v>
       </c>
       <c r="D35" s="53" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F35" s="44" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G35" s="44" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H35" s="53" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I35" s="44" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J35" s="47">
         <v>1</v>
@@ -2980,22 +2977,22 @@
         <v>37</v>
       </c>
       <c r="D36" s="54" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F36" s="45" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="G36" s="45" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H36" s="54" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="I36" s="45" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="J36" s="48">
         <v>4</v>
@@ -3014,22 +3011,22 @@
         <v>38</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F37" s="44" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G37" s="44" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H37" s="53" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="I37" s="44" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="J37" s="47">
         <v>10</v>
@@ -3048,22 +3045,22 @@
         <v>39</v>
       </c>
       <c r="D38" s="54" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E38" s="45" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F38" s="45" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G38" s="45" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H38" s="54" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="I38" s="45" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="J38" s="48">
         <v>1</v>
@@ -3082,22 +3079,22 @@
         <v>40</v>
       </c>
       <c r="D39" s="53" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F39" s="53" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G39" s="44" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H39" s="53" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="I39" s="44" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="J39" s="47">
         <v>7</v>
@@ -3116,22 +3113,22 @@
         <v>41</v>
       </c>
       <c r="D40" s="54" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E40" s="45" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F40" s="54" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="G40" s="45" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H40" s="54" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="I40" s="45" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="J40" s="48">
         <v>2</v>
@@ -3150,22 +3147,22 @@
         <v>42</v>
       </c>
       <c r="D41" s="53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F41" s="53" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="G41" s="44" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H41" s="53" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="I41" s="44" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="J41" s="47">
         <v>2</v>
@@ -3184,22 +3181,22 @@
         <v>43</v>
       </c>
       <c r="D42" s="54" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E42" s="45" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F42" s="45" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G42" s="45" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H42" s="54" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="I42" s="45" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="J42" s="48">
         <v>1</v>
@@ -3218,28 +3215,28 @@
         <v>44</v>
       </c>
       <c r="D43" s="53" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G43" s="50" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H43" s="55" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="I43" s="50" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J43" s="47">
         <v>3</v>
       </c>
       <c r="K43" s="58" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
@@ -3252,22 +3249,22 @@
         <v>45</v>
       </c>
       <c r="D44" s="54" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E44" s="45" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F44" s="45" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G44" s="45" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H44" s="54" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="I44" s="51" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J44" s="48">
         <v>1</v>
@@ -3286,22 +3283,22 @@
         <v>46</v>
       </c>
       <c r="D45" s="53" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F45" s="44" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G45" s="44" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="H45" s="55" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="I45" s="50" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J45" s="47">
         <v>1</v>
@@ -3320,22 +3317,22 @@
         <v>47</v>
       </c>
       <c r="D46" s="54" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E46" s="45" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F46" s="45" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G46" s="45" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H46" s="54" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="I46" s="51" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J46" s="48">
         <v>1</v>
@@ -3354,22 +3351,22 @@
         <v>48</v>
       </c>
       <c r="D47" s="53" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F47" s="44" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G47" s="44" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="H47" s="55" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="I47" s="50" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J47" s="47">
         <v>1</v>
@@ -3388,22 +3385,22 @@
         <v>49</v>
       </c>
       <c r="D48" s="54" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E48" s="45" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F48" s="45" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G48" s="45" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H48" s="54" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="I48" s="51" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J48" s="48">
         <v>1</v>
@@ -3422,22 +3419,22 @@
         <v>50</v>
       </c>
       <c r="D49" s="53" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F49" s="44" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G49" s="44" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H49" s="55" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="I49" s="50" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J49" s="47">
         <v>1</v>
@@ -3456,22 +3453,22 @@
         <v>51</v>
       </c>
       <c r="D50" s="54" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E50" s="45" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F50" s="45" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G50" s="45" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H50" s="54" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="I50" s="51" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J50" s="48">
         <v>1</v>
@@ -3490,22 +3487,22 @@
         <v>52</v>
       </c>
       <c r="D51" s="53" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F51" s="44" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G51" s="44" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H51" s="53" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="I51" s="50" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J51" s="47">
         <v>1</v>
@@ -3524,22 +3521,22 @@
         <v>53</v>
       </c>
       <c r="D52" s="54" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E52" s="45" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F52" s="45" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G52" s="45" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H52" s="54" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="I52" s="51" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J52" s="48">
         <v>1</v>
@@ -3558,22 +3555,22 @@
         <v>54</v>
       </c>
       <c r="D53" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F53" s="44" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G53" s="44" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H53" s="53" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I53" s="44" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="J53" s="47">
         <v>2</v>
@@ -3592,22 +3589,22 @@
         <v>55</v>
       </c>
       <c r="D54" s="54" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E54" s="45" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F54" s="45" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G54" s="45" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H54" s="54" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="I54" s="45" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="J54" s="48">
         <v>1</v>
@@ -3626,22 +3623,22 @@
         <v>56</v>
       </c>
       <c r="D55" s="56" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E55" s="60" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F55" s="60" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G55" s="60" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H55" s="56" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="I55" s="60" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="J55" s="49">
         <v>1</v>

--- a/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575E30EA-9A14-4D3C-A37C-BCE36693EABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26CC9F6-51D2-407A-B8BE-31117E0FF244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -680,9 +680,6 @@
     <t>C86816</t>
   </si>
   <si>
-    <t>Quantity (1 Board)</t>
-  </si>
-  <si>
     <t>LCSC/MOQ/5 Boards</t>
   </si>
   <si>
@@ -855,6 +852,9 @@
   </si>
   <si>
     <t>C2935910</t>
+  </si>
+  <si>
+    <t>Quantity (Per Board)</t>
   </si>
 </sst>
 </file>
@@ -1607,12 +1607,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>607218</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>33130</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>19942</xdr:rowOff>
+      <xdr:rowOff>53072</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2438400" cy="1164730"/>
+    <xdr:ext cx="2383009" cy="1089928"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Picture 8">
@@ -1639,8 +1639,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12590859" y="633114"/>
-          <a:ext cx="2438400" cy="1164730"/>
+          <a:off x="12647543" y="657702"/>
+          <a:ext cx="2383009" cy="1089928"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1926,8 +1926,8 @@
     <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.85546875" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2077,10 +2077,10 @@
         <v>185</v>
       </c>
       <c r="J9" s="62" t="s">
+        <v>274</v>
+      </c>
+      <c r="K9" s="30" t="s">
         <v>216</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
@@ -2133,13 +2133,13 @@
         <v>102</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G11" s="44" t="s">
         <v>157</v>
       </c>
       <c r="H11" s="53" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I11" s="44" t="s">
         <v>187</v>
@@ -2173,7 +2173,7 @@
         <v>158</v>
       </c>
       <c r="H12" s="54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I12" s="45" t="s">
         <v>188</v>
@@ -2207,7 +2207,7 @@
         <v>159</v>
       </c>
       <c r="H13" s="53" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I13" s="44" t="s">
         <v>189</v>
@@ -2241,7 +2241,7 @@
         <v>160</v>
       </c>
       <c r="H14" s="54" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I14" s="45" t="s">
         <v>190</v>
@@ -2275,7 +2275,7 @@
         <v>159</v>
       </c>
       <c r="H15" s="53" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I15" s="44" t="s">
         <v>191</v>
@@ -2309,7 +2309,7 @@
         <v>157</v>
       </c>
       <c r="H16" s="54" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I16" s="45" t="s">
         <v>192</v>
@@ -2331,19 +2331,19 @@
         <v>18</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E17" s="44" t="s">
         <v>102</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G17" s="44" t="s">
         <v>159</v>
       </c>
       <c r="H17" s="53" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I17" s="44" t="s">
         <v>193</v>
@@ -2377,7 +2377,7 @@
         <v>157</v>
       </c>
       <c r="H18" s="54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I18" s="45" t="s">
         <v>194</v>
@@ -2411,7 +2411,7 @@
         <v>161</v>
       </c>
       <c r="H19" s="53" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I19" s="50" t="s">
         <v>212</v>
@@ -2445,7 +2445,7 @@
         <v>162</v>
       </c>
       <c r="H20" s="54" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I20" s="51" t="s">
         <v>212</v>
@@ -2479,7 +2479,7 @@
         <v>163</v>
       </c>
       <c r="H21" s="53" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I21" s="50" t="s">
         <v>212</v>
@@ -2513,7 +2513,7 @@
         <v>164</v>
       </c>
       <c r="H22" s="54" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I22" s="51" t="s">
         <v>212</v>
@@ -2535,19 +2535,19 @@
         <v>24</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E23" s="44" t="s">
         <v>108</v>
       </c>
       <c r="F23" s="50" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G23" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="H23" s="53" t="s">
         <v>272</v>
-      </c>
-      <c r="H23" s="53" t="s">
-        <v>273</v>
       </c>
       <c r="I23" s="50" t="s">
         <v>212</v>
@@ -2581,7 +2581,7 @@
         <v>161</v>
       </c>
       <c r="H24" s="54" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I24" s="51" t="s">
         <v>212</v>
@@ -2603,19 +2603,19 @@
         <v>26</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E25" s="44" t="s">
         <v>110</v>
       </c>
       <c r="F25" s="50" t="s">
+        <v>270</v>
+      </c>
+      <c r="G25" s="44" t="s">
         <v>271</v>
       </c>
-      <c r="G25" s="44" t="s">
-        <v>272</v>
-      </c>
       <c r="H25" s="53" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I25" s="50" t="s">
         <v>212</v>
@@ -2649,7 +2649,7 @@
         <v>160</v>
       </c>
       <c r="H26" s="57" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I26" s="45" t="s">
         <v>195</v>
@@ -2683,7 +2683,7 @@
         <v>165</v>
       </c>
       <c r="H27" s="53" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I27" s="44" t="s">
         <v>196</v>
@@ -2717,7 +2717,7 @@
         <v>166</v>
       </c>
       <c r="H28" s="54" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I28" s="45" t="s">
         <v>196</v>
@@ -2751,7 +2751,7 @@
         <v>167</v>
       </c>
       <c r="H29" s="53" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I29" s="44" t="s">
         <v>197</v>
@@ -2785,7 +2785,7 @@
         <v>157</v>
       </c>
       <c r="H30" s="54" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I30" s="45" t="s">
         <v>198</v>
@@ -2819,7 +2819,7 @@
         <v>157</v>
       </c>
       <c r="H31" s="53" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I31" s="50" t="s">
         <v>213</v>
@@ -2853,7 +2853,7 @@
         <v>168</v>
       </c>
       <c r="H32" s="54" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I32" s="45" t="s">
         <v>199</v>
@@ -2881,13 +2881,13 @@
         <v>117</v>
       </c>
       <c r="F33" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G33" s="44" t="s">
         <v>169</v>
       </c>
       <c r="H33" s="53" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I33" s="50" t="s">
         <v>213</v>
@@ -2915,13 +2915,13 @@
         <v>117</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G34" s="45" t="s">
         <v>169</v>
       </c>
       <c r="H34" s="54" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I34" s="51" t="s">
         <v>213</v>
@@ -2955,7 +2955,7 @@
         <v>170</v>
       </c>
       <c r="H35" s="53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I35" s="44" t="s">
         <v>200</v>
@@ -2977,19 +2977,19 @@
         <v>37</v>
       </c>
       <c r="D36" s="54" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E36" s="45" t="s">
         <v>119</v>
       </c>
       <c r="F36" s="45" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G36" s="45" t="s">
         <v>159</v>
       </c>
       <c r="H36" s="54" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I36" s="45" t="s">
         <v>201</v>
@@ -3023,7 +3023,7 @@
         <v>159</v>
       </c>
       <c r="H37" s="53" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I37" s="44" t="s">
         <v>202</v>
@@ -3057,7 +3057,7 @@
         <v>171</v>
       </c>
       <c r="H38" s="54" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I38" s="45" t="s">
         <v>203</v>
@@ -3085,13 +3085,13 @@
         <v>119</v>
       </c>
       <c r="F39" s="53" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G39" s="44" t="s">
         <v>172</v>
       </c>
       <c r="H39" s="53" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I39" s="44" t="s">
         <v>204</v>
@@ -3119,13 +3119,13 @@
         <v>119</v>
       </c>
       <c r="F40" s="54" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G40" s="45" t="s">
         <v>172</v>
       </c>
       <c r="H40" s="54" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I40" s="45" t="s">
         <v>205</v>
@@ -3153,13 +3153,13 @@
         <v>118</v>
       </c>
       <c r="F41" s="53" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G41" s="44" t="s">
         <v>173</v>
       </c>
       <c r="H41" s="53" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I41" s="44" t="s">
         <v>206</v>
@@ -3193,7 +3193,7 @@
         <v>159</v>
       </c>
       <c r="H42" s="54" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I42" s="45" t="s">
         <v>207</v>
@@ -3227,7 +3227,7 @@
         <v>213</v>
       </c>
       <c r="H43" s="55" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I43" s="50" t="s">
         <v>213</v>
@@ -3261,7 +3261,7 @@
         <v>174</v>
       </c>
       <c r="H44" s="54" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I44" s="51" t="s">
         <v>213</v>
@@ -3295,7 +3295,7 @@
         <v>175</v>
       </c>
       <c r="H45" s="55" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I45" s="50" t="s">
         <v>213</v>
@@ -3329,7 +3329,7 @@
         <v>176</v>
       </c>
       <c r="H46" s="54" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I46" s="51" t="s">
         <v>213</v>
@@ -3363,7 +3363,7 @@
         <v>177</v>
       </c>
       <c r="H47" s="55" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I47" s="50" t="s">
         <v>213</v>
@@ -3397,7 +3397,7 @@
         <v>178</v>
       </c>
       <c r="H48" s="54" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I48" s="51" t="s">
         <v>213</v>
@@ -3465,7 +3465,7 @@
         <v>180</v>
       </c>
       <c r="H50" s="54" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I50" s="51" t="s">
         <v>213</v>
@@ -3499,7 +3499,7 @@
         <v>181</v>
       </c>
       <c r="H51" s="53" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I51" s="50" t="s">
         <v>213</v>
@@ -3533,7 +3533,7 @@
         <v>182</v>
       </c>
       <c r="H52" s="54" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I52" s="51" t="s">
         <v>213</v>
@@ -3567,7 +3567,7 @@
         <v>183</v>
       </c>
       <c r="H53" s="53" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I53" s="44" t="s">
         <v>208</v>
@@ -3601,7 +3601,7 @@
         <v>183</v>
       </c>
       <c r="H54" s="54" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I54" s="45" t="s">
         <v>209</v>
@@ -3635,7 +3635,7 @@
         <v>184</v>
       </c>
       <c r="H55" s="56" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I55" s="60" t="s">
         <v>210</v>

--- a/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26CC9F6-51D2-407A-B8BE-31117E0FF244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCF1C63-595B-4E7A-B0C1-49680AE34CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="276">
   <si>
     <t>Component list</t>
   </si>
@@ -272,9 +272,6 @@
     <t>LED RED CLEAR CHIP SMD</t>
   </si>
   <si>
-    <t>0.1W ±5% ±1500ppm/℃ 25mΩ 0603 Chip Resistor - Surface Mount ROHS</t>
-  </si>
-  <si>
     <t>RES SMD 10K OHM 1% 1/16W 0402</t>
   </si>
   <si>
@@ -464,9 +461,6 @@
     <t>BLM18PG300SN1D</t>
   </si>
   <si>
-    <t>RTT03R025JTP</t>
-  </si>
-  <si>
     <t>RC0402FR-0710KL</t>
   </si>
   <si>
@@ -542,9 +536,6 @@
     <t>SunLED</t>
   </si>
   <si>
-    <t>Relac</t>
-  </si>
-  <si>
     <t>FOJAN</t>
   </si>
   <si>
@@ -761,9 +752,6 @@
     <t>C71911</t>
   </si>
   <si>
-    <t>C158897</t>
-  </si>
-  <si>
     <t>C60490</t>
   </si>
   <si>
@@ -855,6 +843,21 @@
   </si>
   <si>
     <t>Quantity (Per Board)</t>
+  </si>
+  <si>
+    <t>RES SMD 25m Ohms 125mW 0805</t>
+  </si>
+  <si>
+    <t>Res0805</t>
+  </si>
+  <si>
+    <t>0805W8F250MT5E</t>
+  </si>
+  <si>
+    <t>UNI-ROYAL</t>
+  </si>
+  <si>
+    <t>C620515</t>
   </si>
 </sst>
 </file>
@@ -864,7 +867,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -996,6 +999,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1029,7 +1038,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1361,11 +1370,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1545,6 +1569,12 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1940,8 +1970,8 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="77"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="79"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1956,9 +1986,9 @@
       <c r="F2" s="10"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="75"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -1974,8 +2004,8 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="72"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="74"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1991,8 +2021,8 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="72"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="74"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2008,8 +2038,8 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="72"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="74"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2021,8 +2051,8 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="73"/>
-      <c r="K6" s="72"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="74"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2034,8 +2064,8 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="72"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="74"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2047,8 +2077,8 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="73"/>
-      <c r="K8" s="72"/>
+      <c r="J8" s="75"/>
+      <c r="K8" s="74"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2062,25 +2092,25 @@
         <v>57</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H9" s="61" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J9" s="62" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
@@ -2096,19 +2126,19 @@
         <v>58</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I10" s="43" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J10" s="46">
         <v>3</v>
@@ -2130,19 +2160,19 @@
         <v>59</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H11" s="53" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J11" s="47">
         <v>24</v>
@@ -2164,19 +2194,19 @@
         <v>60</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G12" s="45" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H12" s="54" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I12" s="45" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J12" s="48">
         <v>1</v>
@@ -2198,19 +2228,19 @@
         <v>61</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H13" s="53" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J13" s="47">
         <v>8</v>
@@ -2232,19 +2262,19 @@
         <v>62</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F14" s="45" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G14" s="45" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H14" s="54" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I14" s="45" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J14" s="48">
         <v>3</v>
@@ -2266,19 +2296,19 @@
         <v>63</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H15" s="53" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J15" s="47">
         <v>8</v>
@@ -2300,19 +2330,19 @@
         <v>64</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F16" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H16" s="54" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I16" s="45" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J16" s="48">
         <v>1</v>
@@ -2331,22 +2361,22 @@
         <v>18</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H17" s="53" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J17" s="47">
         <v>2</v>
@@ -2368,19 +2398,19 @@
         <v>65</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F18" s="45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G18" s="45" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H18" s="54" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I18" s="45" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J18" s="48">
         <v>1</v>
@@ -2402,19 +2432,19 @@
         <v>66</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F19" s="44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H19" s="53" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J19" s="47">
         <v>1</v>
@@ -2436,19 +2466,19 @@
         <v>67</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F20" s="45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G20" s="45" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H20" s="54" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I20" s="51" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J20" s="48">
         <v>1</v>
@@ -2470,19 +2500,19 @@
         <v>68</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F21" s="44" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H21" s="53" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I21" s="50" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J21" s="47">
         <v>1</v>
@@ -2504,19 +2534,19 @@
         <v>69</v>
       </c>
       <c r="E22" s="45" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G22" s="45" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H22" s="54" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I22" s="51" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J22" s="48">
         <v>1</v>
@@ -2535,22 +2565,22 @@
         <v>24</v>
       </c>
       <c r="D23" s="44" t="s">
+        <v>263</v>
+      </c>
+      <c r="E23" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="50" t="s">
+        <v>265</v>
+      </c>
+      <c r="G23" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="E23" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="F23" s="50" t="s">
-        <v>269</v>
-      </c>
-      <c r="G23" s="44" t="s">
-        <v>271</v>
-      </c>
       <c r="H23" s="53" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J23" s="47">
         <v>1</v>
@@ -2572,19 +2602,19 @@
         <v>70</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F24" s="45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G24" s="45" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H24" s="54" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I24" s="51" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J24" s="48">
         <v>1</v>
@@ -2603,22 +2633,22 @@
         <v>26</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G25" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H25" s="53" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J25" s="47">
         <v>1</v>
@@ -2640,19 +2670,19 @@
         <v>71</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F26" s="45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G26" s="45" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H26" s="57" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I26" s="45" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J26" s="48">
         <v>1</v>
@@ -2674,19 +2704,19 @@
         <v>72</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F27" s="44" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G27" s="44" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H27" s="53" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I27" s="44" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J27" s="47">
         <v>1</v>
@@ -2708,19 +2738,19 @@
         <v>73</v>
       </c>
       <c r="E28" s="45" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G28" s="45" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H28" s="54" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="I28" s="45" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J28" s="48">
         <v>1</v>
@@ -2742,19 +2772,19 @@
         <v>74</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F29" s="44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G29" s="44" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H29" s="53" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I29" s="44" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J29" s="47">
         <v>1</v>
@@ -2776,19 +2806,19 @@
         <v>75</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F30" s="45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G30" s="45" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H30" s="54" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="I30" s="45" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J30" s="48">
         <v>1</v>
@@ -2810,19 +2840,19 @@
         <v>76</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F31" s="44" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G31" s="44" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H31" s="53" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I31" s="50" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J31" s="47">
         <v>1</v>
@@ -2844,19 +2874,19 @@
         <v>77</v>
       </c>
       <c r="E32" s="45" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F32" s="45" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G32" s="45" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H32" s="54" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I32" s="45" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J32" s="48">
         <v>1</v>
@@ -2878,19 +2908,19 @@
         <v>78</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F33" s="53" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G33" s="44" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H33" s="53" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I33" s="50" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J33" s="47">
         <v>2</v>
@@ -2912,19 +2942,19 @@
         <v>79</v>
       </c>
       <c r="E34" s="45" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G34" s="45" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H34" s="54" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I34" s="51" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J34" s="48">
         <v>1</v>
@@ -2933,7 +2963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="64">
         <f t="shared" si="0"/>
@@ -2942,23 +2972,23 @@
       <c r="C35" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="E35" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="F35" s="44" t="s">
-        <v>144</v>
-      </c>
-      <c r="G35" s="44" t="s">
-        <v>170</v>
+      <c r="D35" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="E35" s="69" t="s">
+        <v>272</v>
+      </c>
+      <c r="F35" s="69" t="s">
+        <v>273</v>
+      </c>
+      <c r="G35" s="69" t="s">
+        <v>274</v>
       </c>
       <c r="H35" s="53" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="I35" s="44" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J35" s="47">
         <v>1</v>
@@ -2977,22 +3007,22 @@
         <v>37</v>
       </c>
       <c r="D36" s="54" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F36" s="45" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="G36" s="45" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H36" s="54" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I36" s="45" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J36" s="48">
         <v>4</v>
@@ -3011,22 +3041,22 @@
         <v>38</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F37" s="44" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G37" s="44" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H37" s="53" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I37" s="44" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J37" s="47">
         <v>10</v>
@@ -3045,22 +3075,22 @@
         <v>39</v>
       </c>
       <c r="D38" s="54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E38" s="45" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F38" s="45" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G38" s="45" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H38" s="54" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I38" s="45" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J38" s="48">
         <v>1</v>
@@ -3079,22 +3109,22 @@
         <v>40</v>
       </c>
       <c r="D39" s="53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F39" s="53" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G39" s="44" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H39" s="53" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I39" s="44" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J39" s="47">
         <v>7</v>
@@ -3113,22 +3143,22 @@
         <v>41</v>
       </c>
       <c r="D40" s="54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E40" s="45" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F40" s="54" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G40" s="45" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H40" s="54" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I40" s="45" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J40" s="48">
         <v>2</v>
@@ -3147,22 +3177,22 @@
         <v>42</v>
       </c>
       <c r="D41" s="53" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F41" s="53" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G41" s="44" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H41" s="53" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I41" s="44" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="J41" s="47">
         <v>2</v>
@@ -3181,22 +3211,22 @@
         <v>43</v>
       </c>
       <c r="D42" s="54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E42" s="45" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F42" s="45" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G42" s="45" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H42" s="54" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I42" s="45" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J42" s="48">
         <v>1</v>
@@ -3215,28 +3245,28 @@
         <v>44</v>
       </c>
       <c r="D43" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G43" s="50" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H43" s="55" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I43" s="50" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J43" s="47">
         <v>3</v>
       </c>
       <c r="K43" s="58" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
@@ -3249,22 +3279,22 @@
         <v>45</v>
       </c>
       <c r="D44" s="54" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E44" s="45" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F44" s="45" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G44" s="45" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H44" s="54" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I44" s="51" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J44" s="48">
         <v>1</v>
@@ -3283,22 +3313,22 @@
         <v>46</v>
       </c>
       <c r="D45" s="53" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F45" s="44" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G45" s="44" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H45" s="55" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I45" s="50" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J45" s="47">
         <v>1</v>
@@ -3317,22 +3347,22 @@
         <v>47</v>
       </c>
       <c r="D46" s="54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E46" s="45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F46" s="45" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G46" s="45" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H46" s="54" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I46" s="51" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J46" s="48">
         <v>1</v>
@@ -3351,22 +3381,22 @@
         <v>48</v>
       </c>
       <c r="D47" s="53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F47" s="44" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G47" s="44" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H47" s="55" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I47" s="50" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J47" s="47">
         <v>1</v>
@@ -3385,22 +3415,22 @@
         <v>49</v>
       </c>
       <c r="D48" s="54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E48" s="45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F48" s="45" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G48" s="45" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H48" s="54" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I48" s="51" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J48" s="48">
         <v>1</v>
@@ -3419,22 +3449,22 @@
         <v>50</v>
       </c>
       <c r="D49" s="53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F49" s="44" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G49" s="44" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H49" s="55" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I49" s="50" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J49" s="47">
         <v>1</v>
@@ -3453,22 +3483,22 @@
         <v>51</v>
       </c>
       <c r="D50" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E50" s="45" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F50" s="45" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G50" s="45" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H50" s="54" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I50" s="51" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J50" s="48">
         <v>1</v>
@@ -3487,22 +3517,22 @@
         <v>52</v>
       </c>
       <c r="D51" s="53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F51" s="44" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G51" s="44" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H51" s="53" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="I51" s="50" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J51" s="47">
         <v>1</v>
@@ -3521,22 +3551,22 @@
         <v>53</v>
       </c>
       <c r="D52" s="54" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E52" s="45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F52" s="45" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G52" s="45" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H52" s="54" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I52" s="51" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J52" s="48">
         <v>1</v>
@@ -3555,22 +3585,22 @@
         <v>54</v>
       </c>
       <c r="D53" s="53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F53" s="44" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G53" s="44" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H53" s="53" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="I53" s="44" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="J53" s="47">
         <v>2</v>
@@ -3589,22 +3619,22 @@
         <v>55</v>
       </c>
       <c r="D54" s="54" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E54" s="45" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F54" s="45" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G54" s="45" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H54" s="54" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I54" s="45" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="J54" s="48">
         <v>1</v>
@@ -3623,22 +3653,22 @@
         <v>56</v>
       </c>
       <c r="D55" s="56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E55" s="60" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F55" s="60" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G55" s="60" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H55" s="56" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I55" s="60" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="J55" s="49">
         <v>1</v>
@@ -3658,9 +3688,9 @@
       <c r="F56" s="59"/>
       <c r="G56" s="59"/>
       <c r="H56" s="59"/>
-      <c r="I56" s="68"/>
-      <c r="J56" s="68"/>
-      <c r="K56" s="69"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="70"/>
+      <c r="K56" s="71"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
@@ -3673,9 +3703,9 @@
       <c r="F57" s="37"/>
       <c r="G57" s="37"/>
       <c r="H57" s="37"/>
-      <c r="I57" s="70"/>
-      <c r="J57" s="70"/>
-      <c r="K57" s="71"/>
+      <c r="I57" s="72"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCF1C63-595B-4E7A-B0C1-49680AE34CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D744508-2691-4D57-ACB2-B3FA38E0B969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22515" yWindow="3405" windowWidth="11790" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="282">
   <si>
     <t>Component list</t>
   </si>
@@ -77,18 +78,12 @@
     <t>C8, C25, C26, C27, C28, C39, C40, C50</t>
   </si>
   <si>
-    <t>C9, C23, C33</t>
-  </si>
-  <si>
     <t>C16, C30, C32, C43, C45, C46, C48, C51</t>
   </si>
   <si>
     <t>C17</t>
   </si>
   <si>
-    <t>C29, C44</t>
-  </si>
-  <si>
     <t>C38</t>
   </si>
   <si>
@@ -116,9 +111,6 @@
     <t>L1</t>
   </si>
   <si>
-    <t>L2</t>
-  </si>
-  <si>
     <t>L3</t>
   </si>
   <si>
@@ -248,9 +240,6 @@
     <t>FIXED IND 2.2UH 1.5A 160MOHM SMD</t>
   </si>
   <si>
-    <t>FIXED IND 10UH 360MA 1.32OHM SMD</t>
-  </si>
-  <si>
     <t>500mA 10uH ±20% 320mΩ 0805 Inductors (SMD) ROHS</t>
   </si>
   <si>
@@ -365,9 +354,6 @@
     <t>MAKK2016T2R2M</t>
   </si>
   <si>
-    <t>NLCV25T-100K-EFRD</t>
-  </si>
-  <si>
     <t>Ind0805</t>
   </si>
   <si>
@@ -521,9 +507,6 @@
     <t>XFCN</t>
   </si>
   <si>
-    <t>TDK</t>
-  </si>
-  <si>
     <t>microgate</t>
   </si>
   <si>
@@ -722,9 +705,6 @@
     <t>C424659</t>
   </si>
   <si>
-    <t>C295388</t>
-  </si>
-  <si>
     <t>C281113</t>
   </si>
   <si>
@@ -858,6 +838,45 @@
   </si>
   <si>
     <t>C620515</t>
+  </si>
+  <si>
+    <t>C44</t>
+  </si>
+  <si>
+    <t>C9, 33</t>
+  </si>
+  <si>
+    <t>C3, C4, C6, C10, C11, C12, C13, C14, C15, C18, C19, C20, C21, C22, C23, C24, C31, C34, C35, C36, C41, C42, C47, C49</t>
+  </si>
+  <si>
+    <t>C9, C33</t>
+  </si>
+  <si>
+    <t>C16, C32, C43, C45, C46, C48, C51</t>
+  </si>
+  <si>
+    <t>C37</t>
+  </si>
+  <si>
+    <t>CAP CER 100pF 50V C0G 0402</t>
+  </si>
+  <si>
+    <t>Cap 0403</t>
+  </si>
+  <si>
+    <t>GCM1555C1H101JA16D</t>
+  </si>
+  <si>
+    <t>100pF</t>
+  </si>
+  <si>
+    <t>R7, R8, R13, R14, R15, R16, R17, R26</t>
+  </si>
+  <si>
+    <t>SW1, SW2</t>
+  </si>
+  <si>
+    <t>C126492</t>
   </si>
 </sst>
 </file>
@@ -867,7 +886,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1005,6 +1024,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="13"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1038,7 +1063,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1385,11 +1410,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1576,6 +1629,101 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -1609,6 +1757,54 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1671,6 +1867,55 @@
         <a:xfrm>
           <a:off x="12647543" y="657702"/>
           <a:ext cx="2383009" cy="1089928"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10417</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1714500" cy="1104008"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D35ED14F-294C-4592-98D6-4CAC8DEA33B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14306550" y="620017"/>
+          <a:ext cx="1714500" cy="1104008"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1946,7 +2191,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="23" customWidth="1"/>
@@ -1970,8 +2215,8 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="79"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="116"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1986,9 +2231,9 @@
       <c r="F2" s="10"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="77"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="114"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2004,8 +2249,8 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="74"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="111"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2021,8 +2266,8 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="74"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="111"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2038,8 +2283,8 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="74"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="111"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2051,8 +2296,8 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="74"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="111"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2064,8 +2309,8 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="74"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="111"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2077,8 +2322,8 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="74"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="111"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2089,28 +2334,28 @@
         <v>10</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="H9" s="61" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="J9" s="62" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
@@ -2123,22 +2368,22 @@
         <v>11</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="I10" s="43" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J10" s="46">
         <v>3</v>
@@ -2150,29 +2395,29 @@
     <row r="11" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="64">
-        <f t="shared" ref="B11:B55" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B54" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="44" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H11" s="53" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J11" s="47">
         <v>24</v>
@@ -2191,22 +2436,22 @@
         <v>13</v>
       </c>
       <c r="D12" s="54" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G12" s="45" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H12" s="54" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="I12" s="45" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J12" s="48">
         <v>1</v>
@@ -2225,22 +2470,22 @@
         <v>14</v>
       </c>
       <c r="D13" s="53" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H13" s="53" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="J13" s="47">
         <v>8</v>
@@ -2256,28 +2501,28 @@
         <v>5</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>15</v>
+        <v>270</v>
       </c>
       <c r="D14" s="54" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F14" s="45" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G14" s="45" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="H14" s="54" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="I14" s="45" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="J14" s="48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" s="28">
         <v>50</v>
@@ -2290,25 +2535,25 @@
         <v>6</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" s="53" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H15" s="53" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="J15" s="47">
         <v>8</v>
@@ -2324,25 +2569,25 @@
         <v>7</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16" s="54" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F16" s="45" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H16" s="54" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I16" s="45" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="J16" s="48">
         <v>1</v>
@@ -2358,28 +2603,28 @@
         <v>8</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>18</v>
+        <v>269</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H17" s="53" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="J17" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" s="29">
         <v>100</v>
@@ -2392,25 +2637,25 @@
         <v>9</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D18" s="54" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F18" s="45" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G18" s="45" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H18" s="54" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I18" s="45" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="J18" s="48">
         <v>1</v>
@@ -2426,25 +2671,25 @@
         <v>10</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F19" s="44" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="H19" s="53" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J19" s="47">
         <v>1</v>
@@ -2463,22 +2708,22 @@
         <v>21</v>
       </c>
       <c r="D20" s="54" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F20" s="45" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G20" s="45" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="H20" s="54" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="I20" s="51" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J20" s="48">
         <v>1</v>
@@ -2494,25 +2739,25 @@
         <v>12</v>
       </c>
       <c r="C21" s="44" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F21" s="44" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H21" s="53" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="I21" s="50" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J21" s="47">
         <v>1</v>
@@ -2528,25 +2773,25 @@
         <v>13</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E22" s="45" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G22" s="45" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H22" s="54" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="I22" s="51" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J22" s="48">
         <v>1</v>
@@ -2562,25 +2807,25 @@
         <v>14</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F23" s="50" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G23" s="44" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="H23" s="53" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J23" s="47">
         <v>1</v>
@@ -2596,25 +2841,25 @@
         <v>15</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D24" s="54" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F24" s="45" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G24" s="45" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="H24" s="54" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="I24" s="51" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J24" s="48">
         <v>1</v>
@@ -2630,25 +2875,25 @@
         <v>16</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G25" s="44" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="H25" s="53" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J25" s="47">
         <v>1</v>
@@ -2664,25 +2909,25 @@
         <v>17</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D26" s="54" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F26" s="45" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G26" s="45" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="H26" s="57" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="I26" s="45" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="J26" s="48">
         <v>1</v>
@@ -2691,1025 +2936,991 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" s="44" t="s">
-        <v>208</v>
-      </c>
-      <c r="F27" s="44" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="44" t="s">
-        <v>163</v>
-      </c>
-      <c r="H27" s="53" t="s">
-        <v>230</v>
-      </c>
-      <c r="I27" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="J27" s="47">
-        <v>1</v>
-      </c>
-      <c r="K27" s="29">
-        <v>7</v>
+      <c r="C27" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27" s="45" t="s">
+        <v>158</v>
+      </c>
+      <c r="H27" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="I27" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="J27" s="48">
+        <v>1</v>
+      </c>
+      <c r="K27" s="32">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="64">
-        <f>ROW(B28) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="E28" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="F28" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="G28" s="45" t="s">
-        <v>164</v>
-      </c>
-      <c r="H28" s="54" t="s">
-        <v>231</v>
-      </c>
-      <c r="I28" s="45" t="s">
-        <v>193</v>
-      </c>
-      <c r="J28" s="48">
-        <v>1</v>
-      </c>
-      <c r="K28" s="32">
+      <c r="C28" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="F28" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G28" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="H28" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="I28" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="J28" s="47">
+        <v>1</v>
+      </c>
+      <c r="K28" s="29">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29" s="44" t="s">
-        <v>208</v>
-      </c>
-      <c r="F29" s="44" t="s">
-        <v>113</v>
-      </c>
-      <c r="G29" s="44" t="s">
-        <v>165</v>
-      </c>
-      <c r="H29" s="53" t="s">
-        <v>232</v>
-      </c>
-      <c r="I29" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="J29" s="47">
-        <v>1</v>
-      </c>
-      <c r="K29" s="29">
+      <c r="C29" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="F29" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="G29" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="H29" s="54" t="s">
+        <v>227</v>
+      </c>
+      <c r="I29" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J29" s="48">
+        <v>1</v>
+      </c>
+      <c r="K29" s="28">
         <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="64">
-        <f>ROW(B30) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="54" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="F30" s="45" t="s">
-        <v>141</v>
-      </c>
-      <c r="G30" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="H30" s="54" t="s">
-        <v>234</v>
-      </c>
-      <c r="I30" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="J30" s="48">
-        <v>1</v>
-      </c>
-      <c r="K30" s="28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="C30" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="G30" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="I30" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="J30" s="47">
+        <v>1</v>
+      </c>
+      <c r="K30" s="29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="F31" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="G31" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="H31" s="53" t="s">
-        <v>235</v>
-      </c>
-      <c r="I31" s="50" t="s">
-        <v>210</v>
-      </c>
-      <c r="J31" s="47">
-        <v>1</v>
-      </c>
-      <c r="K31" s="29">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="C31" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="H31" s="54" t="s">
+        <v>226</v>
+      </c>
+      <c r="I31" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="J31" s="48">
+        <v>1</v>
+      </c>
+      <c r="K31" s="32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="64">
-        <f>ROW(B32) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="54" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="F32" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="G32" s="45" t="s">
-        <v>166</v>
-      </c>
-      <c r="H32" s="54" t="s">
-        <v>233</v>
-      </c>
-      <c r="I32" s="45" t="s">
-        <v>196</v>
-      </c>
-      <c r="J32" s="48">
-        <v>1</v>
-      </c>
-      <c r="K32" s="32">
-        <v>10</v>
+      <c r="C32" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="G32" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="H32" s="53" t="s">
+        <v>230</v>
+      </c>
+      <c r="I32" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="J32" s="47">
+        <v>2</v>
+      </c>
+      <c r="K32" s="29">
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="E33" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="F33" s="53" t="s">
-        <v>236</v>
-      </c>
-      <c r="G33" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="H33" s="53" t="s">
-        <v>237</v>
-      </c>
-      <c r="I33" s="50" t="s">
-        <v>210</v>
-      </c>
-      <c r="J33" s="47">
-        <v>2</v>
-      </c>
-      <c r="K33" s="29">
-        <v>50</v>
+      <c r="C33" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="G33" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="H33" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="I33" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="J33" s="48">
+        <v>1</v>
+      </c>
+      <c r="K33" s="28">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="64">
-        <f>ROW(B34) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="E34" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="F34" s="54" t="s">
-        <v>238</v>
-      </c>
-      <c r="G34" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="H34" s="54" t="s">
-        <v>239</v>
-      </c>
-      <c r="I34" s="51" t="s">
-        <v>210</v>
-      </c>
-      <c r="J34" s="48">
-        <v>1</v>
-      </c>
-      <c r="K34" s="28">
-        <v>10</v>
+      <c r="C34" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="E34" s="69" t="s">
+        <v>265</v>
+      </c>
+      <c r="F34" s="69" t="s">
+        <v>266</v>
+      </c>
+      <c r="G34" s="69" t="s">
+        <v>267</v>
+      </c>
+      <c r="H34" s="53" t="s">
+        <v>268</v>
+      </c>
+      <c r="I34" s="44" t="s">
+        <v>191</v>
+      </c>
+      <c r="J34" s="47">
+        <v>1</v>
+      </c>
+      <c r="K34" s="29">
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="68" t="s">
-        <v>271</v>
-      </c>
-      <c r="E35" s="69" t="s">
-        <v>272</v>
-      </c>
-      <c r="F35" s="69" t="s">
-        <v>273</v>
-      </c>
-      <c r="G35" s="69" t="s">
-        <v>274</v>
-      </c>
-      <c r="H35" s="53" t="s">
-        <v>275</v>
-      </c>
-      <c r="I35" s="44" t="s">
-        <v>197</v>
-      </c>
-      <c r="J35" s="47">
-        <v>1</v>
-      </c>
-      <c r="K35" s="29">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C35" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="54" t="s">
+        <v>253</v>
+      </c>
+      <c r="E35" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="F35" s="45" t="s">
+        <v>252</v>
+      </c>
+      <c r="G35" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="H35" s="54" t="s">
+        <v>251</v>
+      </c>
+      <c r="I35" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="J35" s="48">
+        <v>4</v>
+      </c>
+      <c r="K35" s="28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="64">
-        <f>ROW(B36) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="54" t="s">
-        <v>260</v>
-      </c>
-      <c r="E36" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="F36" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="G36" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="H36" s="54" t="s">
-        <v>258</v>
-      </c>
-      <c r="I36" s="45" t="s">
-        <v>198</v>
-      </c>
-      <c r="J36" s="48">
-        <v>4</v>
-      </c>
-      <c r="K36" s="28">
+      <c r="C36" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="F36" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="G36" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="H36" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="I36" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="J36" s="47">
+        <v>10</v>
+      </c>
+      <c r="K36" s="29">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="E37" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="F37" s="44" t="s">
-        <v>143</v>
-      </c>
-      <c r="G37" s="44" t="s">
-        <v>157</v>
-      </c>
-      <c r="H37" s="53" t="s">
-        <v>240</v>
-      </c>
-      <c r="I37" s="44" t="s">
-        <v>199</v>
-      </c>
-      <c r="J37" s="47">
-        <v>10</v>
-      </c>
-      <c r="K37" s="29">
+      <c r="C37" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="G37" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="H37" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="I37" s="45" t="s">
+        <v>194</v>
+      </c>
+      <c r="J37" s="48">
+        <v>1</v>
+      </c>
+      <c r="K37" s="28">
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="64">
-        <f>ROW(B38) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="54" t="s">
-        <v>81</v>
-      </c>
-      <c r="E38" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="F38" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="G38" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="H38" s="54" t="s">
-        <v>241</v>
-      </c>
-      <c r="I38" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="J38" s="48">
-        <v>1</v>
-      </c>
-      <c r="K38" s="28">
+      <c r="C38" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="F38" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="G38" s="44" t="s">
+        <v>163</v>
+      </c>
+      <c r="H38" s="53" t="s">
+        <v>237</v>
+      </c>
+      <c r="I38" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="J38" s="47">
+        <v>7</v>
+      </c>
+      <c r="K38" s="29">
         <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="D39" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="E39" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="F39" s="53" t="s">
-        <v>243</v>
-      </c>
-      <c r="G39" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="H39" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="I39" s="44" t="s">
-        <v>201</v>
-      </c>
-      <c r="J39" s="47">
-        <v>7</v>
-      </c>
-      <c r="K39" s="29">
+      <c r="C39" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="F39" s="54" t="s">
+        <v>238</v>
+      </c>
+      <c r="G39" s="45" t="s">
+        <v>163</v>
+      </c>
+      <c r="H39" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="I39" s="45" t="s">
+        <v>196</v>
+      </c>
+      <c r="J39" s="48">
+        <v>2</v>
+      </c>
+      <c r="K39" s="28">
         <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="64">
-        <f>ROW(B40) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="54" t="s">
-        <v>83</v>
-      </c>
-      <c r="E40" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="F40" s="54" t="s">
-        <v>245</v>
-      </c>
-      <c r="G40" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="H40" s="54" t="s">
-        <v>246</v>
-      </c>
-      <c r="I40" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="J40" s="48">
+      <c r="C40" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="F40" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="H40" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="I40" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="J40" s="47">
         <v>2</v>
       </c>
-      <c r="K40" s="28">
+      <c r="K40" s="29">
         <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="44" t="s">
-        <v>42</v>
-      </c>
-      <c r="D41" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="E41" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="F41" s="53" t="s">
-        <v>247</v>
-      </c>
-      <c r="G41" s="44" t="s">
-        <v>170</v>
-      </c>
-      <c r="H41" s="53" t="s">
-        <v>248</v>
-      </c>
-      <c r="I41" s="44" t="s">
-        <v>203</v>
-      </c>
-      <c r="J41" s="47">
-        <v>2</v>
-      </c>
-      <c r="K41" s="29">
-        <v>100</v>
+      <c r="C41" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="F41" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="G41" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="H41" s="54" t="s">
+        <v>235</v>
+      </c>
+      <c r="I41" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="J41" s="48">
+        <v>1</v>
+      </c>
+      <c r="K41" s="28">
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="64">
-        <f>ROW(B42) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="D42" s="54" t="s">
-        <v>85</v>
-      </c>
-      <c r="E42" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="F42" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="G42" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="H42" s="54" t="s">
-        <v>242</v>
-      </c>
-      <c r="I42" s="45" t="s">
+      <c r="C42" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="F42" s="50" t="s">
         <v>204</v>
       </c>
-      <c r="J42" s="48">
-        <v>1</v>
-      </c>
-      <c r="K42" s="28">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G42" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="H42" s="55" t="s">
+        <v>254</v>
+      </c>
+      <c r="I42" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="J42" s="47">
+        <v>3</v>
+      </c>
+      <c r="K42" s="58" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="44" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="E43" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="F43" s="50" t="s">
-        <v>210</v>
-      </c>
-      <c r="G43" s="50" t="s">
-        <v>210</v>
-      </c>
-      <c r="H43" s="55" t="s">
-        <v>261</v>
-      </c>
-      <c r="I43" s="50" t="s">
-        <v>210</v>
-      </c>
-      <c r="J43" s="47">
-        <v>3</v>
-      </c>
-      <c r="K43" s="58" t="s">
-        <v>209</v>
+      <c r="C43" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="F43" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="G43" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="H43" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="I43" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="J43" s="48">
+        <v>1</v>
+      </c>
+      <c r="K43" s="28">
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="64">
-        <f>ROW(B44) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="D44" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="E44" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="F44" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="G44" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="H44" s="54" t="s">
-        <v>249</v>
-      </c>
-      <c r="I44" s="51" t="s">
-        <v>210</v>
-      </c>
-      <c r="J44" s="48">
-        <v>1</v>
-      </c>
-      <c r="K44" s="28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="C44" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="F44" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="G44" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="H44" s="55" t="s">
+        <v>254</v>
+      </c>
+      <c r="I44" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="J44" s="47">
+        <v>1</v>
+      </c>
+      <c r="K44" s="29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E45" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="F45" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="G45" s="44" t="s">
-        <v>172</v>
-      </c>
-      <c r="H45" s="55" t="s">
-        <v>261</v>
-      </c>
-      <c r="I45" s="50" t="s">
-        <v>210</v>
-      </c>
-      <c r="J45" s="47">
-        <v>1</v>
-      </c>
-      <c r="K45" s="29">
+      <c r="C45" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="E45" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="F45" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="G45" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="H45" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I45" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="J45" s="48">
+        <v>1</v>
+      </c>
+      <c r="K45" s="28">
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="64">
-        <f>ROW(B46) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="D46" s="54" t="s">
-        <v>89</v>
-      </c>
-      <c r="E46" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="F46" s="45" t="s">
-        <v>147</v>
-      </c>
-      <c r="G46" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="H46" s="54" t="s">
-        <v>250</v>
-      </c>
-      <c r="I46" s="51" t="s">
-        <v>210</v>
-      </c>
-      <c r="J46" s="48">
-        <v>1</v>
-      </c>
-      <c r="K46" s="28">
+      <c r="C46" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="E46" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="F46" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="G46" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="H46" s="55" t="s">
+        <v>254</v>
+      </c>
+      <c r="I46" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="J46" s="47">
+        <v>1</v>
+      </c>
+      <c r="K46" s="29">
         <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="D47" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="E47" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="F47" s="44" t="s">
-        <v>148</v>
-      </c>
-      <c r="G47" s="44" t="s">
-        <v>174</v>
-      </c>
-      <c r="H47" s="55" t="s">
-        <v>261</v>
-      </c>
-      <c r="I47" s="50" t="s">
-        <v>210</v>
-      </c>
-      <c r="J47" s="47">
-        <v>1</v>
-      </c>
-      <c r="K47" s="29">
+      <c r="C47" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="D47" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="E47" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="F47" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="G47" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="H47" s="54" t="s">
+        <v>244</v>
+      </c>
+      <c r="I47" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="J47" s="48">
+        <v>1</v>
+      </c>
+      <c r="K47" s="28">
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="64">
-        <f>ROW(B48) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="D48" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="E48" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="F48" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="G48" s="45" t="s">
-        <v>175</v>
-      </c>
-      <c r="H48" s="54" t="s">
-        <v>251</v>
-      </c>
-      <c r="I48" s="51" t="s">
-        <v>210</v>
-      </c>
-      <c r="J48" s="48">
-        <v>1</v>
-      </c>
-      <c r="K48" s="28">
+      <c r="C48" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E48" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="F48" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="G48" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="H48" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="I48" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="J48" s="47">
+        <v>1</v>
+      </c>
+      <c r="K48" s="29">
         <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="D49" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="E49" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="F49" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="G49" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="H49" s="55" t="s">
-        <v>209</v>
-      </c>
-      <c r="I49" s="50" t="s">
-        <v>210</v>
-      </c>
-      <c r="J49" s="47">
-        <v>1</v>
-      </c>
-      <c r="K49" s="29">
+      <c r="C49" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49" s="54" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="F49" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="G49" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="H49" s="54" t="s">
+        <v>245</v>
+      </c>
+      <c r="I49" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="J49" s="48">
+        <v>1</v>
+      </c>
+      <c r="K49" s="28">
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="64">
-        <f>ROW(B50) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="D50" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="E50" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="F50" s="45" t="s">
-        <v>151</v>
-      </c>
-      <c r="G50" s="45" t="s">
-        <v>177</v>
-      </c>
-      <c r="H50" s="54" t="s">
-        <v>252</v>
-      </c>
-      <c r="I50" s="51" t="s">
-        <v>210</v>
-      </c>
-      <c r="J50" s="48">
-        <v>1</v>
-      </c>
-      <c r="K50" s="28">
+      <c r="C50" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="F50" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="G50" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="H50" s="53" t="s">
+        <v>246</v>
+      </c>
+      <c r="I50" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="J50" s="47">
+        <v>1</v>
+      </c>
+      <c r="K50" s="29">
         <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="D51" s="53" t="s">
-        <v>94</v>
-      </c>
-      <c r="E51" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="F51" s="44" t="s">
-        <v>152</v>
-      </c>
-      <c r="G51" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="H51" s="53" t="s">
-        <v>253</v>
-      </c>
-      <c r="I51" s="50" t="s">
-        <v>210</v>
-      </c>
-      <c r="J51" s="47">
-        <v>1</v>
-      </c>
-      <c r="K51" s="29">
-        <v>6</v>
+      <c r="C51" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="E51" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="F51" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="G51" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="H51" s="54" t="s">
+        <v>247</v>
+      </c>
+      <c r="I51" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="J51" s="48">
+        <v>1</v>
+      </c>
+      <c r="K51" s="28">
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="64">
-        <f>ROW(B52) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="D52" s="54" t="s">
-        <v>95</v>
-      </c>
-      <c r="E52" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="F52" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="G52" s="45" t="s">
-        <v>179</v>
-      </c>
-      <c r="H52" s="54" t="s">
-        <v>254</v>
-      </c>
-      <c r="I52" s="51" t="s">
-        <v>210</v>
-      </c>
-      <c r="J52" s="48">
-        <v>1</v>
-      </c>
-      <c r="K52" s="28">
-        <v>10</v>
+      <c r="C52" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="E52" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="F52" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="G52" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="H52" s="53" t="s">
+        <v>248</v>
+      </c>
+      <c r="I52" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="J52" s="47">
+        <v>2</v>
+      </c>
+      <c r="K52" s="29">
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="64">
-        <f t="shared" si="0"/>
+        <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
-      <c r="C53" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="D53" s="53" t="s">
-        <v>96</v>
-      </c>
-      <c r="E53" s="44" t="s">
-        <v>208</v>
-      </c>
-      <c r="F53" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="G53" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="H53" s="53" t="s">
-        <v>255</v>
-      </c>
-      <c r="I53" s="44" t="s">
-        <v>205</v>
-      </c>
-      <c r="J53" s="47">
-        <v>2</v>
-      </c>
-      <c r="K53" s="29">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="C53" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="E53" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="F53" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="G53" s="45" t="s">
+        <v>174</v>
+      </c>
+      <c r="H53" s="54" t="s">
+        <v>249</v>
+      </c>
+      <c r="I53" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="J53" s="48">
+        <v>1</v>
+      </c>
+      <c r="K53" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
-      <c r="B54" s="64">
-        <f>ROW(B54) - ROW($B$9)</f>
+      <c r="B54" s="65">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="D54" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="E54" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="F54" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="G54" s="45" t="s">
-        <v>180</v>
-      </c>
-      <c r="H54" s="54" t="s">
-        <v>256</v>
-      </c>
-      <c r="I54" s="45" t="s">
-        <v>206</v>
-      </c>
-      <c r="J54" s="48">
-        <v>1</v>
-      </c>
-      <c r="K54" s="28">
+      <c r="C54" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="E54" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="F54" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="G54" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="H54" s="56" t="s">
+        <v>250</v>
+      </c>
+      <c r="I54" s="60" t="s">
+        <v>201</v>
+      </c>
+      <c r="J54" s="49">
+        <v>1</v>
+      </c>
+      <c r="K54" s="38">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="B55" s="65">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="C55" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="D55" s="56" t="s">
-        <v>98</v>
-      </c>
-      <c r="E55" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="F55" s="60" t="s">
-        <v>131</v>
-      </c>
-      <c r="G55" s="60" t="s">
-        <v>181</v>
-      </c>
-      <c r="H55" s="56" t="s">
-        <v>257</v>
-      </c>
-      <c r="I55" s="60" t="s">
-        <v>207</v>
-      </c>
-      <c r="J55" s="49">
-        <v>1</v>
-      </c>
-      <c r="K55" s="38">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="39"/>
+      <c r="C55" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="41"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="59"/>
+      <c r="G55" s="59"/>
+      <c r="H55" s="59"/>
+      <c r="I55" s="107"/>
+      <c r="J55" s="107"/>
+      <c r="K55" s="108"/>
+    </row>
+    <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
-      <c r="B56" s="39"/>
-      <c r="C56" s="40" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56" s="41"/>
-      <c r="E56" s="42"/>
-      <c r="F56" s="59"/>
-      <c r="G56" s="59"/>
-      <c r="H56" s="59"/>
-      <c r="I56" s="70"/>
-      <c r="J56" s="70"/>
-      <c r="K56" s="71"/>
-    </row>
-    <row r="57" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="1"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="8" t="s">
+      <c r="B56" s="22"/>
+      <c r="C56" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
-      <c r="H57" s="37"/>
-      <c r="I57" s="72"/>
-      <c r="J57" s="72"/>
-      <c r="K57" s="73"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="37"/>
+      <c r="H56" s="37"/>
+      <c r="I56" s="109"/>
+      <c r="J56" s="109"/>
+      <c r="K56" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="I56:K57"/>
+    <mergeCell ref="I55:K56"/>
     <mergeCell ref="K3:K8"/>
     <mergeCell ref="J3:J8"/>
     <mergeCell ref="I2:K2"/>
@@ -3719,4 +3930,1680 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348A8FCB-7220-490A-87EB-3CE6A0C47FB5}">
+  <dimension ref="B1:K56"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H1" s="105"/>
+    </row>
+    <row r="2" spans="2:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="70"/>
+      <c r="C2" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="71"/>
+      <c r="E2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="118"/>
+    </row>
+    <row r="3" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="19"/>
+      <c r="C3" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="72"/>
+      <c r="E3" s="73" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="72"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="119"/>
+    </row>
+    <row r="4" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="19"/>
+      <c r="C4" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="72"/>
+      <c r="E4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="75"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="111"/>
+    </row>
+    <row r="5" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="19"/>
+      <c r="C5" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="72"/>
+      <c r="E5" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="77"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="111"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B6" s="20"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
+      <c r="K6" s="111"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="21"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="111"/>
+    </row>
+    <row r="8" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="33"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="111"/>
+    </row>
+    <row r="9" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="J9" s="62" t="s">
+        <v>263</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" s="94" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="84">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="95" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="95" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="96" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="95" t="s">
+        <v>150</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="I10" s="95" t="s">
+        <v>177</v>
+      </c>
+      <c r="J10" s="85">
+        <v>3</v>
+      </c>
+      <c r="K10" s="36">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="84">
+        <f t="shared" ref="B11:B54" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="98" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="97" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="G11" s="97" t="s">
+        <v>150</v>
+      </c>
+      <c r="H11" s="53" t="s">
+        <v>209</v>
+      </c>
+      <c r="I11" s="97" t="s">
+        <v>178</v>
+      </c>
+      <c r="J11" s="86">
+        <v>24</v>
+      </c>
+      <c r="K11" s="29">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="84">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C12" s="99" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="100" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="99" t="s">
+        <v>98</v>
+      </c>
+      <c r="F12" s="100" t="s">
+        <v>129</v>
+      </c>
+      <c r="G12" s="99" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" s="54" t="s">
+        <v>210</v>
+      </c>
+      <c r="I12" s="99" t="s">
+        <v>179</v>
+      </c>
+      <c r="J12" s="87">
+        <v>1</v>
+      </c>
+      <c r="K12" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="84">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="97" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="98" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="97" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="98" t="s">
+        <v>130</v>
+      </c>
+      <c r="G13" s="97" t="s">
+        <v>152</v>
+      </c>
+      <c r="H13" s="53" t="s">
+        <v>212</v>
+      </c>
+      <c r="I13" s="97" t="s">
+        <v>180</v>
+      </c>
+      <c r="J13" s="86">
+        <v>8</v>
+      </c>
+      <c r="K13" s="29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="84">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C14" s="99" t="s">
+        <v>272</v>
+      </c>
+      <c r="D14" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="99" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="100" t="s">
+        <v>131</v>
+      </c>
+      <c r="G14" s="99" t="s">
+        <v>153</v>
+      </c>
+      <c r="H14" s="54" t="s">
+        <v>211</v>
+      </c>
+      <c r="I14" s="99" t="s">
+        <v>181</v>
+      </c>
+      <c r="J14" s="87">
+        <v>2</v>
+      </c>
+      <c r="K14" s="28">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="84">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="97" t="s">
+        <v>273</v>
+      </c>
+      <c r="D15" s="98" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="97" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="98" t="s">
+        <v>132</v>
+      </c>
+      <c r="G15" s="97" t="s">
+        <v>152</v>
+      </c>
+      <c r="H15" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="I15" s="97" t="s">
+        <v>182</v>
+      </c>
+      <c r="J15" s="86">
+        <v>7</v>
+      </c>
+      <c r="K15" s="29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="84">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C16" s="99" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="100" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="99" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="100" t="s">
+        <v>133</v>
+      </c>
+      <c r="G16" s="99" t="s">
+        <v>150</v>
+      </c>
+      <c r="H16" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="I16" s="99" t="s">
+        <v>183</v>
+      </c>
+      <c r="J16" s="87">
+        <v>1</v>
+      </c>
+      <c r="K16" s="32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="84">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="97" t="s">
+        <v>274</v>
+      </c>
+      <c r="D17" s="98" t="s">
+        <v>275</v>
+      </c>
+      <c r="E17" s="97" t="s">
+        <v>276</v>
+      </c>
+      <c r="F17" s="98" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="97" t="s">
+        <v>150</v>
+      </c>
+      <c r="H17" s="125" t="s">
+        <v>281</v>
+      </c>
+      <c r="I17" s="97" t="s">
+        <v>278</v>
+      </c>
+      <c r="J17" s="86">
+        <v>1</v>
+      </c>
+      <c r="K17" s="29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="84">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C18" s="99" t="s">
+        <v>269</v>
+      </c>
+      <c r="D18" s="100" t="s">
+        <v>216</v>
+      </c>
+      <c r="E18" s="99" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="100" t="s">
+        <v>217</v>
+      </c>
+      <c r="G18" s="99" t="s">
+        <v>152</v>
+      </c>
+      <c r="H18" s="54" t="s">
+        <v>215</v>
+      </c>
+      <c r="I18" s="99" t="s">
+        <v>184</v>
+      </c>
+      <c r="J18" s="124">
+        <v>1</v>
+      </c>
+      <c r="K18" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="84">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="97" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="98" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="97" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="98" t="s">
+        <v>134</v>
+      </c>
+      <c r="G19" s="97" t="s">
+        <v>150</v>
+      </c>
+      <c r="H19" s="53" t="s">
+        <v>218</v>
+      </c>
+      <c r="I19" s="97" t="s">
+        <v>185</v>
+      </c>
+      <c r="J19" s="86">
+        <v>1</v>
+      </c>
+      <c r="K19" s="29">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="84">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="99" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="100" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="99" t="s">
+        <v>202</v>
+      </c>
+      <c r="F20" s="100" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="99" t="s">
+        <v>154</v>
+      </c>
+      <c r="H20" s="54" t="s">
+        <v>219</v>
+      </c>
+      <c r="I20" s="106" t="s">
+        <v>203</v>
+      </c>
+      <c r="J20" s="124">
+        <v>1</v>
+      </c>
+      <c r="K20" s="32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="84">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="97" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="97" t="s">
+        <v>202</v>
+      </c>
+      <c r="F21" s="98" t="s">
+        <v>100</v>
+      </c>
+      <c r="G21" s="97" t="s">
+        <v>155</v>
+      </c>
+      <c r="H21" s="53" t="s">
+        <v>220</v>
+      </c>
+      <c r="I21" s="101" t="s">
+        <v>203</v>
+      </c>
+      <c r="J21" s="86">
+        <v>1</v>
+      </c>
+      <c r="K21" s="29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="84">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="99" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="100" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="99" t="s">
+        <v>202</v>
+      </c>
+      <c r="F22" s="100" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="99" t="s">
+        <v>156</v>
+      </c>
+      <c r="H22" s="54" t="s">
+        <v>221</v>
+      </c>
+      <c r="I22" s="106" t="s">
+        <v>203</v>
+      </c>
+      <c r="J22" s="124">
+        <v>1</v>
+      </c>
+      <c r="K22" s="32">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="84">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="97" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="97" t="s">
+        <v>202</v>
+      </c>
+      <c r="F23" s="98" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" s="97" t="s">
+        <v>157</v>
+      </c>
+      <c r="H23" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="I23" s="101" t="s">
+        <v>203</v>
+      </c>
+      <c r="J23" s="86">
+        <v>1</v>
+      </c>
+      <c r="K23" s="29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="84">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C24" s="99" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="100" t="s">
+        <v>256</v>
+      </c>
+      <c r="E24" s="99" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="100" t="s">
+        <v>258</v>
+      </c>
+      <c r="G24" s="106" t="s">
+        <v>260</v>
+      </c>
+      <c r="H24" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="I24" s="106" t="s">
+        <v>203</v>
+      </c>
+      <c r="J24" s="124">
+        <v>1</v>
+      </c>
+      <c r="K24" s="32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="84">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="97" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="98" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="97" t="s">
+        <v>202</v>
+      </c>
+      <c r="F25" s="98" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="97" t="s">
+        <v>154</v>
+      </c>
+      <c r="H25" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="I25" s="101" t="s">
+        <v>203</v>
+      </c>
+      <c r="J25" s="86">
+        <v>1</v>
+      </c>
+      <c r="K25" s="29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="84">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C26" s="99" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="100" t="s">
+        <v>257</v>
+      </c>
+      <c r="E26" s="99" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" s="100" t="s">
+        <v>259</v>
+      </c>
+      <c r="G26" s="106" t="s">
+        <v>260</v>
+      </c>
+      <c r="H26" s="54" t="s">
+        <v>262</v>
+      </c>
+      <c r="I26" s="106" t="s">
+        <v>203</v>
+      </c>
+      <c r="J26" s="124">
+        <v>1</v>
+      </c>
+      <c r="K26" s="32">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="84">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C27" s="97" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="98" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="97" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" s="98" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="97" t="s">
+        <v>153</v>
+      </c>
+      <c r="H27" s="55" t="s">
+        <v>255</v>
+      </c>
+      <c r="I27" s="97" t="s">
+        <v>186</v>
+      </c>
+      <c r="J27" s="86">
+        <v>1</v>
+      </c>
+      <c r="K27" s="29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="84">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C28" s="99" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="99" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" s="100" t="s">
+        <v>135</v>
+      </c>
+      <c r="G28" s="99" t="s">
+        <v>158</v>
+      </c>
+      <c r="H28" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="I28" s="99" t="s">
+        <v>187</v>
+      </c>
+      <c r="J28" s="124">
+        <v>1</v>
+      </c>
+      <c r="K28" s="32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="84">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" s="97" t="s">
+        <v>202</v>
+      </c>
+      <c r="F29" s="98" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="97" t="s">
+        <v>159</v>
+      </c>
+      <c r="H29" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="I29" s="97" t="s">
+        <v>188</v>
+      </c>
+      <c r="J29" s="86">
+        <v>1</v>
+      </c>
+      <c r="K29" s="29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="84">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C30" s="99" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="99" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" s="100" t="s">
+        <v>136</v>
+      </c>
+      <c r="G30" s="99" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" s="54" t="s">
+        <v>227</v>
+      </c>
+      <c r="I30" s="99" t="s">
+        <v>189</v>
+      </c>
+      <c r="J30" s="124">
+        <v>1</v>
+      </c>
+      <c r="K30" s="32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="84">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C31" s="97" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="E31" s="97" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31" s="98" t="s">
+        <v>137</v>
+      </c>
+      <c r="G31" s="97" t="s">
+        <v>150</v>
+      </c>
+      <c r="H31" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="I31" s="101" t="s">
+        <v>204</v>
+      </c>
+      <c r="J31" s="86">
+        <v>1</v>
+      </c>
+      <c r="K31" s="29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="84">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C32" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="99" t="s">
+        <v>202</v>
+      </c>
+      <c r="F32" s="100" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" s="99" t="s">
+        <v>160</v>
+      </c>
+      <c r="H32" s="54" t="s">
+        <v>226</v>
+      </c>
+      <c r="I32" s="99" t="s">
+        <v>190</v>
+      </c>
+      <c r="J32" s="124">
+        <v>1</v>
+      </c>
+      <c r="K32" s="32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="84">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C33" s="97" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="98" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" s="97" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="G33" s="97" t="s">
+        <v>161</v>
+      </c>
+      <c r="H33" s="53" t="s">
+        <v>230</v>
+      </c>
+      <c r="I33" s="101" t="s">
+        <v>204</v>
+      </c>
+      <c r="J33" s="86">
+        <v>2</v>
+      </c>
+      <c r="K33" s="29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="84">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C34" s="99" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="100" t="s">
+        <v>75</v>
+      </c>
+      <c r="E34" s="99" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="G34" s="99" t="s">
+        <v>161</v>
+      </c>
+      <c r="H34" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="I34" s="106" t="s">
+        <v>204</v>
+      </c>
+      <c r="J34" s="124">
+        <v>1</v>
+      </c>
+      <c r="K34" s="32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="84">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C35" s="97" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="102" t="s">
+        <v>264</v>
+      </c>
+      <c r="E35" s="97" t="s">
+        <v>265</v>
+      </c>
+      <c r="F35" s="98" t="s">
+        <v>266</v>
+      </c>
+      <c r="G35" s="97" t="s">
+        <v>267</v>
+      </c>
+      <c r="H35" s="53" t="s">
+        <v>268</v>
+      </c>
+      <c r="I35" s="97" t="s">
+        <v>191</v>
+      </c>
+      <c r="J35" s="86">
+        <v>1</v>
+      </c>
+      <c r="K35" s="29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="84">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="103" t="s">
+        <v>253</v>
+      </c>
+      <c r="E36" s="99" t="s">
+        <v>113</v>
+      </c>
+      <c r="F36" s="103" t="s">
+        <v>252</v>
+      </c>
+      <c r="G36" s="104" t="s">
+        <v>152</v>
+      </c>
+      <c r="H36" s="54" t="s">
+        <v>251</v>
+      </c>
+      <c r="I36" s="99" t="s">
+        <v>192</v>
+      </c>
+      <c r="J36" s="124">
+        <v>4</v>
+      </c>
+      <c r="K36" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="84">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C37" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="98" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" s="97" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" s="98" t="s">
+        <v>138</v>
+      </c>
+      <c r="G37" s="97" t="s">
+        <v>152</v>
+      </c>
+      <c r="H37" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="I37" s="97" t="s">
+        <v>193</v>
+      </c>
+      <c r="J37" s="86">
+        <v>10</v>
+      </c>
+      <c r="K37" s="29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="84">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="99" t="s">
+        <v>279</v>
+      </c>
+      <c r="D38" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="99" t="s">
+        <v>113</v>
+      </c>
+      <c r="F38" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="G38" s="99" t="s">
+        <v>163</v>
+      </c>
+      <c r="H38" s="54" t="s">
+        <v>237</v>
+      </c>
+      <c r="I38" s="99" t="s">
+        <v>195</v>
+      </c>
+      <c r="J38" s="124">
+        <v>8</v>
+      </c>
+      <c r="K38" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="84">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C39" s="97" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="98" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="97" t="s">
+        <v>113</v>
+      </c>
+      <c r="F39" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="G39" s="97" t="s">
+        <v>163</v>
+      </c>
+      <c r="H39" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="I39" s="97" t="s">
+        <v>196</v>
+      </c>
+      <c r="J39" s="86">
+        <v>2</v>
+      </c>
+      <c r="K39" s="29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="84">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="99" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="100" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="99" t="s">
+        <v>112</v>
+      </c>
+      <c r="F40" s="45" t="s">
+        <v>240</v>
+      </c>
+      <c r="G40" s="99" t="s">
+        <v>164</v>
+      </c>
+      <c r="H40" s="54" t="s">
+        <v>241</v>
+      </c>
+      <c r="I40" s="99" t="s">
+        <v>197</v>
+      </c>
+      <c r="J40" s="124">
+        <v>2</v>
+      </c>
+      <c r="K40" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="84">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="97" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="97" t="s">
+        <v>113</v>
+      </c>
+      <c r="F41" s="98" t="s">
+        <v>140</v>
+      </c>
+      <c r="G41" s="97" t="s">
+        <v>152</v>
+      </c>
+      <c r="H41" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="I41" s="97" t="s">
+        <v>198</v>
+      </c>
+      <c r="J41" s="86">
+        <v>1</v>
+      </c>
+      <c r="K41" s="29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="84">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C42" s="99" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="100" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="99" t="s">
+        <v>114</v>
+      </c>
+      <c r="F42" s="126" t="s">
+        <v>204</v>
+      </c>
+      <c r="G42" s="106" t="s">
+        <v>204</v>
+      </c>
+      <c r="H42" s="57" t="s">
+        <v>254</v>
+      </c>
+      <c r="I42" s="106" t="s">
+        <v>204</v>
+      </c>
+      <c r="J42" s="124">
+        <v>3</v>
+      </c>
+      <c r="K42" s="127" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="84">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C43" s="97" t="s">
+        <v>280</v>
+      </c>
+      <c r="D43" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" s="97" t="s">
+        <v>202</v>
+      </c>
+      <c r="F43" s="98" t="s">
+        <v>115</v>
+      </c>
+      <c r="G43" s="97" t="s">
+        <v>165</v>
+      </c>
+      <c r="H43" s="53" t="s">
+        <v>242</v>
+      </c>
+      <c r="I43" s="101" t="s">
+        <v>204</v>
+      </c>
+      <c r="J43" s="86">
+        <v>2</v>
+      </c>
+      <c r="K43" s="29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="84">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C44" s="99" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="99" t="s">
+        <v>116</v>
+      </c>
+      <c r="F44" s="100" t="s">
+        <v>141</v>
+      </c>
+      <c r="G44" s="99" t="s">
+        <v>166</v>
+      </c>
+      <c r="H44" s="57" t="s">
+        <v>254</v>
+      </c>
+      <c r="I44" s="106" t="s">
+        <v>204</v>
+      </c>
+      <c r="J44" s="124">
+        <v>1</v>
+      </c>
+      <c r="K44" s="32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="84">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C45" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="98" t="s">
+        <v>85</v>
+      </c>
+      <c r="E45" s="97" t="s">
+        <v>117</v>
+      </c>
+      <c r="F45" s="98" t="s">
+        <v>142</v>
+      </c>
+      <c r="G45" s="97" t="s">
+        <v>167</v>
+      </c>
+      <c r="H45" s="53" t="s">
+        <v>243</v>
+      </c>
+      <c r="I45" s="101" t="s">
+        <v>204</v>
+      </c>
+      <c r="J45" s="86">
+        <v>1</v>
+      </c>
+      <c r="K45" s="29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="84">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C46" s="99" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="100" t="s">
+        <v>86</v>
+      </c>
+      <c r="E46" s="99" t="s">
+        <v>118</v>
+      </c>
+      <c r="F46" s="100" t="s">
+        <v>143</v>
+      </c>
+      <c r="G46" s="99" t="s">
+        <v>168</v>
+      </c>
+      <c r="H46" s="57" t="s">
+        <v>254</v>
+      </c>
+      <c r="I46" s="106" t="s">
+        <v>204</v>
+      </c>
+      <c r="J46" s="124">
+        <v>1</v>
+      </c>
+      <c r="K46" s="32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="84">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="C47" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="D47" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="E47" s="97" t="s">
+        <v>119</v>
+      </c>
+      <c r="F47" s="98" t="s">
+        <v>144</v>
+      </c>
+      <c r="G47" s="97" t="s">
+        <v>169</v>
+      </c>
+      <c r="H47" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="I47" s="101" t="s">
+        <v>204</v>
+      </c>
+      <c r="J47" s="86">
+        <v>1</v>
+      </c>
+      <c r="K47" s="29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="84">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C48" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="E48" s="99" t="s">
+        <v>120</v>
+      </c>
+      <c r="F48" s="100" t="s">
+        <v>145</v>
+      </c>
+      <c r="G48" s="99" t="s">
+        <v>170</v>
+      </c>
+      <c r="H48" s="57" t="s">
+        <v>203</v>
+      </c>
+      <c r="I48" s="106" t="s">
+        <v>204</v>
+      </c>
+      <c r="J48" s="124">
+        <v>1</v>
+      </c>
+      <c r="K48" s="32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="84">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C49" s="97" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="F49" s="98" t="s">
+        <v>146</v>
+      </c>
+      <c r="G49" s="97" t="s">
+        <v>171</v>
+      </c>
+      <c r="H49" s="53" t="s">
+        <v>245</v>
+      </c>
+      <c r="I49" s="101" t="s">
+        <v>204</v>
+      </c>
+      <c r="J49" s="86">
+        <v>1</v>
+      </c>
+      <c r="K49" s="29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="84">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C50" s="99" t="s">
+        <v>49</v>
+      </c>
+      <c r="D50" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" s="99" t="s">
+        <v>122</v>
+      </c>
+      <c r="F50" s="100" t="s">
+        <v>147</v>
+      </c>
+      <c r="G50" s="99" t="s">
+        <v>172</v>
+      </c>
+      <c r="H50" s="54" t="s">
+        <v>246</v>
+      </c>
+      <c r="I50" s="106" t="s">
+        <v>204</v>
+      </c>
+      <c r="J50" s="124">
+        <v>1</v>
+      </c>
+      <c r="K50" s="32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="84">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="C51" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="E51" s="97" t="s">
+        <v>123</v>
+      </c>
+      <c r="F51" s="98" t="s">
+        <v>148</v>
+      </c>
+      <c r="G51" s="97" t="s">
+        <v>173</v>
+      </c>
+      <c r="H51" s="53" t="s">
+        <v>247</v>
+      </c>
+      <c r="I51" s="101" t="s">
+        <v>204</v>
+      </c>
+      <c r="J51" s="86">
+        <v>1</v>
+      </c>
+      <c r="K51" s="29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="84">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C52" s="99" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" s="54" t="s">
+        <v>92</v>
+      </c>
+      <c r="E52" s="99" t="s">
+        <v>202</v>
+      </c>
+      <c r="F52" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="G52" s="99" t="s">
+        <v>174</v>
+      </c>
+      <c r="H52" s="54" t="s">
+        <v>248</v>
+      </c>
+      <c r="I52" s="99" t="s">
+        <v>199</v>
+      </c>
+      <c r="J52" s="124">
+        <v>2</v>
+      </c>
+      <c r="K52" s="32">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="84">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C53" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="E53" s="97" t="s">
+        <v>202</v>
+      </c>
+      <c r="F53" s="98" t="s">
+        <v>125</v>
+      </c>
+      <c r="G53" s="97" t="s">
+        <v>174</v>
+      </c>
+      <c r="H53" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="I53" s="97" t="s">
+        <v>200</v>
+      </c>
+      <c r="J53" s="86">
+        <v>1</v>
+      </c>
+      <c r="K53" s="29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="84">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="C54" s="128" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="129" t="s">
+        <v>94</v>
+      </c>
+      <c r="E54" s="128" t="s">
+        <v>202</v>
+      </c>
+      <c r="F54" s="130" t="s">
+        <v>126</v>
+      </c>
+      <c r="G54" s="128" t="s">
+        <v>175</v>
+      </c>
+      <c r="H54" s="129" t="s">
+        <v>250</v>
+      </c>
+      <c r="I54" s="128" t="s">
+        <v>201</v>
+      </c>
+      <c r="J54" s="131">
+        <v>1</v>
+      </c>
+      <c r="K54" s="132">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B55" s="88"/>
+      <c r="C55" s="89" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="90"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="120"/>
+      <c r="G55" s="120"/>
+      <c r="H55" s="120"/>
+      <c r="I55" s="120"/>
+      <c r="J55" s="120"/>
+      <c r="K55" s="121"/>
+    </row>
+    <row r="56" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="91"/>
+      <c r="C56" s="92" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="93"/>
+      <c r="E56" s="93"/>
+      <c r="F56" s="122"/>
+      <c r="G56" s="122"/>
+      <c r="H56" s="122"/>
+      <c r="I56" s="122"/>
+      <c r="J56" s="122"/>
+      <c r="K56" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="K3:K8"/>
+    <mergeCell ref="F55:K56"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D744508-2691-4D57-ACB2-B3FA38E0B969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4F51F9-7803-4E96-A4CA-C01A43F4E153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22515" yWindow="3405" windowWidth="11790" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="285">
   <si>
     <t>Component list</t>
   </si>
@@ -877,6 +877,15 @@
   </si>
   <si>
     <t>C126492</t>
+  </si>
+  <si>
+    <t>Quantity (1 Board)</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>DO NOT MOUNT</t>
   </si>
 </sst>
 </file>
@@ -886,7 +895,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1030,6 +1039,23 @@
       <color indexed="13"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1430,19 +1456,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1635,22 +1657,11 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1724,6 +1735,21 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -1779,31 +1805,39 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1882,7 +1916,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>10417</xdr:rowOff>
@@ -1890,10 +1924,10 @@
     <xdr:ext cx="1714500" cy="1104008"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D35ED14F-294C-4592-98D6-4CAC8DEA33B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09969436-8A94-45CE-BB95-34EF24CD6072}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1914,7 +1948,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14306550" y="620017"/>
+          <a:off x="13230225" y="620017"/>
           <a:ext cx="1714500" cy="1104008"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2215,8 +2249,8 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="116"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="114"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2231,9 +2265,9 @@
       <c r="F2" s="10"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="114"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="111"/>
+      <c r="K2" s="112"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2249,8 +2283,8 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="112"/>
-      <c r="K3" s="111"/>
+      <c r="J3" s="110"/>
+      <c r="K3" s="109"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2266,8 +2300,8 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="111"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="109"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2283,8 +2317,8 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="112"/>
-      <c r="K5" s="111"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="109"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2296,8 +2330,8 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="111"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="109"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2309,8 +2343,8 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="111"/>
+      <c r="J7" s="110"/>
+      <c r="K7" s="109"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2322,8 +2356,8 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="111"/>
+      <c r="J8" s="110"/>
+      <c r="K8" s="109"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -3899,9 +3933,9 @@
       <c r="F55" s="59"/>
       <c r="G55" s="59"/>
       <c r="H55" s="59"/>
-      <c r="I55" s="107"/>
-      <c r="J55" s="107"/>
-      <c r="K55" s="108"/>
+      <c r="I55" s="105"/>
+      <c r="J55" s="105"/>
+      <c r="K55" s="106"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
@@ -3914,9 +3948,9 @@
       <c r="F56" s="37"/>
       <c r="G56" s="37"/>
       <c r="H56" s="37"/>
-      <c r="I56" s="109"/>
-      <c r="J56" s="109"/>
-      <c r="K56" s="110"/>
+      <c r="I56" s="107"/>
+      <c r="J56" s="107"/>
+      <c r="K56" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3934,7 +3968,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348A8FCB-7220-490A-87EB-3CE6A0C47FB5}">
-  <dimension ref="B1:K56"/>
+  <dimension ref="B1:L56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -3946,13 +3980,13 @@
     <col min="8" max="8" width="18.85546875" customWidth="1"/>
     <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.28515625" customWidth="1"/>
+    <col min="11" max="12" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H1" s="105"/>
-    </row>
-    <row r="2" spans="2:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H1" s="98"/>
+    </row>
+    <row r="2" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="70"/>
       <c r="C2" s="71" t="s">
         <v>0</v>
@@ -3965,94 +3999,101 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="118"/>
-    </row>
-    <row r="3" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="116"/>
+    </row>
+    <row r="3" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" s="19"/>
-      <c r="C3" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="72"/>
-      <c r="E3" s="73" t="s">
+      <c r="C3" s="129" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="129"/>
+      <c r="E3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="72"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="119"/>
-    </row>
-    <row r="4" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F3" s="129"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="117"/>
+    </row>
+    <row r="4" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="19"/>
-      <c r="C4" s="72" t="s">
+      <c r="C4" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="72"/>
+      <c r="D4" s="129"/>
       <c r="E4" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="75"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="111"/>
-    </row>
-    <row r="5" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F4" s="72"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="109"/>
+    </row>
+    <row r="5" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="19"/>
-      <c r="C5" s="72" t="s">
+      <c r="C5" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="72"/>
+      <c r="D5" s="129"/>
       <c r="E5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="77"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="111"/>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F5" s="74"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="109"/>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="20"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
       <c r="E6" s="15"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="111"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F6" s="74"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
+      <c r="L6" s="109"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="21"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
       <c r="E7" s="17"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="111"/>
-    </row>
-    <row r="8" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F7" s="131"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="132"/>
+      <c r="L7" s="109"/>
+    </row>
+    <row r="8" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="33"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="81"/>
-      <c r="K8" s="111"/>
-    </row>
-    <row r="9" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="132"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="132"/>
+      <c r="L8" s="109"/>
+    </row>
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="30" t="s">
         <v>4</v>
       </c>
@@ -4078,1532 +4119,1585 @@
         <v>176</v>
       </c>
       <c r="J9" s="62" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="K9" s="30" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="10" spans="2:11" s="94" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="84">
+      <c r="L9" s="30" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" s="87" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="77">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="95" t="s">
+      <c r="C10" s="88" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="95" t="s">
+      <c r="E10" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="96" t="s">
+      <c r="F10" s="89" t="s">
         <v>128</v>
       </c>
-      <c r="G10" s="95" t="s">
+      <c r="G10" s="88" t="s">
         <v>150</v>
       </c>
       <c r="H10" s="52" t="s">
         <v>206</v>
       </c>
-      <c r="I10" s="95" t="s">
+      <c r="I10" s="88" t="s">
         <v>177</v>
       </c>
-      <c r="J10" s="85">
+      <c r="J10" s="78">
         <v>3</v>
       </c>
       <c r="K10" s="36">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="84">
+      <c r="L10" s="36"/>
+    </row>
+    <row r="11" spans="2:12" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="77">
         <f t="shared" ref="B11:B54" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="44" t="s">
         <v>271</v>
       </c>
-      <c r="D11" s="98" t="s">
+      <c r="D11" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="97" t="s">
+      <c r="E11" s="90" t="s">
         <v>97</v>
       </c>
       <c r="F11" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="G11" s="97" t="s">
+      <c r="G11" s="90" t="s">
         <v>150</v>
       </c>
       <c r="H11" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="I11" s="97" t="s">
+      <c r="I11" s="90" t="s">
         <v>178</v>
       </c>
-      <c r="J11" s="86">
+      <c r="J11" s="79">
         <v>24</v>
       </c>
       <c r="K11" s="29">
         <v>150</v>
       </c>
-    </row>
-    <row r="12" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="84">
+      <c r="L11" s="29"/>
+    </row>
+    <row r="12" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="77">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="99" t="s">
+      <c r="C12" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="100" t="s">
+      <c r="D12" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="99" t="s">
+      <c r="E12" s="92" t="s">
         <v>98</v>
       </c>
-      <c r="F12" s="100" t="s">
+      <c r="F12" s="93" t="s">
         <v>129</v>
       </c>
-      <c r="G12" s="99" t="s">
+      <c r="G12" s="92" t="s">
         <v>151</v>
       </c>
       <c r="H12" s="54" t="s">
         <v>210</v>
       </c>
-      <c r="I12" s="99" t="s">
+      <c r="I12" s="92" t="s">
         <v>179</v>
       </c>
-      <c r="J12" s="87">
+      <c r="J12" s="80">
         <v>1</v>
       </c>
       <c r="K12" s="28">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="84">
+      <c r="L12" s="28"/>
+    </row>
+    <row r="13" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="77">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="97" t="s">
+      <c r="C13" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="98" t="s">
+      <c r="D13" s="91" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="97" t="s">
+      <c r="E13" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="98" t="s">
+      <c r="F13" s="91" t="s">
         <v>130</v>
       </c>
-      <c r="G13" s="97" t="s">
+      <c r="G13" s="90" t="s">
         <v>152</v>
       </c>
       <c r="H13" s="53" t="s">
         <v>212</v>
       </c>
-      <c r="I13" s="97" t="s">
+      <c r="I13" s="90" t="s">
         <v>180</v>
       </c>
-      <c r="J13" s="86">
+      <c r="J13" s="79">
         <v>8</v>
       </c>
       <c r="K13" s="29">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="84">
+      <c r="L13" s="29"/>
+    </row>
+    <row r="14" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="77">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="99" t="s">
+      <c r="C14" s="92" t="s">
         <v>272</v>
       </c>
       <c r="D14" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="99" t="s">
+      <c r="E14" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="100" t="s">
+      <c r="F14" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="G14" s="99" t="s">
+      <c r="G14" s="92" t="s">
         <v>153</v>
       </c>
       <c r="H14" s="54" t="s">
         <v>211</v>
       </c>
-      <c r="I14" s="99" t="s">
+      <c r="I14" s="92" t="s">
         <v>181</v>
       </c>
-      <c r="J14" s="87">
+      <c r="J14" s="80">
         <v>2</v>
       </c>
       <c r="K14" s="28">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="84">
+      <c r="L14" s="28"/>
+    </row>
+    <row r="15" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="77">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="97" t="s">
+      <c r="C15" s="90" t="s">
         <v>273</v>
       </c>
-      <c r="D15" s="98" t="s">
+      <c r="D15" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="97" t="s">
+      <c r="E15" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="98" t="s">
+      <c r="F15" s="91" t="s">
         <v>132</v>
       </c>
-      <c r="G15" s="97" t="s">
+      <c r="G15" s="90" t="s">
         <v>152</v>
       </c>
       <c r="H15" s="53" t="s">
         <v>213</v>
       </c>
-      <c r="I15" s="97" t="s">
+      <c r="I15" s="90" t="s">
         <v>182</v>
       </c>
-      <c r="J15" s="86">
+      <c r="J15" s="79">
         <v>7</v>
       </c>
       <c r="K15" s="29">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="84">
+      <c r="L15" s="29"/>
+    </row>
+    <row r="16" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="77">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="99" t="s">
+      <c r="C16" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="100" t="s">
+      <c r="D16" s="93" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="99" t="s">
+      <c r="E16" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="100" t="s">
+      <c r="F16" s="93" t="s">
         <v>133</v>
       </c>
-      <c r="G16" s="99" t="s">
+      <c r="G16" s="92" t="s">
         <v>150</v>
       </c>
       <c r="H16" s="54" t="s">
         <v>214</v>
       </c>
-      <c r="I16" s="99" t="s">
+      <c r="I16" s="92" t="s">
         <v>183</v>
       </c>
-      <c r="J16" s="87">
+      <c r="J16" s="80">
         <v>1</v>
       </c>
       <c r="K16" s="32">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="84">
+      <c r="L16" s="32"/>
+    </row>
+    <row r="17" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="77">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="97" t="s">
+      <c r="C17" s="90" t="s">
         <v>274</v>
       </c>
-      <c r="D17" s="98" t="s">
+      <c r="D17" s="91" t="s">
         <v>275</v>
       </c>
-      <c r="E17" s="97" t="s">
+      <c r="E17" s="90" t="s">
         <v>276</v>
       </c>
-      <c r="F17" s="98" t="s">
+      <c r="F17" s="91" t="s">
         <v>277</v>
       </c>
-      <c r="G17" s="97" t="s">
+      <c r="G17" s="90" t="s">
         <v>150</v>
       </c>
-      <c r="H17" s="125" t="s">
+      <c r="H17" s="101" t="s">
         <v>281</v>
       </c>
-      <c r="I17" s="97" t="s">
+      <c r="I17" s="90" t="s">
         <v>278</v>
       </c>
-      <c r="J17" s="86">
+      <c r="J17" s="79">
         <v>1</v>
       </c>
       <c r="K17" s="29">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="84">
+      <c r="L17" s="29"/>
+    </row>
+    <row r="18" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="77">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="99" t="s">
+      <c r="C18" s="92" t="s">
         <v>269</v>
       </c>
-      <c r="D18" s="100" t="s">
+      <c r="D18" s="93" t="s">
         <v>216</v>
       </c>
-      <c r="E18" s="99" t="s">
+      <c r="E18" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="F18" s="100" t="s">
+      <c r="F18" s="93" t="s">
         <v>217</v>
       </c>
-      <c r="G18" s="99" t="s">
+      <c r="G18" s="92" t="s">
         <v>152</v>
       </c>
       <c r="H18" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="I18" s="99" t="s">
+      <c r="I18" s="92" t="s">
         <v>184</v>
       </c>
-      <c r="J18" s="124">
+      <c r="J18" s="100">
         <v>1</v>
       </c>
       <c r="K18" s="32">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="84">
+      <c r="L18" s="32"/>
+    </row>
+    <row r="19" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="77">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="97" t="s">
+      <c r="C19" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="98" t="s">
+      <c r="D19" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="97" t="s">
+      <c r="E19" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="F19" s="98" t="s">
+      <c r="F19" s="91" t="s">
         <v>134</v>
       </c>
-      <c r="G19" s="97" t="s">
+      <c r="G19" s="90" t="s">
         <v>150</v>
       </c>
       <c r="H19" s="53" t="s">
         <v>218</v>
       </c>
-      <c r="I19" s="97" t="s">
+      <c r="I19" s="90" t="s">
         <v>185</v>
       </c>
-      <c r="J19" s="86">
+      <c r="J19" s="79">
         <v>1</v>
       </c>
       <c r="K19" s="29">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="84">
+      <c r="L19" s="29"/>
+    </row>
+    <row r="20" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="77">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="99" t="s">
+      <c r="C20" s="92" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="100" t="s">
+      <c r="D20" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="99" t="s">
+      <c r="E20" s="92" t="s">
         <v>202</v>
       </c>
-      <c r="F20" s="100" t="s">
+      <c r="F20" s="93" t="s">
         <v>99</v>
       </c>
-      <c r="G20" s="99" t="s">
+      <c r="G20" s="92" t="s">
         <v>154</v>
       </c>
       <c r="H20" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="I20" s="106" t="s">
+      <c r="I20" s="99" t="s">
         <v>203</v>
       </c>
-      <c r="J20" s="124">
+      <c r="J20" s="100">
         <v>1</v>
       </c>
       <c r="K20" s="32">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="84">
+      <c r="L20" s="32"/>
+    </row>
+    <row r="21" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="77">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="97" t="s">
+      <c r="C21" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="98" t="s">
+      <c r="D21" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="97" t="s">
+      <c r="E21" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F21" s="98" t="s">
+      <c r="F21" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="G21" s="97" t="s">
+      <c r="G21" s="90" t="s">
         <v>155</v>
       </c>
       <c r="H21" s="53" t="s">
         <v>220</v>
       </c>
-      <c r="I21" s="101" t="s">
+      <c r="I21" s="94" t="s">
         <v>203</v>
       </c>
-      <c r="J21" s="86">
+      <c r="J21" s="79">
         <v>1</v>
       </c>
       <c r="K21" s="29">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="84">
+      <c r="L21" s="29"/>
+    </row>
+    <row r="22" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="77">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="99" t="s">
+      <c r="C22" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="100" t="s">
+      <c r="D22" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="99" t="s">
+      <c r="E22" s="92" t="s">
         <v>202</v>
       </c>
-      <c r="F22" s="100" t="s">
+      <c r="F22" s="93" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="99" t="s">
+      <c r="G22" s="92" t="s">
         <v>156</v>
       </c>
       <c r="H22" s="54" t="s">
         <v>221</v>
       </c>
-      <c r="I22" s="106" t="s">
+      <c r="I22" s="99" t="s">
         <v>203</v>
       </c>
-      <c r="J22" s="124">
+      <c r="J22" s="100">
         <v>1</v>
       </c>
       <c r="K22" s="32">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="84">
+      <c r="L22" s="32"/>
+    </row>
+    <row r="23" spans="2:12" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="77">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="97" t="s">
+      <c r="C23" s="90" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="E23" s="97" t="s">
+      <c r="E23" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F23" s="98" t="s">
+      <c r="F23" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="G23" s="97" t="s">
+      <c r="G23" s="90" t="s">
         <v>157</v>
       </c>
       <c r="H23" s="53" t="s">
         <v>222</v>
       </c>
-      <c r="I23" s="101" t="s">
+      <c r="I23" s="94" t="s">
         <v>203</v>
       </c>
-      <c r="J23" s="86">
+      <c r="J23" s="79">
         <v>1</v>
       </c>
       <c r="K23" s="29">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="84">
+      <c r="L23" s="29"/>
+    </row>
+    <row r="24" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="77">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="99" t="s">
+      <c r="C24" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="100" t="s">
+      <c r="D24" s="93" t="s">
         <v>256</v>
       </c>
-      <c r="E24" s="99" t="s">
+      <c r="E24" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="F24" s="100" t="s">
+      <c r="F24" s="93" t="s">
         <v>258</v>
       </c>
-      <c r="G24" s="106" t="s">
+      <c r="G24" s="99" t="s">
         <v>260</v>
       </c>
       <c r="H24" s="54" t="s">
         <v>261</v>
       </c>
-      <c r="I24" s="106" t="s">
+      <c r="I24" s="99" t="s">
         <v>203</v>
       </c>
-      <c r="J24" s="124">
+      <c r="J24" s="100">
         <v>1</v>
       </c>
       <c r="K24" s="32">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="84">
+      <c r="L24" s="32"/>
+    </row>
+    <row r="25" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="77">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="97" t="s">
+      <c r="C25" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="98" t="s">
+      <c r="D25" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="97" t="s">
+      <c r="E25" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F25" s="98" t="s">
+      <c r="F25" s="91" t="s">
         <v>104</v>
       </c>
-      <c r="G25" s="97" t="s">
+      <c r="G25" s="90" t="s">
         <v>154</v>
       </c>
       <c r="H25" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="I25" s="101" t="s">
+      <c r="I25" s="94" t="s">
         <v>203</v>
       </c>
-      <c r="J25" s="86">
+      <c r="J25" s="79">
         <v>1</v>
       </c>
       <c r="K25" s="29">
         <v>6</v>
       </c>
-    </row>
-    <row r="26" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="84">
+      <c r="L25" s="29"/>
+    </row>
+    <row r="26" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="77">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="99" t="s">
+      <c r="C26" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="100" t="s">
+      <c r="D26" s="93" t="s">
         <v>257</v>
       </c>
-      <c r="E26" s="99" t="s">
+      <c r="E26" s="92" t="s">
         <v>105</v>
       </c>
-      <c r="F26" s="100" t="s">
+      <c r="F26" s="93" t="s">
         <v>259</v>
       </c>
-      <c r="G26" s="106" t="s">
+      <c r="G26" s="99" t="s">
         <v>260</v>
       </c>
       <c r="H26" s="54" t="s">
         <v>262</v>
       </c>
-      <c r="I26" s="106" t="s">
+      <c r="I26" s="99" t="s">
         <v>203</v>
       </c>
-      <c r="J26" s="124">
+      <c r="J26" s="100">
         <v>1</v>
       </c>
       <c r="K26" s="32">
         <v>20</v>
       </c>
-    </row>
-    <row r="27" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="84">
+      <c r="L26" s="32"/>
+    </row>
+    <row r="27" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="77">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="97" t="s">
+      <c r="C27" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="98" t="s">
+      <c r="D27" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="E27" s="97" t="s">
+      <c r="E27" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F27" s="98" t="s">
+      <c r="F27" s="91" t="s">
         <v>106</v>
       </c>
-      <c r="G27" s="97" t="s">
+      <c r="G27" s="90" t="s">
         <v>153</v>
       </c>
       <c r="H27" s="55" t="s">
         <v>255</v>
       </c>
-      <c r="I27" s="97" t="s">
+      <c r="I27" s="90" t="s">
         <v>186</v>
       </c>
-      <c r="J27" s="86">
+      <c r="J27" s="79">
         <v>1</v>
       </c>
       <c r="K27" s="29">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="84">
+      <c r="L27" s="29"/>
+    </row>
+    <row r="28" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="77">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="99" t="s">
+      <c r="C28" s="92" t="s">
         <v>26</v>
       </c>
       <c r="D28" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="E28" s="99" t="s">
+      <c r="E28" s="92" t="s">
         <v>107</v>
       </c>
-      <c r="F28" s="100" t="s">
+      <c r="F28" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="G28" s="99" t="s">
+      <c r="G28" s="92" t="s">
         <v>158</v>
       </c>
       <c r="H28" s="54" t="s">
         <v>224</v>
       </c>
-      <c r="I28" s="99" t="s">
+      <c r="I28" s="92" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="124">
+      <c r="J28" s="100">
         <v>1</v>
       </c>
       <c r="K28" s="32">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="84">
+      <c r="L28" s="32"/>
+    </row>
+    <row r="29" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="77">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="97" t="s">
+      <c r="C29" s="90" t="s">
         <v>27</v>
       </c>
       <c r="D29" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="97" t="s">
+      <c r="E29" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F29" s="98" t="s">
+      <c r="F29" s="91" t="s">
         <v>108</v>
       </c>
-      <c r="G29" s="97" t="s">
+      <c r="G29" s="90" t="s">
         <v>159</v>
       </c>
       <c r="H29" s="53" t="s">
         <v>225</v>
       </c>
-      <c r="I29" s="97" t="s">
+      <c r="I29" s="90" t="s">
         <v>188</v>
       </c>
-      <c r="J29" s="86">
+      <c r="J29" s="79">
         <v>1</v>
       </c>
       <c r="K29" s="29">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="84">
+      <c r="L29" s="29"/>
+    </row>
+    <row r="30" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="77">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="99" t="s">
+      <c r="C30" s="92" t="s">
         <v>28</v>
       </c>
       <c r="D30" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="E30" s="99" t="s">
+      <c r="E30" s="92" t="s">
         <v>109</v>
       </c>
-      <c r="F30" s="100" t="s">
+      <c r="F30" s="93" t="s">
         <v>136</v>
       </c>
-      <c r="G30" s="99" t="s">
+      <c r="G30" s="92" t="s">
         <v>150</v>
       </c>
       <c r="H30" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="I30" s="99" t="s">
+      <c r="I30" s="92" t="s">
         <v>189</v>
       </c>
-      <c r="J30" s="124">
+      <c r="J30" s="100">
         <v>1</v>
       </c>
       <c r="K30" s="32">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="84">
+      <c r="L30" s="32"/>
+    </row>
+    <row r="31" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="77">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="97" t="s">
+      <c r="C31" s="90" t="s">
         <v>29</v>
       </c>
       <c r="D31" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="E31" s="97" t="s">
+      <c r="E31" s="90" t="s">
         <v>109</v>
       </c>
-      <c r="F31" s="98" t="s">
+      <c r="F31" s="91" t="s">
         <v>137</v>
       </c>
-      <c r="G31" s="97" t="s">
+      <c r="G31" s="90" t="s">
         <v>150</v>
       </c>
       <c r="H31" s="53" t="s">
         <v>228</v>
       </c>
-      <c r="I31" s="101" t="s">
+      <c r="I31" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J31" s="86">
+      <c r="J31" s="79">
         <v>1</v>
       </c>
       <c r="K31" s="29">
         <v>50</v>
       </c>
-    </row>
-    <row r="32" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="84">
+      <c r="L31" s="29"/>
+    </row>
+    <row r="32" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="77">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="99" t="s">
+      <c r="C32" s="92" t="s">
         <v>30</v>
       </c>
       <c r="D32" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="E32" s="99" t="s">
+      <c r="E32" s="92" t="s">
         <v>202</v>
       </c>
-      <c r="F32" s="100" t="s">
+      <c r="F32" s="93" t="s">
         <v>110</v>
       </c>
-      <c r="G32" s="99" t="s">
+      <c r="G32" s="92" t="s">
         <v>160</v>
       </c>
       <c r="H32" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="I32" s="99" t="s">
+      <c r="I32" s="92" t="s">
         <v>190</v>
       </c>
-      <c r="J32" s="124">
+      <c r="J32" s="100">
         <v>1</v>
       </c>
       <c r="K32" s="32">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="84">
+      <c r="L32" s="32"/>
+    </row>
+    <row r="33" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="77">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="97" t="s">
+      <c r="C33" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="98" t="s">
+      <c r="D33" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="E33" s="97" t="s">
+      <c r="E33" s="90" t="s">
         <v>111</v>
       </c>
       <c r="F33" s="44" t="s">
         <v>229</v>
       </c>
-      <c r="G33" s="97" t="s">
+      <c r="G33" s="90" t="s">
         <v>161</v>
       </c>
       <c r="H33" s="53" t="s">
         <v>230</v>
       </c>
-      <c r="I33" s="101" t="s">
+      <c r="I33" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J33" s="86">
+      <c r="J33" s="79">
         <v>2</v>
       </c>
       <c r="K33" s="29">
         <v>50</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="84">
+      <c r="L33" s="29"/>
+    </row>
+    <row r="34" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="77">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="99" t="s">
+      <c r="C34" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="100" t="s">
+      <c r="D34" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="E34" s="99" t="s">
+      <c r="E34" s="92" t="s">
         <v>111</v>
       </c>
       <c r="F34" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="G34" s="99" t="s">
+      <c r="G34" s="92" t="s">
         <v>161</v>
       </c>
       <c r="H34" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="I34" s="106" t="s">
+      <c r="I34" s="99" t="s">
         <v>204</v>
       </c>
-      <c r="J34" s="124">
+      <c r="J34" s="100">
         <v>1</v>
       </c>
       <c r="K34" s="32">
         <v>10</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="84">
+      <c r="L34" s="32"/>
+    </row>
+    <row r="35" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="77">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="97" t="s">
+      <c r="C35" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="102" t="s">
+      <c r="D35" s="95" t="s">
         <v>264</v>
       </c>
-      <c r="E35" s="97" t="s">
+      <c r="E35" s="90" t="s">
         <v>265</v>
       </c>
-      <c r="F35" s="98" t="s">
+      <c r="F35" s="91" t="s">
         <v>266</v>
       </c>
-      <c r="G35" s="97" t="s">
+      <c r="G35" s="90" t="s">
         <v>267</v>
       </c>
       <c r="H35" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="I35" s="97" t="s">
+      <c r="I35" s="90" t="s">
         <v>191</v>
       </c>
-      <c r="J35" s="86">
+      <c r="J35" s="79">
         <v>1</v>
       </c>
       <c r="K35" s="29">
         <v>50</v>
       </c>
-    </row>
-    <row r="36" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="84">
+      <c r="L35" s="29"/>
+    </row>
+    <row r="36" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="77">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="99" t="s">
+      <c r="C36" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="103" t="s">
+      <c r="D36" s="96" t="s">
         <v>253</v>
       </c>
-      <c r="E36" s="99" t="s">
+      <c r="E36" s="92" t="s">
         <v>113</v>
       </c>
-      <c r="F36" s="103" t="s">
+      <c r="F36" s="96" t="s">
         <v>252</v>
       </c>
-      <c r="G36" s="104" t="s">
+      <c r="G36" s="97" t="s">
         <v>152</v>
       </c>
       <c r="H36" s="54" t="s">
         <v>251</v>
       </c>
-      <c r="I36" s="99" t="s">
+      <c r="I36" s="92" t="s">
         <v>192</v>
       </c>
-      <c r="J36" s="124">
+      <c r="J36" s="100">
         <v>4</v>
       </c>
       <c r="K36" s="32">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="84">
+      <c r="L36" s="32"/>
+    </row>
+    <row r="37" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="77">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C37" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="98" t="s">
+      <c r="D37" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="E37" s="97" t="s">
+      <c r="E37" s="90" t="s">
         <v>113</v>
       </c>
-      <c r="F37" s="98" t="s">
+      <c r="F37" s="91" t="s">
         <v>138</v>
       </c>
-      <c r="G37" s="97" t="s">
+      <c r="G37" s="90" t="s">
         <v>152</v>
       </c>
       <c r="H37" s="53" t="s">
         <v>233</v>
       </c>
-      <c r="I37" s="97" t="s">
+      <c r="I37" s="90" t="s">
         <v>193</v>
       </c>
-      <c r="J37" s="86">
+      <c r="J37" s="79">
         <v>10</v>
       </c>
       <c r="K37" s="29">
         <v>100</v>
       </c>
-    </row>
-    <row r="38" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="84">
+      <c r="L37" s="29"/>
+    </row>
+    <row r="38" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="77">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="99" t="s">
+      <c r="C38" s="92" t="s">
         <v>279</v>
       </c>
-      <c r="D38" s="100" t="s">
+      <c r="D38" s="93" t="s">
         <v>78</v>
       </c>
-      <c r="E38" s="99" t="s">
+      <c r="E38" s="92" t="s">
         <v>113</v>
       </c>
       <c r="F38" s="45" t="s">
         <v>236</v>
       </c>
-      <c r="G38" s="99" t="s">
+      <c r="G38" s="92" t="s">
         <v>163</v>
       </c>
       <c r="H38" s="54" t="s">
         <v>237</v>
       </c>
-      <c r="I38" s="99" t="s">
+      <c r="I38" s="92" t="s">
         <v>195</v>
       </c>
-      <c r="J38" s="124">
+      <c r="J38" s="100">
         <v>8</v>
       </c>
       <c r="K38" s="32">
         <v>100</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="84">
+      <c r="L38" s="32"/>
+    </row>
+    <row r="39" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="77">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="97" t="s">
+      <c r="C39" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="98" t="s">
+      <c r="D39" s="91" t="s">
         <v>79</v>
       </c>
-      <c r="E39" s="97" t="s">
+      <c r="E39" s="90" t="s">
         <v>113</v>
       </c>
       <c r="F39" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="G39" s="97" t="s">
+      <c r="G39" s="90" t="s">
         <v>163</v>
       </c>
       <c r="H39" s="53" t="s">
         <v>239</v>
       </c>
-      <c r="I39" s="97" t="s">
+      <c r="I39" s="90" t="s">
         <v>196</v>
       </c>
-      <c r="J39" s="86">
+      <c r="J39" s="79">
         <v>2</v>
       </c>
       <c r="K39" s="29">
         <v>100</v>
       </c>
-    </row>
-    <row r="40" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="84">
+      <c r="L39" s="29"/>
+    </row>
+    <row r="40" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="77">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="99" t="s">
+      <c r="C40" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="100" t="s">
+      <c r="D40" s="93" t="s">
         <v>80</v>
       </c>
-      <c r="E40" s="99" t="s">
+      <c r="E40" s="92" t="s">
         <v>112</v>
       </c>
       <c r="F40" s="45" t="s">
         <v>240</v>
       </c>
-      <c r="G40" s="99" t="s">
+      <c r="G40" s="92" t="s">
         <v>164</v>
       </c>
       <c r="H40" s="54" t="s">
         <v>241</v>
       </c>
-      <c r="I40" s="99" t="s">
+      <c r="I40" s="92" t="s">
         <v>197</v>
       </c>
-      <c r="J40" s="124">
+      <c r="J40" s="100">
         <v>2</v>
       </c>
       <c r="K40" s="32">
         <v>100</v>
       </c>
-    </row>
-    <row r="41" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="84">
+      <c r="L40" s="32"/>
+    </row>
+    <row r="41" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="77">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="97" t="s">
+      <c r="C41" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="D41" s="98" t="s">
+      <c r="D41" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="E41" s="97" t="s">
+      <c r="E41" s="90" t="s">
         <v>113</v>
       </c>
-      <c r="F41" s="98" t="s">
+      <c r="F41" s="91" t="s">
         <v>140</v>
       </c>
-      <c r="G41" s="97" t="s">
+      <c r="G41" s="90" t="s">
         <v>152</v>
       </c>
       <c r="H41" s="53" t="s">
         <v>235</v>
       </c>
-      <c r="I41" s="97" t="s">
+      <c r="I41" s="90" t="s">
         <v>198</v>
       </c>
-      <c r="J41" s="86">
+      <c r="J41" s="79">
         <v>1</v>
       </c>
       <c r="K41" s="29">
         <v>50</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="84">
+      <c r="L41" s="29"/>
+    </row>
+    <row r="42" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="77">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="99" t="s">
+      <c r="C42" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D42" s="100" t="s">
+      <c r="D42" s="123" t="s">
         <v>82</v>
       </c>
-      <c r="E42" s="99" t="s">
+      <c r="E42" s="122" t="s">
         <v>114</v>
       </c>
-      <c r="F42" s="126" t="s">
+      <c r="F42" s="124" t="s">
         <v>204</v>
       </c>
-      <c r="G42" s="106" t="s">
+      <c r="G42" s="125" t="s">
         <v>204</v>
       </c>
-      <c r="H42" s="57" t="s">
+      <c r="H42" s="126" t="s">
         <v>254</v>
       </c>
-      <c r="I42" s="106" t="s">
+      <c r="I42" s="125" t="s">
         <v>204</v>
       </c>
-      <c r="J42" s="124">
+      <c r="J42" s="122">
         <v>3</v>
       </c>
       <c r="K42" s="127" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="84">
+      <c r="L42" s="128" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="77">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="97" t="s">
+      <c r="C43" s="90" t="s">
         <v>280</v>
       </c>
       <c r="D43" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="E43" s="97" t="s">
+      <c r="E43" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F43" s="98" t="s">
+      <c r="F43" s="91" t="s">
         <v>115</v>
       </c>
-      <c r="G43" s="97" t="s">
+      <c r="G43" s="90" t="s">
         <v>165</v>
       </c>
       <c r="H43" s="53" t="s">
         <v>242</v>
       </c>
-      <c r="I43" s="101" t="s">
+      <c r="I43" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J43" s="86">
+      <c r="J43" s="79">
         <v>2</v>
       </c>
       <c r="K43" s="29">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="84">
+      <c r="L43" s="29"/>
+    </row>
+    <row r="44" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="77">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="99" t="s">
+      <c r="C44" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="D44" s="100" t="s">
+      <c r="D44" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="99" t="s">
+      <c r="E44" s="92" t="s">
         <v>116</v>
       </c>
-      <c r="F44" s="100" t="s">
+      <c r="F44" s="93" t="s">
         <v>141</v>
       </c>
-      <c r="G44" s="99" t="s">
+      <c r="G44" s="92" t="s">
         <v>166</v>
       </c>
       <c r="H44" s="57" t="s">
         <v>254</v>
       </c>
-      <c r="I44" s="106" t="s">
+      <c r="I44" s="99" t="s">
         <v>204</v>
       </c>
-      <c r="J44" s="124">
+      <c r="J44" s="100">
         <v>1</v>
       </c>
       <c r="K44" s="32">
         <v>6</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="84">
+      <c r="L44" s="32"/>
+    </row>
+    <row r="45" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="77">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="97" t="s">
+      <c r="C45" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="D45" s="98" t="s">
+      <c r="D45" s="91" t="s">
         <v>85</v>
       </c>
-      <c r="E45" s="97" t="s">
+      <c r="E45" s="90" t="s">
         <v>117</v>
       </c>
-      <c r="F45" s="98" t="s">
+      <c r="F45" s="91" t="s">
         <v>142</v>
       </c>
-      <c r="G45" s="97" t="s">
+      <c r="G45" s="90" t="s">
         <v>167</v>
       </c>
       <c r="H45" s="53" t="s">
         <v>243</v>
       </c>
-      <c r="I45" s="101" t="s">
+      <c r="I45" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J45" s="86">
+      <c r="J45" s="79">
         <v>1</v>
       </c>
       <c r="K45" s="29">
         <v>6</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="84">
+      <c r="L45" s="29"/>
+    </row>
+    <row r="46" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="77">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="99" t="s">
+      <c r="C46" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="D46" s="100" t="s">
+      <c r="D46" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="E46" s="99" t="s">
+      <c r="E46" s="92" t="s">
         <v>118</v>
       </c>
-      <c r="F46" s="100" t="s">
+      <c r="F46" s="93" t="s">
         <v>143</v>
       </c>
-      <c r="G46" s="99" t="s">
+      <c r="G46" s="92" t="s">
         <v>168</v>
       </c>
       <c r="H46" s="57" t="s">
         <v>254</v>
       </c>
-      <c r="I46" s="106" t="s">
+      <c r="I46" s="99" t="s">
         <v>204</v>
       </c>
-      <c r="J46" s="124">
+      <c r="J46" s="100">
         <v>1</v>
       </c>
       <c r="K46" s="32">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="84">
+      <c r="L46" s="32"/>
+    </row>
+    <row r="47" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="77">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="97" t="s">
+      <c r="C47" s="90" t="s">
         <v>46</v>
       </c>
       <c r="D47" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="E47" s="97" t="s">
+      <c r="E47" s="90" t="s">
         <v>119</v>
       </c>
-      <c r="F47" s="98" t="s">
+      <c r="F47" s="91" t="s">
         <v>144</v>
       </c>
-      <c r="G47" s="97" t="s">
+      <c r="G47" s="90" t="s">
         <v>169</v>
       </c>
       <c r="H47" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="I47" s="101" t="s">
+      <c r="I47" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J47" s="86">
+      <c r="J47" s="79">
         <v>1</v>
       </c>
       <c r="K47" s="29">
         <v>6</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="84">
+      <c r="L47" s="29"/>
+    </row>
+    <row r="48" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="77">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="99" t="s">
+      <c r="C48" s="92" t="s">
         <v>47</v>
       </c>
       <c r="D48" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="E48" s="99" t="s">
+      <c r="E48" s="92" t="s">
         <v>120</v>
       </c>
-      <c r="F48" s="100" t="s">
+      <c r="F48" s="93" t="s">
         <v>145</v>
       </c>
-      <c r="G48" s="99" t="s">
+      <c r="G48" s="92" t="s">
         <v>170</v>
       </c>
       <c r="H48" s="57" t="s">
         <v>203</v>
       </c>
-      <c r="I48" s="106" t="s">
+      <c r="I48" s="99" t="s">
         <v>204</v>
       </c>
-      <c r="J48" s="124">
+      <c r="J48" s="100">
         <v>1</v>
       </c>
       <c r="K48" s="32">
         <v>6</v>
       </c>
-    </row>
-    <row r="49" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="84">
+      <c r="L48" s="32"/>
+    </row>
+    <row r="49" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="77">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="97" t="s">
+      <c r="C49" s="90" t="s">
         <v>48</v>
       </c>
       <c r="D49" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="E49" s="97" t="s">
+      <c r="E49" s="90" t="s">
         <v>121</v>
       </c>
-      <c r="F49" s="98" t="s">
+      <c r="F49" s="91" t="s">
         <v>146</v>
       </c>
-      <c r="G49" s="97" t="s">
+      <c r="G49" s="90" t="s">
         <v>171</v>
       </c>
       <c r="H49" s="53" t="s">
         <v>245</v>
       </c>
-      <c r="I49" s="101" t="s">
+      <c r="I49" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J49" s="86">
+      <c r="J49" s="79">
         <v>1</v>
       </c>
       <c r="K49" s="29">
         <v>6</v>
       </c>
-    </row>
-    <row r="50" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="84">
+      <c r="L49" s="29"/>
+    </row>
+    <row r="50" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="77">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="99" t="s">
+      <c r="C50" s="92" t="s">
         <v>49</v>
       </c>
       <c r="D50" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="E50" s="99" t="s">
+      <c r="E50" s="92" t="s">
         <v>122</v>
       </c>
-      <c r="F50" s="100" t="s">
+      <c r="F50" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="G50" s="99" t="s">
+      <c r="G50" s="92" t="s">
         <v>172</v>
       </c>
       <c r="H50" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="I50" s="106" t="s">
+      <c r="I50" s="99" t="s">
         <v>204</v>
       </c>
-      <c r="J50" s="124">
+      <c r="J50" s="100">
         <v>1</v>
       </c>
       <c r="K50" s="32">
         <v>6</v>
       </c>
-    </row>
-    <row r="51" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="84">
+      <c r="L50" s="32"/>
+    </row>
+    <row r="51" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="77">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="97" t="s">
+      <c r="C51" s="90" t="s">
         <v>50</v>
       </c>
       <c r="D51" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="E51" s="97" t="s">
+      <c r="E51" s="90" t="s">
         <v>123</v>
       </c>
-      <c r="F51" s="98" t="s">
+      <c r="F51" s="91" t="s">
         <v>148</v>
       </c>
-      <c r="G51" s="97" t="s">
+      <c r="G51" s="90" t="s">
         <v>173</v>
       </c>
       <c r="H51" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="I51" s="101" t="s">
+      <c r="I51" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J51" s="86">
+      <c r="J51" s="79">
         <v>1</v>
       </c>
       <c r="K51" s="29">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="84">
+      <c r="L51" s="29"/>
+    </row>
+    <row r="52" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="77">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="99" t="s">
+      <c r="C52" s="92" t="s">
         <v>51</v>
       </c>
       <c r="D52" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="E52" s="99" t="s">
+      <c r="E52" s="92" t="s">
         <v>202</v>
       </c>
-      <c r="F52" s="100" t="s">
+      <c r="F52" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="G52" s="99" t="s">
+      <c r="G52" s="92" t="s">
         <v>174</v>
       </c>
       <c r="H52" s="54" t="s">
         <v>248</v>
       </c>
-      <c r="I52" s="99" t="s">
+      <c r="I52" s="92" t="s">
         <v>199</v>
       </c>
-      <c r="J52" s="124">
+      <c r="J52" s="100">
         <v>2</v>
       </c>
       <c r="K52" s="32">
         <v>11</v>
       </c>
-    </row>
-    <row r="53" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="84">
+      <c r="L52" s="32"/>
+    </row>
+    <row r="53" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="77">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="97" t="s">
+      <c r="C53" s="90" t="s">
         <v>52</v>
       </c>
       <c r="D53" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="E53" s="97" t="s">
+      <c r="E53" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F53" s="98" t="s">
+      <c r="F53" s="91" t="s">
         <v>125</v>
       </c>
-      <c r="G53" s="97" t="s">
+      <c r="G53" s="90" t="s">
         <v>174</v>
       </c>
       <c r="H53" s="53" t="s">
         <v>249</v>
       </c>
-      <c r="I53" s="97" t="s">
+      <c r="I53" s="90" t="s">
         <v>200</v>
       </c>
-      <c r="J53" s="86">
+      <c r="J53" s="79">
         <v>1</v>
       </c>
       <c r="K53" s="29">
         <v>10</v>
       </c>
-    </row>
-    <row r="54" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="84">
+      <c r="L53" s="29"/>
+    </row>
+    <row r="54" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="134">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="128" t="s">
+      <c r="C54" s="135" t="s">
         <v>53</v>
       </c>
-      <c r="D54" s="129" t="s">
+      <c r="D54" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="E54" s="128" t="s">
+      <c r="E54" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="F54" s="130" t="s">
+      <c r="F54" s="103" t="s">
         <v>126</v>
       </c>
-      <c r="G54" s="128" t="s">
+      <c r="G54" s="135" t="s">
         <v>175</v>
       </c>
-      <c r="H54" s="129" t="s">
+      <c r="H54" s="102" t="s">
         <v>250</v>
       </c>
-      <c r="I54" s="128" t="s">
+      <c r="I54" s="135" t="s">
         <v>201</v>
       </c>
-      <c r="J54" s="131">
-        <v>1</v>
-      </c>
-      <c r="K54" s="132">
+      <c r="J54" s="136">
+        <v>1</v>
+      </c>
+      <c r="K54" s="104">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B55" s="88"/>
-      <c r="C55" s="89" t="s">
+      <c r="L54" s="104"/>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B55" s="81"/>
+      <c r="C55" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="D55" s="90"/>
+      <c r="D55" s="83"/>
       <c r="E55" s="42"/>
-      <c r="F55" s="120"/>
-      <c r="G55" s="120"/>
-      <c r="H55" s="120"/>
-      <c r="I55" s="120"/>
-      <c r="J55" s="120"/>
-      <c r="K55" s="121"/>
-    </row>
-    <row r="56" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="91"/>
-      <c r="C56" s="92" t="s">
+      <c r="F55" s="118"/>
+      <c r="G55" s="118"/>
+      <c r="H55" s="118"/>
+      <c r="I55" s="118"/>
+      <c r="J55" s="118"/>
+      <c r="K55" s="118"/>
+      <c r="L55" s="119"/>
+    </row>
+    <row r="56" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="84"/>
+      <c r="C56" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="D56" s="93"/>
-      <c r="E56" s="93"/>
-      <c r="F56" s="122"/>
-      <c r="G56" s="122"/>
-      <c r="H56" s="122"/>
-      <c r="I56" s="122"/>
-      <c r="J56" s="122"/>
-      <c r="K56" s="123"/>
+      <c r="D56" s="86"/>
+      <c r="E56" s="86"/>
+      <c r="F56" s="120"/>
+      <c r="G56" s="120"/>
+      <c r="H56" s="120"/>
+      <c r="I56" s="120"/>
+      <c r="J56" s="120"/>
+      <c r="K56" s="120"/>
+      <c r="L56" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="K3:K8"/>
-    <mergeCell ref="F55:K56"/>
+    <mergeCell ref="L3:L8"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="F55:L56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4F51F9-7803-4E96-A4CA-C01A43F4E153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0DF7D1-C0B1-4293-934D-6B0E7CC96557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="294">
   <si>
     <t>Component list</t>
   </si>
@@ -886,6 +886,33 @@
   </si>
   <si>
     <t>DO NOT MOUNT</t>
+  </si>
+  <si>
+    <t>Item Type</t>
+  </si>
+  <si>
+    <t>Capacitor</t>
+  </si>
+  <si>
+    <t>Connector</t>
+  </si>
+  <si>
+    <t>Inductor</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>Resistor</t>
+  </si>
+  <si>
+    <t>Switch</t>
+  </si>
+  <si>
+    <t>ICs</t>
+  </si>
+  <si>
+    <t>Crystal</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1460,11 +1487,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1750,61 +1790,6 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1838,6 +1823,117 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1916,7 +2012,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>10417</xdr:rowOff>
@@ -2249,8 +2345,8 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="114"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="129"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2265,9 +2361,9 @@
       <c r="F2" s="10"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-      <c r="K2" s="112"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
+      <c r="K2" s="127"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2283,8 +2379,8 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="109"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="124"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2300,8 +2396,8 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="109"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="124"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2317,8 +2413,8 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="109"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="124"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2330,8 +2426,8 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="109"/>
+      <c r="J6" s="125"/>
+      <c r="K6" s="124"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2343,8 +2439,8 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="109"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="124"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2356,8 +2452,8 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="109"/>
+      <c r="J8" s="125"/>
+      <c r="K8" s="124"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -3933,9 +4029,9 @@
       <c r="F55" s="59"/>
       <c r="G55" s="59"/>
       <c r="H55" s="59"/>
-      <c r="I55" s="105"/>
-      <c r="J55" s="105"/>
-      <c r="K55" s="106"/>
+      <c r="I55" s="120"/>
+      <c r="J55" s="120"/>
+      <c r="K55" s="121"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
@@ -3948,9 +4044,9 @@
       <c r="F56" s="37"/>
       <c r="G56" s="37"/>
       <c r="H56" s="37"/>
-      <c r="I56" s="107"/>
-      <c r="J56" s="107"/>
-      <c r="K56" s="108"/>
+      <c r="I56" s="122"/>
+      <c r="J56" s="122"/>
+      <c r="K56" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3968,1733 +4064,1818 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348A8FCB-7220-490A-87EB-3CE6A0C47FB5}">
-  <dimension ref="B1:L56"/>
+  <dimension ref="B1:M56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.140625" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" customWidth="1"/>
-    <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="26.28515625" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H1" s="98"/>
-    </row>
-    <row r="2" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1" s="98"/>
+    </row>
+    <row r="2" spans="2:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="70"/>
-      <c r="C2" s="71" t="s">
+      <c r="C2" s="137"/>
+      <c r="D2" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="71"/>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="71"/>
+      <c r="F2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="3"/>
+      <c r="G2" s="10"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="116"/>
-    </row>
-    <row r="3" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J2" s="3"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="132"/>
+    </row>
+    <row r="3" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" s="19"/>
-      <c r="C3" s="129" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="129"/>
-      <c r="E3" s="25" t="s">
+      <c r="C3" s="138"/>
+      <c r="D3" s="112" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="112"/>
+      <c r="F3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="129"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="117"/>
-    </row>
-    <row r="4" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="112"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="K3" s="113"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="130"/>
+    </row>
+    <row r="4" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="19"/>
-      <c r="C4" s="129" t="s">
+      <c r="C4" s="138"/>
+      <c r="D4" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="129"/>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="112"/>
+      <c r="F4" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="72"/>
-      <c r="G4" s="73"/>
+      <c r="G4" s="72"/>
       <c r="H4" s="73"/>
       <c r="I4" s="73"/>
       <c r="J4" s="73"/>
       <c r="K4" s="73"/>
-      <c r="L4" s="109"/>
-    </row>
-    <row r="5" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="L4" s="73"/>
+      <c r="M4" s="124"/>
+    </row>
+    <row r="5" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="19"/>
-      <c r="C5" s="129" t="s">
+      <c r="C5" s="138"/>
+      <c r="D5" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="129"/>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="112"/>
+      <c r="F5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="74"/>
-      <c r="G5" s="75"/>
+      <c r="G5" s="74"/>
       <c r="H5" s="75"/>
       <c r="I5" s="75"/>
       <c r="J5" s="75"/>
       <c r="K5" s="75"/>
-      <c r="L5" s="109"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L5" s="75"/>
+      <c r="M5" s="124"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="20"/>
-      <c r="C6" s="76"/>
+      <c r="C6" s="139"/>
       <c r="D6" s="76"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="75"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="74"/>
       <c r="H6" s="75"/>
       <c r="I6" s="75"/>
       <c r="J6" s="75"/>
       <c r="K6" s="75"/>
-      <c r="L6" s="109"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L6" s="75"/>
+      <c r="M6" s="124"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="21"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="132"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="109"/>
-    </row>
-    <row r="8" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="140"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="114"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="115"/>
+      <c r="J7" s="115"/>
+      <c r="K7" s="115"/>
+      <c r="L7" s="115"/>
+      <c r="M7" s="124"/>
+    </row>
+    <row r="8" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="33"/>
-      <c r="C8" s="133"/>
-      <c r="D8" s="133"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="131"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="132"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="132"/>
-      <c r="K8" s="132"/>
-      <c r="L8" s="109"/>
-    </row>
-    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="141"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="114"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="115"/>
+      <c r="J8" s="115"/>
+      <c r="K8" s="115"/>
+      <c r="L8" s="115"/>
+      <c r="M8" s="124"/>
+    </row>
+    <row r="9" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="D9" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="E9" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="F9" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="G9" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="G9" s="30" t="s">
+      <c r="H9" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="I9" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="I9" s="30" t="s">
+      <c r="J9" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="J9" s="62" t="s">
+      <c r="K9" s="62" t="s">
         <v>282</v>
       </c>
-      <c r="K9" s="30" t="s">
+      <c r="L9" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="L9" s="30" t="s">
+      <c r="M9" s="30" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="10" spans="2:12" s="87" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13" s="87" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="77">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="146" t="s">
+        <v>286</v>
+      </c>
+      <c r="D10" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="E10" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="88" t="s">
+      <c r="F10" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="89" t="s">
+      <c r="G10" s="89" t="s">
         <v>128</v>
       </c>
-      <c r="G10" s="88" t="s">
+      <c r="H10" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="H10" s="52" t="s">
+      <c r="I10" s="52" t="s">
         <v>206</v>
       </c>
-      <c r="I10" s="88" t="s">
+      <c r="J10" s="88" t="s">
         <v>177</v>
       </c>
-      <c r="J10" s="78">
+      <c r="K10" s="78">
         <v>3</v>
       </c>
-      <c r="K10" s="36">
+      <c r="L10" s="36">
         <v>20</v>
       </c>
-      <c r="L10" s="36"/>
-    </row>
-    <row r="11" spans="2:12" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M10" s="36"/>
+    </row>
+    <row r="11" spans="2:13" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="77">
         <f t="shared" ref="B11:B54" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="147"/>
+      <c r="D11" s="44" t="s">
         <v>271</v>
       </c>
-      <c r="D11" s="91" t="s">
+      <c r="E11" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="90" t="s">
+      <c r="F11" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="44" t="s">
+      <c r="G11" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="G11" s="90" t="s">
+      <c r="H11" s="90" t="s">
         <v>150</v>
       </c>
-      <c r="H11" s="53" t="s">
+      <c r="I11" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="I11" s="90" t="s">
+      <c r="J11" s="90" t="s">
         <v>178</v>
       </c>
-      <c r="J11" s="79">
+      <c r="K11" s="79">
         <v>24</v>
       </c>
-      <c r="K11" s="29">
+      <c r="L11" s="29">
         <v>150</v>
       </c>
-      <c r="L11" s="29"/>
-    </row>
-    <row r="12" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="29"/>
+    </row>
+    <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="77">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="92" t="s">
+      <c r="C12" s="147"/>
+      <c r="D12" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="93" t="s">
+      <c r="E12" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="92" t="s">
+      <c r="F12" s="92" t="s">
         <v>98</v>
       </c>
-      <c r="F12" s="93" t="s">
+      <c r="G12" s="93" t="s">
         <v>129</v>
       </c>
-      <c r="G12" s="92" t="s">
+      <c r="H12" s="92" t="s">
         <v>151</v>
       </c>
-      <c r="H12" s="54" t="s">
+      <c r="I12" s="54" t="s">
         <v>210</v>
       </c>
-      <c r="I12" s="92" t="s">
+      <c r="J12" s="92" t="s">
         <v>179</v>
       </c>
-      <c r="J12" s="80">
-        <v>1</v>
-      </c>
-      <c r="K12" s="28">
+      <c r="K12" s="80">
+        <v>1</v>
+      </c>
+      <c r="L12" s="28">
         <v>20</v>
       </c>
-      <c r="L12" s="28"/>
-    </row>
-    <row r="13" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="28"/>
+    </row>
+    <row r="13" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="77">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="90" t="s">
+      <c r="C13" s="147"/>
+      <c r="D13" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="91" t="s">
+      <c r="E13" s="91" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="90" t="s">
+      <c r="F13" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="91" t="s">
+      <c r="G13" s="91" t="s">
         <v>130</v>
       </c>
-      <c r="G13" s="90" t="s">
+      <c r="H13" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="H13" s="53" t="s">
+      <c r="I13" s="53" t="s">
         <v>212</v>
       </c>
-      <c r="I13" s="90" t="s">
+      <c r="J13" s="90" t="s">
         <v>180</v>
       </c>
-      <c r="J13" s="79">
+      <c r="K13" s="79">
         <v>8</v>
       </c>
-      <c r="K13" s="29">
+      <c r="L13" s="29">
         <v>100</v>
       </c>
-      <c r="L13" s="29"/>
-    </row>
-    <row r="14" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="29"/>
+    </row>
+    <row r="14" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="77">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="92" t="s">
+      <c r="C14" s="147"/>
+      <c r="D14" s="92" t="s">
         <v>272</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="E14" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="92" t="s">
+      <c r="F14" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="93" t="s">
+      <c r="G14" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="G14" s="92" t="s">
+      <c r="H14" s="92" t="s">
         <v>153</v>
       </c>
-      <c r="H14" s="54" t="s">
+      <c r="I14" s="54" t="s">
         <v>211</v>
       </c>
-      <c r="I14" s="92" t="s">
+      <c r="J14" s="92" t="s">
         <v>181</v>
       </c>
-      <c r="J14" s="80">
+      <c r="K14" s="80">
         <v>2</v>
       </c>
-      <c r="K14" s="28">
+      <c r="L14" s="28">
         <v>50</v>
       </c>
-      <c r="L14" s="28"/>
-    </row>
-    <row r="15" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M14" s="28"/>
+    </row>
+    <row r="15" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="77">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="90" t="s">
+      <c r="C15" s="147"/>
+      <c r="D15" s="90" t="s">
         <v>273</v>
       </c>
-      <c r="D15" s="91" t="s">
+      <c r="E15" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="90" t="s">
+      <c r="F15" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="91" t="s">
+      <c r="G15" s="91" t="s">
         <v>132</v>
       </c>
-      <c r="G15" s="90" t="s">
+      <c r="H15" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="H15" s="53" t="s">
+      <c r="I15" s="53" t="s">
         <v>213</v>
       </c>
-      <c r="I15" s="90" t="s">
+      <c r="J15" s="90" t="s">
         <v>182</v>
       </c>
-      <c r="J15" s="79">
+      <c r="K15" s="79">
         <v>7</v>
       </c>
-      <c r="K15" s="29">
+      <c r="L15" s="29">
         <v>50</v>
       </c>
-      <c r="L15" s="29"/>
-    </row>
-    <row r="16" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M15" s="29"/>
+    </row>
+    <row r="16" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="77">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="92" t="s">
+      <c r="C16" s="147"/>
+      <c r="D16" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="93" t="s">
+      <c r="E16" s="93" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="92" t="s">
+      <c r="F16" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="93" t="s">
+      <c r="G16" s="93" t="s">
         <v>133</v>
       </c>
-      <c r="G16" s="92" t="s">
+      <c r="H16" s="92" t="s">
         <v>150</v>
       </c>
-      <c r="H16" s="54" t="s">
+      <c r="I16" s="54" t="s">
         <v>214</v>
       </c>
-      <c r="I16" s="92" t="s">
+      <c r="J16" s="92" t="s">
         <v>183</v>
       </c>
-      <c r="J16" s="80">
-        <v>1</v>
-      </c>
-      <c r="K16" s="32">
+      <c r="K16" s="80">
+        <v>1</v>
+      </c>
+      <c r="L16" s="32">
         <v>10</v>
       </c>
-      <c r="L16" s="32"/>
-    </row>
-    <row r="17" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="32"/>
+    </row>
+    <row r="17" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="77">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="90" t="s">
+      <c r="C17" s="147"/>
+      <c r="D17" s="90" t="s">
         <v>274</v>
       </c>
-      <c r="D17" s="91" t="s">
+      <c r="E17" s="91" t="s">
         <v>275</v>
       </c>
-      <c r="E17" s="90" t="s">
+      <c r="F17" s="90" t="s">
         <v>276</v>
       </c>
-      <c r="F17" s="91" t="s">
+      <c r="G17" s="91" t="s">
         <v>277</v>
       </c>
-      <c r="G17" s="90" t="s">
+      <c r="H17" s="90" t="s">
         <v>150</v>
       </c>
-      <c r="H17" s="101" t="s">
+      <c r="I17" s="101" t="s">
         <v>281</v>
       </c>
-      <c r="I17" s="90" t="s">
+      <c r="J17" s="90" t="s">
         <v>278</v>
       </c>
-      <c r="J17" s="79">
-        <v>1</v>
-      </c>
-      <c r="K17" s="29">
+      <c r="K17" s="79">
+        <v>1</v>
+      </c>
+      <c r="L17" s="29">
         <v>50</v>
       </c>
-      <c r="L17" s="29"/>
-    </row>
-    <row r="18" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M17" s="29"/>
+    </row>
+    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="77">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="92" t="s">
+      <c r="C18" s="147"/>
+      <c r="D18" s="92" t="s">
         <v>269</v>
       </c>
-      <c r="D18" s="93" t="s">
+      <c r="E18" s="93" t="s">
         <v>216</v>
       </c>
-      <c r="E18" s="92" t="s">
+      <c r="F18" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="F18" s="93" t="s">
+      <c r="G18" s="93" t="s">
         <v>217</v>
       </c>
-      <c r="G18" s="92" t="s">
+      <c r="H18" s="92" t="s">
         <v>152</v>
       </c>
-      <c r="H18" s="54" t="s">
+      <c r="I18" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="I18" s="92" t="s">
+      <c r="J18" s="92" t="s">
         <v>184</v>
       </c>
-      <c r="J18" s="100">
-        <v>1</v>
-      </c>
-      <c r="K18" s="32">
+      <c r="K18" s="100">
+        <v>1</v>
+      </c>
+      <c r="L18" s="32">
         <v>100</v>
       </c>
-      <c r="L18" s="32"/>
-    </row>
-    <row r="19" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M18" s="32"/>
+    </row>
+    <row r="19" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="77">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="90" t="s">
+      <c r="C19" s="148"/>
+      <c r="D19" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="91" t="s">
+      <c r="E19" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="90" t="s">
+      <c r="F19" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="F19" s="91" t="s">
+      <c r="G19" s="91" t="s">
         <v>134</v>
       </c>
-      <c r="G19" s="90" t="s">
+      <c r="H19" s="90" t="s">
         <v>150</v>
       </c>
-      <c r="H19" s="53" t="s">
+      <c r="I19" s="53" t="s">
         <v>218</v>
       </c>
-      <c r="I19" s="90" t="s">
+      <c r="J19" s="90" t="s">
         <v>185</v>
       </c>
-      <c r="J19" s="79">
-        <v>1</v>
-      </c>
-      <c r="K19" s="29">
+      <c r="K19" s="79">
+        <v>1</v>
+      </c>
+      <c r="L19" s="29">
         <v>20</v>
       </c>
-      <c r="L19" s="29"/>
-    </row>
-    <row r="20" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M19" s="29"/>
+    </row>
+    <row r="20" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="77">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="92" t="s">
+      <c r="C20" s="146" t="s">
+        <v>287</v>
+      </c>
+      <c r="D20" s="92" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="93" t="s">
+      <c r="E20" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="92" t="s">
+      <c r="F20" s="92" t="s">
         <v>202</v>
       </c>
-      <c r="F20" s="93" t="s">
+      <c r="G20" s="93" t="s">
         <v>99</v>
       </c>
-      <c r="G20" s="92" t="s">
+      <c r="H20" s="92" t="s">
         <v>154</v>
       </c>
-      <c r="H20" s="54" t="s">
+      <c r="I20" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="I20" s="99" t="s">
+      <c r="J20" s="99" t="s">
         <v>203</v>
       </c>
-      <c r="J20" s="100">
-        <v>1</v>
-      </c>
-      <c r="K20" s="32">
+      <c r="K20" s="100">
+        <v>1</v>
+      </c>
+      <c r="L20" s="32">
         <v>10</v>
       </c>
-      <c r="L20" s="32"/>
-    </row>
-    <row r="21" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M20" s="32"/>
+    </row>
+    <row r="21" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="77">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="90" t="s">
+      <c r="C21" s="147"/>
+      <c r="D21" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="91" t="s">
+      <c r="E21" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="90" t="s">
+      <c r="F21" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F21" s="91" t="s">
+      <c r="G21" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="G21" s="90" t="s">
+      <c r="H21" s="90" t="s">
         <v>155</v>
       </c>
-      <c r="H21" s="53" t="s">
+      <c r="I21" s="53" t="s">
         <v>220</v>
       </c>
-      <c r="I21" s="94" t="s">
+      <c r="J21" s="94" t="s">
         <v>203</v>
       </c>
-      <c r="J21" s="79">
-        <v>1</v>
-      </c>
-      <c r="K21" s="29">
+      <c r="K21" s="79">
+        <v>1</v>
+      </c>
+      <c r="L21" s="29">
         <v>6</v>
       </c>
-      <c r="L21" s="29"/>
-    </row>
-    <row r="22" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M21" s="29"/>
+    </row>
+    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="77">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="92" t="s">
+      <c r="C22" s="147"/>
+      <c r="D22" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="93" t="s">
+      <c r="E22" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="92" t="s">
+      <c r="F22" s="105" t="s">
         <v>202</v>
       </c>
-      <c r="F22" s="93" t="s">
+      <c r="G22" s="106" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="92" t="s">
+      <c r="H22" s="105" t="s">
         <v>156</v>
       </c>
-      <c r="H22" s="54" t="s">
+      <c r="I22" s="152" t="s">
         <v>221</v>
       </c>
-      <c r="I22" s="99" t="s">
+      <c r="J22" s="108" t="s">
         <v>203</v>
       </c>
-      <c r="J22" s="100">
-        <v>1</v>
-      </c>
-      <c r="K22" s="32">
+      <c r="K22" s="105">
+        <v>1</v>
+      </c>
+      <c r="L22" s="153">
         <v>20</v>
       </c>
-      <c r="L22" s="32"/>
-    </row>
-    <row r="23" spans="2:12" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M22" s="154" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="77">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="90" t="s">
+      <c r="C23" s="147"/>
+      <c r="D23" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="53" t="s">
+      <c r="E23" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="E23" s="90" t="s">
+      <c r="F23" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F23" s="91" t="s">
+      <c r="G23" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="G23" s="90" t="s">
+      <c r="H23" s="90" t="s">
         <v>157</v>
       </c>
-      <c r="H23" s="53" t="s">
+      <c r="I23" s="53" t="s">
         <v>222</v>
       </c>
-      <c r="I23" s="94" t="s">
+      <c r="J23" s="94" t="s">
         <v>203</v>
       </c>
-      <c r="J23" s="79">
-        <v>1</v>
-      </c>
-      <c r="K23" s="29">
+      <c r="K23" s="79">
+        <v>1</v>
+      </c>
+      <c r="L23" s="29">
         <v>6</v>
       </c>
-      <c r="L23" s="29"/>
-    </row>
-    <row r="24" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M23" s="29"/>
+    </row>
+    <row r="24" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="77">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="92" t="s">
+      <c r="C24" s="147"/>
+      <c r="D24" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="93" t="s">
+      <c r="E24" s="93" t="s">
         <v>256</v>
       </c>
-      <c r="E24" s="92" t="s">
+      <c r="F24" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="F24" s="93" t="s">
+      <c r="G24" s="93" t="s">
         <v>258</v>
       </c>
-      <c r="G24" s="99" t="s">
+      <c r="H24" s="99" t="s">
         <v>260</v>
       </c>
-      <c r="H24" s="54" t="s">
+      <c r="I24" s="54" t="s">
         <v>261</v>
       </c>
-      <c r="I24" s="99" t="s">
+      <c r="J24" s="99" t="s">
         <v>203</v>
       </c>
-      <c r="J24" s="100">
-        <v>1</v>
-      </c>
-      <c r="K24" s="32">
+      <c r="K24" s="100">
+        <v>1</v>
+      </c>
+      <c r="L24" s="32">
         <v>10</v>
       </c>
-      <c r="L24" s="32"/>
-    </row>
-    <row r="25" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M24" s="32"/>
+    </row>
+    <row r="25" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="77">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="90" t="s">
+      <c r="C25" s="147"/>
+      <c r="D25" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="91" t="s">
+      <c r="E25" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="90" t="s">
+      <c r="F25" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F25" s="91" t="s">
+      <c r="G25" s="91" t="s">
         <v>104</v>
       </c>
-      <c r="G25" s="90" t="s">
+      <c r="H25" s="90" t="s">
         <v>154</v>
       </c>
-      <c r="H25" s="53" t="s">
+      <c r="I25" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="I25" s="94" t="s">
+      <c r="J25" s="94" t="s">
         <v>203</v>
       </c>
-      <c r="J25" s="79">
-        <v>1</v>
-      </c>
-      <c r="K25" s="29">
+      <c r="K25" s="79">
+        <v>1</v>
+      </c>
+      <c r="L25" s="29">
         <v>6</v>
       </c>
-      <c r="L25" s="29"/>
-    </row>
-    <row r="26" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M25" s="29"/>
+    </row>
+    <row r="26" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="77">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="92" t="s">
+      <c r="C26" s="148"/>
+      <c r="D26" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="93" t="s">
+      <c r="E26" s="93" t="s">
         <v>257</v>
       </c>
-      <c r="E26" s="92" t="s">
+      <c r="F26" s="92" t="s">
         <v>105</v>
       </c>
-      <c r="F26" s="93" t="s">
+      <c r="G26" s="93" t="s">
         <v>259</v>
       </c>
-      <c r="G26" s="99" t="s">
+      <c r="H26" s="99" t="s">
         <v>260</v>
       </c>
-      <c r="H26" s="54" t="s">
+      <c r="I26" s="54" t="s">
         <v>262</v>
       </c>
-      <c r="I26" s="99" t="s">
+      <c r="J26" s="99" t="s">
         <v>203</v>
       </c>
-      <c r="J26" s="100">
-        <v>1</v>
-      </c>
-      <c r="K26" s="32">
+      <c r="K26" s="100">
+        <v>1</v>
+      </c>
+      <c r="L26" s="32">
         <v>20</v>
       </c>
-      <c r="L26" s="32"/>
-    </row>
-    <row r="27" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M26" s="32"/>
+    </row>
+    <row r="27" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="77">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="90" t="s">
+      <c r="C27" s="146" t="s">
+        <v>288</v>
+      </c>
+      <c r="D27" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="91" t="s">
+      <c r="E27" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="E27" s="90" t="s">
+      <c r="F27" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F27" s="91" t="s">
+      <c r="G27" s="91" t="s">
         <v>106</v>
       </c>
-      <c r="G27" s="90" t="s">
+      <c r="H27" s="90" t="s">
         <v>153</v>
       </c>
-      <c r="H27" s="55" t="s">
+      <c r="I27" s="55" t="s">
         <v>255</v>
       </c>
-      <c r="I27" s="90" t="s">
+      <c r="J27" s="90" t="s">
         <v>186</v>
       </c>
-      <c r="J27" s="79">
-        <v>1</v>
-      </c>
-      <c r="K27" s="29">
+      <c r="K27" s="79">
+        <v>1</v>
+      </c>
+      <c r="L27" s="29">
         <v>7</v>
       </c>
-      <c r="L27" s="29"/>
-    </row>
-    <row r="28" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M27" s="29"/>
+    </row>
+    <row r="28" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="77">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="92" t="s">
+      <c r="C28" s="147"/>
+      <c r="D28" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="54" t="s">
+      <c r="E28" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="E28" s="92" t="s">
+      <c r="F28" s="92" t="s">
         <v>107</v>
       </c>
-      <c r="F28" s="93" t="s">
+      <c r="G28" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="G28" s="92" t="s">
+      <c r="H28" s="92" t="s">
         <v>158</v>
       </c>
-      <c r="H28" s="54" t="s">
+      <c r="I28" s="54" t="s">
         <v>224</v>
       </c>
-      <c r="I28" s="92" t="s">
+      <c r="J28" s="92" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="100">
-        <v>1</v>
-      </c>
-      <c r="K28" s="32">
+      <c r="K28" s="100">
+        <v>1</v>
+      </c>
+      <c r="L28" s="32">
         <v>10</v>
       </c>
-      <c r="L28" s="32"/>
-    </row>
-    <row r="29" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M28" s="32"/>
+    </row>
+    <row r="29" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="77">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="90" t="s">
+      <c r="C29" s="147"/>
+      <c r="D29" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="53" t="s">
+      <c r="E29" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="90" t="s">
+      <c r="F29" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F29" s="91" t="s">
+      <c r="G29" s="91" t="s">
         <v>108</v>
       </c>
-      <c r="G29" s="90" t="s">
+      <c r="H29" s="90" t="s">
         <v>159</v>
       </c>
-      <c r="H29" s="53" t="s">
+      <c r="I29" s="53" t="s">
         <v>225</v>
       </c>
-      <c r="I29" s="90" t="s">
+      <c r="J29" s="90" t="s">
         <v>188</v>
       </c>
-      <c r="J29" s="79">
-        <v>1</v>
-      </c>
-      <c r="K29" s="29">
+      <c r="K29" s="79">
+        <v>1</v>
+      </c>
+      <c r="L29" s="29">
         <v>10</v>
       </c>
-      <c r="L29" s="29"/>
-    </row>
-    <row r="30" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M29" s="29"/>
+    </row>
+    <row r="30" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="77">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="92" t="s">
+      <c r="C30" s="147"/>
+      <c r="D30" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="54" t="s">
+      <c r="E30" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="E30" s="92" t="s">
+      <c r="F30" s="92" t="s">
         <v>109</v>
       </c>
-      <c r="F30" s="93" t="s">
+      <c r="G30" s="93" t="s">
         <v>136</v>
       </c>
-      <c r="G30" s="92" t="s">
+      <c r="H30" s="92" t="s">
         <v>150</v>
       </c>
-      <c r="H30" s="54" t="s">
+      <c r="I30" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="I30" s="92" t="s">
+      <c r="J30" s="92" t="s">
         <v>189</v>
       </c>
-      <c r="J30" s="100">
-        <v>1</v>
-      </c>
-      <c r="K30" s="32">
+      <c r="K30" s="100">
+        <v>1</v>
+      </c>
+      <c r="L30" s="32">
         <v>10</v>
       </c>
-      <c r="L30" s="32"/>
-    </row>
-    <row r="31" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M30" s="32"/>
+    </row>
+    <row r="31" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="77">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="90" t="s">
+      <c r="C31" s="147"/>
+      <c r="D31" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="53" t="s">
+      <c r="E31" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="E31" s="90" t="s">
+      <c r="F31" s="90" t="s">
         <v>109</v>
       </c>
-      <c r="F31" s="91" t="s">
+      <c r="G31" s="91" t="s">
         <v>137</v>
       </c>
-      <c r="G31" s="90" t="s">
+      <c r="H31" s="90" t="s">
         <v>150</v>
       </c>
-      <c r="H31" s="53" t="s">
+      <c r="I31" s="53" t="s">
         <v>228</v>
       </c>
-      <c r="I31" s="94" t="s">
+      <c r="J31" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J31" s="79">
-        <v>1</v>
-      </c>
-      <c r="K31" s="29">
+      <c r="K31" s="79">
+        <v>1</v>
+      </c>
+      <c r="L31" s="29">
         <v>50</v>
       </c>
-      <c r="L31" s="29"/>
-    </row>
-    <row r="32" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M31" s="29"/>
+    </row>
+    <row r="32" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="77">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="92" t="s">
+      <c r="C32" s="148"/>
+      <c r="D32" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="54" t="s">
+      <c r="E32" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="E32" s="92" t="s">
+      <c r="F32" s="92" t="s">
         <v>202</v>
       </c>
-      <c r="F32" s="93" t="s">
+      <c r="G32" s="93" t="s">
         <v>110</v>
       </c>
-      <c r="G32" s="92" t="s">
+      <c r="H32" s="92" t="s">
         <v>160</v>
       </c>
-      <c r="H32" s="54" t="s">
+      <c r="I32" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="I32" s="92" t="s">
+      <c r="J32" s="92" t="s">
         <v>190</v>
       </c>
-      <c r="J32" s="100">
-        <v>1</v>
-      </c>
-      <c r="K32" s="32">
+      <c r="K32" s="100">
+        <v>1</v>
+      </c>
+      <c r="L32" s="32">
         <v>10</v>
       </c>
-      <c r="L32" s="32"/>
-    </row>
-    <row r="33" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M32" s="32"/>
+    </row>
+    <row r="33" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="77">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="90" t="s">
+      <c r="C33" s="146" t="s">
+        <v>289</v>
+      </c>
+      <c r="D33" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="91" t="s">
+      <c r="E33" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="E33" s="90" t="s">
+      <c r="F33" s="90" t="s">
         <v>111</v>
       </c>
-      <c r="F33" s="44" t="s">
+      <c r="G33" s="44" t="s">
         <v>229</v>
       </c>
-      <c r="G33" s="90" t="s">
+      <c r="H33" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="H33" s="53" t="s">
+      <c r="I33" s="53" t="s">
         <v>230</v>
       </c>
-      <c r="I33" s="94" t="s">
+      <c r="J33" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J33" s="79">
+      <c r="K33" s="79">
         <v>2</v>
       </c>
-      <c r="K33" s="29">
+      <c r="L33" s="29">
         <v>50</v>
       </c>
-      <c r="L33" s="29"/>
-    </row>
-    <row r="34" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M33" s="29"/>
+    </row>
+    <row r="34" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="77">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="92" t="s">
+      <c r="C34" s="148"/>
+      <c r="D34" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="93" t="s">
+      <c r="E34" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="E34" s="92" t="s">
+      <c r="F34" s="92" t="s">
         <v>111</v>
       </c>
-      <c r="F34" s="45" t="s">
+      <c r="G34" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="G34" s="92" t="s">
+      <c r="H34" s="92" t="s">
         <v>161</v>
       </c>
-      <c r="H34" s="54" t="s">
+      <c r="I34" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="I34" s="99" t="s">
+      <c r="J34" s="99" t="s">
         <v>204</v>
       </c>
-      <c r="J34" s="100">
-        <v>1</v>
-      </c>
-      <c r="K34" s="32">
+      <c r="K34" s="100">
+        <v>1</v>
+      </c>
+      <c r="L34" s="32">
         <v>10</v>
       </c>
-      <c r="L34" s="32"/>
-    </row>
-    <row r="35" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M34" s="32"/>
+    </row>
+    <row r="35" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="77">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="90" t="s">
+      <c r="C35" s="146" t="s">
+        <v>290</v>
+      </c>
+      <c r="D35" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="95" t="s">
+      <c r="E35" s="95" t="s">
         <v>264</v>
       </c>
-      <c r="E35" s="90" t="s">
+      <c r="F35" s="90" t="s">
         <v>265</v>
       </c>
-      <c r="F35" s="91" t="s">
+      <c r="G35" s="91" t="s">
         <v>266</v>
       </c>
-      <c r="G35" s="90" t="s">
+      <c r="H35" s="90" t="s">
         <v>267</v>
       </c>
-      <c r="H35" s="53" t="s">
+      <c r="I35" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="I35" s="90" t="s">
+      <c r="J35" s="90" t="s">
         <v>191</v>
       </c>
-      <c r="J35" s="79">
-        <v>1</v>
-      </c>
-      <c r="K35" s="29">
+      <c r="K35" s="79">
+        <v>1</v>
+      </c>
+      <c r="L35" s="29">
         <v>50</v>
       </c>
-      <c r="L35" s="29"/>
-    </row>
-    <row r="36" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M35" s="29"/>
+    </row>
+    <row r="36" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="77">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="92" t="s">
+      <c r="C36" s="147"/>
+      <c r="D36" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="96" t="s">
+      <c r="E36" s="96" t="s">
         <v>253</v>
       </c>
-      <c r="E36" s="92" t="s">
+      <c r="F36" s="92" t="s">
         <v>113</v>
       </c>
-      <c r="F36" s="96" t="s">
+      <c r="G36" s="96" t="s">
         <v>252</v>
       </c>
-      <c r="G36" s="97" t="s">
+      <c r="H36" s="97" t="s">
         <v>152</v>
       </c>
-      <c r="H36" s="54" t="s">
+      <c r="I36" s="54" t="s">
         <v>251</v>
       </c>
-      <c r="I36" s="92" t="s">
+      <c r="J36" s="92" t="s">
         <v>192</v>
       </c>
-      <c r="J36" s="100">
+      <c r="K36" s="100">
         <v>4</v>
       </c>
-      <c r="K36" s="32">
+      <c r="L36" s="32">
         <v>100</v>
       </c>
-      <c r="L36" s="32"/>
-    </row>
-    <row r="37" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M36" s="32"/>
+    </row>
+    <row r="37" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="77">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="44" t="s">
+      <c r="C37" s="147"/>
+      <c r="D37" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="91" t="s">
+      <c r="E37" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="E37" s="90" t="s">
+      <c r="F37" s="90" t="s">
         <v>113</v>
       </c>
-      <c r="F37" s="91" t="s">
+      <c r="G37" s="91" t="s">
         <v>138</v>
       </c>
-      <c r="G37" s="90" t="s">
+      <c r="H37" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="H37" s="53" t="s">
+      <c r="I37" s="53" t="s">
         <v>233</v>
       </c>
-      <c r="I37" s="90" t="s">
+      <c r="J37" s="90" t="s">
         <v>193</v>
       </c>
-      <c r="J37" s="79">
+      <c r="K37" s="79">
         <v>10</v>
       </c>
-      <c r="K37" s="29">
+      <c r="L37" s="29">
         <v>100</v>
       </c>
-      <c r="L37" s="29"/>
-    </row>
-    <row r="38" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M37" s="29"/>
+    </row>
+    <row r="38" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="77">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="92" t="s">
+      <c r="C38" s="147"/>
+      <c r="D38" s="92" t="s">
         <v>279</v>
       </c>
-      <c r="D38" s="93" t="s">
+      <c r="E38" s="93" t="s">
         <v>78</v>
       </c>
-      <c r="E38" s="92" t="s">
+      <c r="F38" s="92" t="s">
         <v>113</v>
       </c>
-      <c r="F38" s="45" t="s">
+      <c r="G38" s="45" t="s">
         <v>236</v>
       </c>
-      <c r="G38" s="92" t="s">
+      <c r="H38" s="92" t="s">
         <v>163</v>
       </c>
-      <c r="H38" s="54" t="s">
+      <c r="I38" s="54" t="s">
         <v>237</v>
       </c>
-      <c r="I38" s="92" t="s">
+      <c r="J38" s="92" t="s">
         <v>195</v>
       </c>
-      <c r="J38" s="100">
+      <c r="K38" s="100">
         <v>8</v>
       </c>
-      <c r="K38" s="32">
+      <c r="L38" s="32">
         <v>100</v>
       </c>
-      <c r="L38" s="32"/>
-    </row>
-    <row r="39" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M38" s="32"/>
+    </row>
+    <row r="39" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="77">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="90" t="s">
+      <c r="C39" s="147"/>
+      <c r="D39" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="91" t="s">
+      <c r="E39" s="91" t="s">
         <v>79</v>
       </c>
-      <c r="E39" s="90" t="s">
+      <c r="F39" s="90" t="s">
         <v>113</v>
       </c>
-      <c r="F39" s="44" t="s">
+      <c r="G39" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="G39" s="90" t="s">
+      <c r="H39" s="90" t="s">
         <v>163</v>
       </c>
-      <c r="H39" s="53" t="s">
+      <c r="I39" s="53" t="s">
         <v>239</v>
       </c>
-      <c r="I39" s="90" t="s">
+      <c r="J39" s="90" t="s">
         <v>196</v>
       </c>
-      <c r="J39" s="79">
+      <c r="K39" s="79">
         <v>2</v>
       </c>
-      <c r="K39" s="29">
+      <c r="L39" s="29">
         <v>100</v>
       </c>
-      <c r="L39" s="29"/>
-    </row>
-    <row r="40" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M39" s="29"/>
+    </row>
+    <row r="40" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="77">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="92" t="s">
+      <c r="C40" s="147"/>
+      <c r="D40" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="93" t="s">
+      <c r="E40" s="93" t="s">
         <v>80</v>
       </c>
-      <c r="E40" s="92" t="s">
+      <c r="F40" s="92" t="s">
         <v>112</v>
       </c>
-      <c r="F40" s="45" t="s">
+      <c r="G40" s="45" t="s">
         <v>240</v>
       </c>
-      <c r="G40" s="92" t="s">
+      <c r="H40" s="92" t="s">
         <v>164</v>
       </c>
-      <c r="H40" s="54" t="s">
+      <c r="I40" s="54" t="s">
         <v>241</v>
       </c>
-      <c r="I40" s="92" t="s">
+      <c r="J40" s="92" t="s">
         <v>197</v>
       </c>
-      <c r="J40" s="100">
+      <c r="K40" s="100">
         <v>2</v>
       </c>
-      <c r="K40" s="32">
+      <c r="L40" s="32">
         <v>100</v>
       </c>
-      <c r="L40" s="32"/>
-    </row>
-    <row r="41" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M40" s="32"/>
+    </row>
+    <row r="41" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="77">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="90" t="s">
+      <c r="C41" s="148"/>
+      <c r="D41" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="D41" s="91" t="s">
+      <c r="E41" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="E41" s="90" t="s">
+      <c r="F41" s="90" t="s">
         <v>113</v>
       </c>
-      <c r="F41" s="91" t="s">
+      <c r="G41" s="91" t="s">
         <v>140</v>
       </c>
-      <c r="G41" s="90" t="s">
+      <c r="H41" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="H41" s="53" t="s">
+      <c r="I41" s="53" t="s">
         <v>235</v>
       </c>
-      <c r="I41" s="90" t="s">
+      <c r="J41" s="90" t="s">
         <v>198</v>
       </c>
-      <c r="J41" s="79">
-        <v>1</v>
-      </c>
-      <c r="K41" s="29">
+      <c r="K41" s="79">
+        <v>1</v>
+      </c>
+      <c r="L41" s="29">
         <v>50</v>
       </c>
-      <c r="L41" s="29"/>
-    </row>
-    <row r="42" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M41" s="29"/>
+    </row>
+    <row r="42" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="77">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="122" t="s">
+      <c r="C42" s="150" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D42" s="123" t="s">
+      <c r="E42" s="106" t="s">
         <v>82</v>
       </c>
-      <c r="E42" s="122" t="s">
+      <c r="F42" s="105" t="s">
         <v>114</v>
       </c>
-      <c r="F42" s="124" t="s">
+      <c r="G42" s="107" t="s">
         <v>204</v>
       </c>
-      <c r="G42" s="125" t="s">
+      <c r="H42" s="108" t="s">
         <v>204</v>
       </c>
-      <c r="H42" s="126" t="s">
+      <c r="I42" s="109" t="s">
         <v>254</v>
       </c>
-      <c r="I42" s="125" t="s">
+      <c r="J42" s="108" t="s">
         <v>204</v>
       </c>
-      <c r="J42" s="122">
+      <c r="K42" s="105">
         <v>3</v>
       </c>
-      <c r="K42" s="127" t="s">
+      <c r="L42" s="110" t="s">
         <v>203</v>
       </c>
-      <c r="L42" s="128" t="s">
+      <c r="M42" s="111" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="43" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="77">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="90" t="s">
+      <c r="C43" s="151" t="s">
+        <v>291</v>
+      </c>
+      <c r="D43" s="90" t="s">
         <v>280</v>
       </c>
-      <c r="D43" s="53" t="s">
+      <c r="E43" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="E43" s="90" t="s">
+      <c r="F43" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F43" s="91" t="s">
+      <c r="G43" s="91" t="s">
         <v>115</v>
       </c>
-      <c r="G43" s="90" t="s">
+      <c r="H43" s="90" t="s">
         <v>165</v>
       </c>
-      <c r="H43" s="53" t="s">
+      <c r="I43" s="53" t="s">
         <v>242</v>
       </c>
-      <c r="I43" s="94" t="s">
+      <c r="J43" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J43" s="79">
+      <c r="K43" s="79">
         <v>2</v>
       </c>
-      <c r="K43" s="29">
+      <c r="L43" s="29">
         <v>10</v>
       </c>
-      <c r="L43" s="29"/>
-    </row>
-    <row r="44" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M43" s="29"/>
+    </row>
+    <row r="44" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="77">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="92" t="s">
+      <c r="C44" s="146" t="s">
+        <v>292</v>
+      </c>
+      <c r="D44" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="D44" s="93" t="s">
+      <c r="E44" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="92" t="s">
+      <c r="F44" s="92" t="s">
         <v>116</v>
       </c>
-      <c r="F44" s="93" t="s">
+      <c r="G44" s="93" t="s">
         <v>141</v>
       </c>
-      <c r="G44" s="92" t="s">
+      <c r="H44" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="H44" s="57" t="s">
+      <c r="I44" s="57" t="s">
         <v>254</v>
       </c>
-      <c r="I44" s="99" t="s">
+      <c r="J44" s="99" t="s">
         <v>204</v>
       </c>
-      <c r="J44" s="100">
-        <v>1</v>
-      </c>
-      <c r="K44" s="32">
+      <c r="K44" s="100">
+        <v>1</v>
+      </c>
+      <c r="L44" s="32">
         <v>6</v>
       </c>
-      <c r="L44" s="32"/>
-    </row>
-    <row r="45" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M44" s="32"/>
+    </row>
+    <row r="45" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="77">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="90" t="s">
+      <c r="C45" s="147"/>
+      <c r="D45" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="D45" s="91" t="s">
+      <c r="E45" s="91" t="s">
         <v>85</v>
       </c>
-      <c r="E45" s="90" t="s">
+      <c r="F45" s="90" t="s">
         <v>117</v>
       </c>
-      <c r="F45" s="91" t="s">
+      <c r="G45" s="91" t="s">
         <v>142</v>
       </c>
-      <c r="G45" s="90" t="s">
+      <c r="H45" s="90" t="s">
         <v>167</v>
       </c>
-      <c r="H45" s="53" t="s">
+      <c r="I45" s="53" t="s">
         <v>243</v>
       </c>
-      <c r="I45" s="94" t="s">
+      <c r="J45" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J45" s="79">
-        <v>1</v>
-      </c>
-      <c r="K45" s="29">
+      <c r="K45" s="79">
+        <v>1</v>
+      </c>
+      <c r="L45" s="29">
         <v>6</v>
       </c>
-      <c r="L45" s="29"/>
-    </row>
-    <row r="46" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M45" s="29"/>
+    </row>
+    <row r="46" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="77">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="92" t="s">
+      <c r="C46" s="147"/>
+      <c r="D46" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="D46" s="93" t="s">
+      <c r="E46" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="E46" s="92" t="s">
+      <c r="F46" s="92" t="s">
         <v>118</v>
       </c>
-      <c r="F46" s="93" t="s">
+      <c r="G46" s="93" t="s">
         <v>143</v>
       </c>
-      <c r="G46" s="92" t="s">
+      <c r="H46" s="92" t="s">
         <v>168</v>
       </c>
-      <c r="H46" s="57" t="s">
+      <c r="I46" s="57" t="s">
         <v>254</v>
       </c>
-      <c r="I46" s="99" t="s">
+      <c r="J46" s="99" t="s">
         <v>204</v>
       </c>
-      <c r="J46" s="100">
-        <v>1</v>
-      </c>
-      <c r="K46" s="32">
+      <c r="K46" s="100">
+        <v>1</v>
+      </c>
+      <c r="L46" s="32">
         <v>6</v>
       </c>
-      <c r="L46" s="32"/>
-    </row>
-    <row r="47" spans="2:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M46" s="32"/>
+    </row>
+    <row r="47" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="77">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="90" t="s">
+      <c r="C47" s="147"/>
+      <c r="D47" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="D47" s="53" t="s">
+      <c r="E47" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="E47" s="90" t="s">
+      <c r="F47" s="90" t="s">
         <v>119</v>
       </c>
-      <c r="F47" s="91" t="s">
+      <c r="G47" s="91" t="s">
         <v>144</v>
       </c>
-      <c r="G47" s="90" t="s">
+      <c r="H47" s="90" t="s">
         <v>169</v>
       </c>
-      <c r="H47" s="53" t="s">
+      <c r="I47" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="I47" s="94" t="s">
+      <c r="J47" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J47" s="79">
-        <v>1</v>
-      </c>
-      <c r="K47" s="29">
+      <c r="K47" s="79">
+        <v>1</v>
+      </c>
+      <c r="L47" s="29">
         <v>6</v>
       </c>
-      <c r="L47" s="29"/>
-    </row>
-    <row r="48" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M47" s="29"/>
+    </row>
+    <row r="48" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="77">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="92" t="s">
+      <c r="C48" s="147"/>
+      <c r="D48" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="D48" s="54" t="s">
+      <c r="E48" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="E48" s="92" t="s">
+      <c r="F48" s="92" t="s">
         <v>120</v>
       </c>
-      <c r="F48" s="93" t="s">
+      <c r="G48" s="93" t="s">
         <v>145</v>
       </c>
-      <c r="G48" s="92" t="s">
+      <c r="H48" s="92" t="s">
         <v>170</v>
       </c>
-      <c r="H48" s="57" t="s">
+      <c r="I48" s="57" t="s">
         <v>203</v>
       </c>
-      <c r="I48" s="99" t="s">
+      <c r="J48" s="99" t="s">
         <v>204</v>
       </c>
-      <c r="J48" s="100">
-        <v>1</v>
-      </c>
-      <c r="K48" s="32">
+      <c r="K48" s="100">
+        <v>1</v>
+      </c>
+      <c r="L48" s="32">
         <v>6</v>
       </c>
-      <c r="L48" s="32"/>
-    </row>
-    <row r="49" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M48" s="32"/>
+    </row>
+    <row r="49" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="77">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="90" t="s">
+      <c r="C49" s="147"/>
+      <c r="D49" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="D49" s="53" t="s">
+      <c r="E49" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="E49" s="90" t="s">
+      <c r="F49" s="90" t="s">
         <v>121</v>
       </c>
-      <c r="F49" s="91" t="s">
+      <c r="G49" s="91" t="s">
         <v>146</v>
       </c>
-      <c r="G49" s="90" t="s">
+      <c r="H49" s="90" t="s">
         <v>171</v>
       </c>
-      <c r="H49" s="53" t="s">
+      <c r="I49" s="53" t="s">
         <v>245</v>
       </c>
-      <c r="I49" s="94" t="s">
+      <c r="J49" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J49" s="79">
-        <v>1</v>
-      </c>
-      <c r="K49" s="29">
+      <c r="K49" s="79">
+        <v>1</v>
+      </c>
+      <c r="L49" s="29">
         <v>6</v>
       </c>
-      <c r="L49" s="29"/>
-    </row>
-    <row r="50" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M49" s="29"/>
+    </row>
+    <row r="50" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="77">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="92" t="s">
+      <c r="C50" s="147"/>
+      <c r="D50" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D50" s="54" t="s">
+      <c r="E50" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="E50" s="92" t="s">
+      <c r="F50" s="92" t="s">
         <v>122</v>
       </c>
-      <c r="F50" s="93" t="s">
+      <c r="G50" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="G50" s="92" t="s">
+      <c r="H50" s="92" t="s">
         <v>172</v>
       </c>
-      <c r="H50" s="54" t="s">
+      <c r="I50" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="I50" s="99" t="s">
+      <c r="J50" s="99" t="s">
         <v>204</v>
       </c>
-      <c r="J50" s="100">
-        <v>1</v>
-      </c>
-      <c r="K50" s="32">
+      <c r="K50" s="100">
+        <v>1</v>
+      </c>
+      <c r="L50" s="32">
         <v>6</v>
       </c>
-      <c r="L50" s="32"/>
-    </row>
-    <row r="51" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M50" s="32"/>
+    </row>
+    <row r="51" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="77">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="90" t="s">
+      <c r="C51" s="148"/>
+      <c r="D51" s="90" t="s">
         <v>50</v>
       </c>
-      <c r="D51" s="53" t="s">
+      <c r="E51" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="E51" s="90" t="s">
+      <c r="F51" s="90" t="s">
         <v>123</v>
       </c>
-      <c r="F51" s="91" t="s">
+      <c r="G51" s="91" t="s">
         <v>148</v>
       </c>
-      <c r="G51" s="90" t="s">
+      <c r="H51" s="90" t="s">
         <v>173</v>
       </c>
-      <c r="H51" s="53" t="s">
+      <c r="I51" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="I51" s="94" t="s">
+      <c r="J51" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="J51" s="79">
-        <v>1</v>
-      </c>
-      <c r="K51" s="29">
+      <c r="K51" s="79">
+        <v>1</v>
+      </c>
+      <c r="L51" s="29">
         <v>10</v>
       </c>
-      <c r="L51" s="29"/>
-    </row>
-    <row r="52" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M51" s="29"/>
+    </row>
+    <row r="52" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="77">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="92" t="s">
+      <c r="C52" s="145" t="s">
+        <v>293</v>
+      </c>
+      <c r="D52" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="D52" s="54" t="s">
+      <c r="E52" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="E52" s="92" t="s">
+      <c r="F52" s="92" t="s">
         <v>202</v>
       </c>
-      <c r="F52" s="93" t="s">
+      <c r="G52" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="G52" s="92" t="s">
+      <c r="H52" s="92" t="s">
         <v>174</v>
       </c>
-      <c r="H52" s="54" t="s">
+      <c r="I52" s="54" t="s">
         <v>248</v>
       </c>
-      <c r="I52" s="92" t="s">
+      <c r="J52" s="92" t="s">
         <v>199</v>
       </c>
-      <c r="J52" s="100">
+      <c r="K52" s="100">
         <v>2</v>
       </c>
-      <c r="K52" s="32">
+      <c r="L52" s="32">
         <v>11</v>
       </c>
-      <c r="L52" s="32"/>
-    </row>
-    <row r="53" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M52" s="32"/>
+    </row>
+    <row r="53" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="77">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="90" t="s">
+      <c r="C53" s="144"/>
+      <c r="D53" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="D53" s="53" t="s">
+      <c r="E53" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="E53" s="90" t="s">
+      <c r="F53" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F53" s="91" t="s">
+      <c r="G53" s="91" t="s">
         <v>125</v>
       </c>
-      <c r="G53" s="90" t="s">
+      <c r="H53" s="90" t="s">
         <v>174</v>
       </c>
-      <c r="H53" s="53" t="s">
+      <c r="I53" s="53" t="s">
         <v>249</v>
       </c>
-      <c r="I53" s="90" t="s">
+      <c r="J53" s="90" t="s">
         <v>200</v>
       </c>
-      <c r="J53" s="79">
-        <v>1</v>
-      </c>
-      <c r="K53" s="29">
+      <c r="K53" s="79">
+        <v>1</v>
+      </c>
+      <c r="L53" s="29">
         <v>10</v>
       </c>
-      <c r="L53" s="29"/>
-    </row>
-    <row r="54" spans="2:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="134">
+      <c r="M53" s="29"/>
+    </row>
+    <row r="54" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="117">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="135" t="s">
+      <c r="C54" s="149"/>
+      <c r="D54" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="D54" s="102" t="s">
+      <c r="E54" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="E54" s="135" t="s">
+      <c r="F54" s="118" t="s">
         <v>202</v>
       </c>
-      <c r="F54" s="103" t="s">
+      <c r="G54" s="103" t="s">
         <v>126</v>
       </c>
-      <c r="G54" s="135" t="s">
+      <c r="H54" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="H54" s="102" t="s">
+      <c r="I54" s="102" t="s">
         <v>250</v>
       </c>
-      <c r="I54" s="135" t="s">
+      <c r="J54" s="118" t="s">
         <v>201</v>
       </c>
-      <c r="J54" s="136">
-        <v>1</v>
-      </c>
-      <c r="K54" s="104">
+      <c r="K54" s="119">
+        <v>1</v>
+      </c>
+      <c r="L54" s="104">
         <v>10</v>
       </c>
-      <c r="L54" s="104"/>
-    </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M54" s="104"/>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B55" s="81"/>
-      <c r="C55" s="82" t="s">
+      <c r="C55" s="142"/>
+      <c r="D55" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="D55" s="83"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="118"/>
-      <c r="G55" s="118"/>
-      <c r="H55" s="118"/>
-      <c r="I55" s="118"/>
-      <c r="J55" s="118"/>
-      <c r="K55" s="118"/>
-      <c r="L55" s="119"/>
-    </row>
-    <row r="56" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E55" s="83"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="133"/>
+      <c r="H55" s="133"/>
+      <c r="I55" s="133"/>
+      <c r="J55" s="133"/>
+      <c r="K55" s="133"/>
+      <c r="L55" s="133"/>
+      <c r="M55" s="134"/>
+    </row>
+    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="84"/>
-      <c r="C56" s="85" t="s">
+      <c r="C56" s="143"/>
+      <c r="D56" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="D56" s="86"/>
       <c r="E56" s="86"/>
-      <c r="F56" s="120"/>
-      <c r="G56" s="120"/>
-      <c r="H56" s="120"/>
-      <c r="I56" s="120"/>
-      <c r="J56" s="120"/>
-      <c r="K56" s="120"/>
-      <c r="L56" s="121"/>
+      <c r="F56" s="86"/>
+      <c r="G56" s="135"/>
+      <c r="H56" s="135"/>
+      <c r="I56" s="135"/>
+      <c r="J56" s="135"/>
+      <c r="K56" s="135"/>
+      <c r="L56" s="135"/>
+      <c r="M56" s="136"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="L3:L8"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="F55:L56"/>
+  <mergeCells count="10">
+    <mergeCell ref="M3:M8"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="G55:M56"/>
+    <mergeCell ref="C10:C19"/>
+    <mergeCell ref="C20:C26"/>
+    <mergeCell ref="C27:C32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="C35:C41"/>
+    <mergeCell ref="C44:C51"/>
+    <mergeCell ref="C52:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
+++ b/Deliverables/BOM/Control-Board/PCBWay_BOM-Control-Board.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25501"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ManarHarake-sEMGDevice\Deliverables\BOM\Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0DF7D1-C0B1-4293-934D-6B0E7CC96557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2013D255-062A-4753-99A7-1D28CCA4FE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="296">
   <si>
     <t>Component list</t>
   </si>
@@ -913,6 +913,12 @@
   </si>
   <si>
     <t>Crystal</t>
+  </si>
+  <si>
+    <t>GRM188R61E106MA73D</t>
+  </si>
+  <si>
+    <t>C91606</t>
   </si>
 </sst>
 </file>
@@ -1065,6 +1071,7 @@
       <sz val="12"/>
       <color indexed="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <strike/>
@@ -1504,40 +1511,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1549,7 +1556,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1559,7 +1566,7 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1586,132 +1593,15 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1726,103 +1616,223 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1844,7 +1854,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1880,61 +1890,23 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2322,21 +2294,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="23" customWidth="1"/>
     <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" customWidth="1"/>
-    <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" customWidth="1"/>
+    <col min="6" max="6" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="18"/>
       <c r="C1" s="2"/>
@@ -2345,10 +2317,10 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="129"/>
-    </row>
-    <row r="2" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1" s="123"/>
+      <c r="J1" s="124"/>
+    </row>
+    <row r="2" spans="1:11" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="66"/>
       <c r="C2" s="67" t="s">
@@ -2361,11 +2333,11 @@
       <c r="F2" s="10"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="126"/>
-      <c r="J2" s="126"/>
-      <c r="K2" s="127"/>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="122"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="19"/>
       <c r="C3" s="11" t="s">
@@ -2379,10 +2351,10 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="125"/>
-      <c r="K3" s="124"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J3" s="120"/>
+      <c r="K3" s="119"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="19"/>
       <c r="C4" s="11" t="s">
@@ -2396,10 +2368,10 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="124"/>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J4" s="120"/>
+      <c r="K4" s="119"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="19"/>
       <c r="C5" s="11" t="s">
@@ -2413,10 +2385,10 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="124"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J5" s="120"/>
+      <c r="K5" s="119"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="20"/>
       <c r="C6" s="14"/>
@@ -2426,10 +2398,10 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="125"/>
-      <c r="K6" s="124"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J6" s="120"/>
+      <c r="K6" s="119"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="21"/>
       <c r="C7" s="16"/>
@@ -2439,10 +2411,10 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="124"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J7" s="120"/>
+      <c r="K7" s="119"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="33"/>
       <c r="C8" s="34"/>
@@ -2452,10 +2424,10 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="125"/>
-      <c r="K8" s="124"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="120"/>
+      <c r="K8" s="119"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="61" t="s">
         <v>4</v>
@@ -2488,7 +2460,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="63">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -2522,7 +2494,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="64">
         <f t="shared" ref="B11:B54" si="0">ROW(B11) - ROW($B$9)</f>
@@ -2556,7 +2528,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="64">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -2590,7 +2562,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="64">
         <f t="shared" si="0"/>
@@ -2624,7 +2596,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="64">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -2658,7 +2630,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="64">
         <f t="shared" si="0"/>
@@ -2692,7 +2664,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="64">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -2726,7 +2698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="64">
         <f t="shared" si="0"/>
@@ -2760,7 +2732,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="64">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -2794,7 +2766,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="64">
         <f t="shared" si="0"/>
@@ -2828,7 +2800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="64">
         <f>ROW(B20) - ROW($B$9)</f>
@@ -2862,7 +2834,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="64">
         <f t="shared" si="0"/>
@@ -2896,7 +2868,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="64">
         <f>ROW(B22) - ROW($B$9)</f>
@@ -2930,7 +2902,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="64">
         <f t="shared" si="0"/>
@@ -2964,7 +2936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="64">
         <f>ROW(B24) - ROW($B$9)</f>
@@ -2998,7 +2970,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="64">
         <f t="shared" si="0"/>
@@ -3032,7 +3004,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="64">
         <f>ROW(B26) - ROW($B$9)</f>
@@ -3066,7 +3038,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="64">
         <f>ROW(B27) - ROW($B$9)</f>
@@ -3100,7 +3072,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="64">
         <f t="shared" si="0"/>
@@ -3134,7 +3106,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="64">
         <f>ROW(B29) - ROW($B$9)</f>
@@ -3168,7 +3140,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="64">
         <f t="shared" si="0"/>
@@ -3202,7 +3174,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="64">
         <f>ROW(B31) - ROW($B$9)</f>
@@ -3236,7 +3208,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="64">
         <f t="shared" si="0"/>
@@ -3270,7 +3242,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="64">
         <f>ROW(B33) - ROW($B$9)</f>
@@ -3304,7 +3276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="64">
         <f t="shared" si="0"/>
@@ -3338,7 +3310,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="64">
         <f>ROW(B35) - ROW($B$9)</f>
@@ -3372,7 +3344,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="64">
         <f t="shared" si="0"/>
@@ -3406,7 +3378,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="64">
         <f>ROW(B37) - ROW($B$9)</f>
@@ -3440,7 +3412,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="64">
         <f t="shared" si="0"/>
@@ -3474,7 +3446,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="64">
         <f>ROW(B39) - ROW($B$9)</f>
@@ -3508,7 +3480,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="64">
         <f t="shared" si="0"/>
@@ -3542,7 +3514,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="64">
         <f>ROW(B41) - ROW($B$9)</f>
@@ -3576,7 +3548,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="64">
         <f t="shared" si="0"/>
@@ -3610,7 +3582,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="64">
         <f>ROW(B43) - ROW($B$9)</f>
@@ -3644,7 +3616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="64">
         <f t="shared" si="0"/>
@@ -3678,7 +3650,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="64">
         <f>ROW(B45) - ROW($B$9)</f>
@@ -3712,7 +3684,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="64">
         <f t="shared" si="0"/>
@@ -3746,7 +3718,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="64">
         <f>ROW(B47) - ROW($B$9)</f>
@@ -3780,7 +3752,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="64">
         <f t="shared" si="0"/>
@@ -3814,7 +3786,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="64">
         <f>ROW(B49) - ROW($B$9)</f>
@@ -3848,7 +3820,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="64">
         <f t="shared" si="0"/>
@@ -3882,7 +3854,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="64">
         <f>ROW(B51) - ROW($B$9)</f>
@@ -3916,7 +3888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="64">
         <f t="shared" si="0"/>
@@ -3950,7 +3922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="64">
         <f>ROW(B53) - ROW($B$9)</f>
@@ -3984,7 +3956,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="65">
         <f t="shared" si="0"/>
@@ -4018,7 +3990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="39"/>
       <c r="C55" s="40" t="s">
@@ -4029,11 +4001,11 @@
       <c r="F55" s="59"/>
       <c r="G55" s="59"/>
       <c r="H55" s="59"/>
-      <c r="I55" s="120"/>
-      <c r="J55" s="120"/>
-      <c r="K55" s="121"/>
-    </row>
-    <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I55" s="115"/>
+      <c r="J55" s="115"/>
+      <c r="K55" s="116"/>
+    </row>
+    <row r="56" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="22"/>
       <c r="C56" s="8" t="s">
@@ -4044,9 +4016,9 @@
       <c r="F56" s="37"/>
       <c r="G56" s="37"/>
       <c r="H56" s="37"/>
-      <c r="I56" s="122"/>
-      <c r="J56" s="122"/>
-      <c r="K56" s="123"/>
+      <c r="I56" s="117"/>
+      <c r="J56" s="117"/>
+      <c r="K56" s="118"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4065,27 +4037,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348A8FCB-7220-490A-87EB-3CE6A0C47FB5}">
   <dimension ref="B1:M56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.140625" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" customWidth="1"/>
-    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="26.28515625" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.109375" customWidth="1"/>
+    <col min="6" max="6" width="20.88671875" customWidth="1"/>
+    <col min="7" max="7" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="26.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I1" s="98"/>
-    </row>
-    <row r="2" spans="2:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="2:13" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="70"/>
-      <c r="C2" s="137"/>
+      <c r="C2" s="103"/>
       <c r="D2" s="71" t="s">
         <v>0</v>
       </c>
@@ -4097,107 +4069,107 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="131"/>
-      <c r="L2" s="131"/>
-      <c r="M2" s="132"/>
-    </row>
-    <row r="3" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K2" s="126"/>
+      <c r="L2" s="126"/>
+      <c r="M2" s="127"/>
+    </row>
+    <row r="3" spans="2:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B3" s="19"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="112" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="112"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="11"/>
       <c r="F3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="112"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="K3" s="113"/>
-      <c r="L3" s="113"/>
-      <c r="M3" s="130"/>
-    </row>
-    <row r="4" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="11"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="125"/>
+    </row>
+    <row r="4" spans="2:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="19"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="112" t="s">
+      <c r="C4" s="104"/>
+      <c r="D4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="112"/>
+      <c r="E4" s="11"/>
       <c r="F4" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="72"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="124"/>
-    </row>
-    <row r="5" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="12"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="119"/>
+    </row>
+    <row r="5" spans="2:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="19"/>
-      <c r="C5" s="138"/>
-      <c r="D5" s="112" t="s">
+      <c r="C5" s="104"/>
+      <c r="D5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="112"/>
+      <c r="E5" s="11"/>
       <c r="F5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="74"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="124"/>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="G5" s="13"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="119"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="20"/>
-      <c r="C6" s="139"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
       <c r="F6" s="15"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="75"/>
-      <c r="M6" s="124"/>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="G6" s="13"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="119"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="21"/>
-      <c r="C7" s="140"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="114"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="17"/>
-      <c r="G7" s="114"/>
-      <c r="H7" s="115"/>
-      <c r="I7" s="115"/>
-      <c r="J7" s="115"/>
-      <c r="K7" s="115"/>
-      <c r="L7" s="115"/>
-      <c r="M7" s="124"/>
-    </row>
-    <row r="8" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G7" s="16"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="119"/>
+    </row>
+    <row r="8" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="33"/>
-      <c r="C8" s="141"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="116"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="35"/>
-      <c r="G8" s="114"/>
-      <c r="H8" s="115"/>
-      <c r="I8" s="115"/>
-      <c r="J8" s="115"/>
-      <c r="K8" s="115"/>
-      <c r="L8" s="115"/>
-      <c r="M8" s="124"/>
-    </row>
-    <row r="9" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G8" s="16"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="119"/>
+    </row>
+    <row r="9" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="30" t="s">
         <v>4</v>
       </c>
@@ -4235,36 +4207,36 @@
         <v>283</v>
       </c>
     </row>
-    <row r="10" spans="2:13" s="87" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="77">
+    <row r="10" spans="2:13" s="76" customFormat="1" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="72">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="146" t="s">
+      <c r="C10" s="132" t="s">
         <v>286</v>
       </c>
-      <c r="D10" s="88" t="s">
+      <c r="D10" s="77" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="88" t="s">
+      <c r="F10" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="G10" s="89" t="s">
+      <c r="G10" s="78" t="s">
         <v>128</v>
       </c>
-      <c r="H10" s="88" t="s">
+      <c r="H10" s="77" t="s">
         <v>150</v>
       </c>
       <c r="I10" s="52" t="s">
         <v>206</v>
       </c>
-      <c r="J10" s="88" t="s">
+      <c r="J10" s="77" t="s">
         <v>177</v>
       </c>
-      <c r="K10" s="78">
+      <c r="K10" s="73">
         <v>3</v>
       </c>
       <c r="L10" s="36">
@@ -4272,34 +4244,34 @@
       </c>
       <c r="M10" s="36"/>
     </row>
-    <row r="11" spans="2:13" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="77">
+    <row r="11" spans="2:13" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="72">
         <f t="shared" ref="B11:B54" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="147"/>
+      <c r="C11" s="133"/>
       <c r="D11" s="44" t="s">
         <v>271</v>
       </c>
-      <c r="E11" s="91" t="s">
+      <c r="E11" s="80" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="90" t="s">
+      <c r="F11" s="79" t="s">
         <v>97</v>
       </c>
       <c r="G11" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="H11" s="90" t="s">
+      <c r="H11" s="79" t="s">
         <v>150</v>
       </c>
       <c r="I11" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="J11" s="90" t="s">
+      <c r="J11" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="K11" s="79">
+      <c r="K11" s="74">
         <v>24</v>
       </c>
       <c r="L11" s="29">
@@ -4307,69 +4279,69 @@
       </c>
       <c r="M11" s="29"/>
     </row>
-    <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="77">
+    <row r="12" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="72">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="147"/>
-      <c r="D12" s="92" t="s">
+      <c r="C12" s="133"/>
+      <c r="D12" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="93" t="s">
+      <c r="E12" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="92" t="s">
+      <c r="F12" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="93" t="s">
-        <v>129</v>
-      </c>
-      <c r="H12" s="92" t="s">
+      <c r="G12" s="51" t="s">
+        <v>294</v>
+      </c>
+      <c r="H12" s="81" t="s">
         <v>151</v>
       </c>
       <c r="I12" s="54" t="s">
-        <v>210</v>
-      </c>
-      <c r="J12" s="92" t="s">
+        <v>295</v>
+      </c>
+      <c r="J12" s="81" t="s">
         <v>179</v>
       </c>
-      <c r="K12" s="80">
+      <c r="K12" s="75">
         <v>1</v>
       </c>
       <c r="L12" s="28">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M12" s="28"/>
     </row>
-    <row r="13" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="77">
+    <row r="13" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="72">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="147"/>
-      <c r="D13" s="90" t="s">
+      <c r="C13" s="133"/>
+      <c r="D13" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="91" t="s">
+      <c r="E13" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="90" t="s">
+      <c r="F13" s="79" t="s">
         <v>97</v>
       </c>
-      <c r="G13" s="91" t="s">
+      <c r="G13" s="80" t="s">
         <v>130</v>
       </c>
-      <c r="H13" s="90" t="s">
+      <c r="H13" s="79" t="s">
         <v>152</v>
       </c>
       <c r="I13" s="53" t="s">
         <v>212</v>
       </c>
-      <c r="J13" s="90" t="s">
+      <c r="J13" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="K13" s="79">
+      <c r="K13" s="74">
         <v>8</v>
       </c>
       <c r="L13" s="29">
@@ -4377,34 +4349,34 @@
       </c>
       <c r="M13" s="29"/>
     </row>
-    <row r="14" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="77">
+    <row r="14" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="72">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="147"/>
-      <c r="D14" s="92" t="s">
+      <c r="C14" s="133"/>
+      <c r="D14" s="81" t="s">
         <v>272</v>
       </c>
       <c r="E14" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="92" t="s">
+      <c r="F14" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="G14" s="93" t="s">
+      <c r="G14" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="H14" s="92" t="s">
+      <c r="H14" s="81" t="s">
         <v>153</v>
       </c>
       <c r="I14" s="54" t="s">
         <v>211</v>
       </c>
-      <c r="J14" s="92" t="s">
+      <c r="J14" s="81" t="s">
         <v>181</v>
       </c>
-      <c r="K14" s="80">
+      <c r="K14" s="75">
         <v>2</v>
       </c>
       <c r="L14" s="28">
@@ -4412,34 +4384,34 @@
       </c>
       <c r="M14" s="28"/>
     </row>
-    <row r="15" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="77">
+    <row r="15" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="72">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="147"/>
-      <c r="D15" s="90" t="s">
+      <c r="C15" s="133"/>
+      <c r="D15" s="79" t="s">
         <v>273</v>
       </c>
-      <c r="E15" s="91" t="s">
+      <c r="E15" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="90" t="s">
+      <c r="F15" s="79" t="s">
         <v>97</v>
       </c>
-      <c r="G15" s="91" t="s">
+      <c r="G15" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="H15" s="90" t="s">
+      <c r="H15" s="79" t="s">
         <v>152</v>
       </c>
       <c r="I15" s="53" t="s">
         <v>213</v>
       </c>
-      <c r="J15" s="90" t="s">
+      <c r="J15" s="79" t="s">
         <v>182</v>
       </c>
-      <c r="K15" s="79">
+      <c r="K15" s="74">
         <v>7</v>
       </c>
       <c r="L15" s="29">
@@ -4447,34 +4419,34 @@
       </c>
       <c r="M15" s="29"/>
     </row>
-    <row r="16" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="77">
+    <row r="16" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="72">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="147"/>
-      <c r="D16" s="92" t="s">
+      <c r="C16" s="133"/>
+      <c r="D16" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="93" t="s">
+      <c r="E16" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="92" t="s">
+      <c r="F16" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="G16" s="93" t="s">
+      <c r="G16" s="82" t="s">
         <v>133</v>
       </c>
-      <c r="H16" s="92" t="s">
+      <c r="H16" s="81" t="s">
         <v>150</v>
       </c>
       <c r="I16" s="54" t="s">
         <v>214</v>
       </c>
-      <c r="J16" s="92" t="s">
+      <c r="J16" s="81" t="s">
         <v>183</v>
       </c>
-      <c r="K16" s="80">
+      <c r="K16" s="75">
         <v>1</v>
       </c>
       <c r="L16" s="32">
@@ -4482,34 +4454,34 @@
       </c>
       <c r="M16" s="32"/>
     </row>
-    <row r="17" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="77">
+    <row r="17" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="72">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="147"/>
-      <c r="D17" s="90" t="s">
+      <c r="C17" s="133"/>
+      <c r="D17" s="79" t="s">
         <v>274</v>
       </c>
-      <c r="E17" s="91" t="s">
+      <c r="E17" s="80" t="s">
         <v>275</v>
       </c>
-      <c r="F17" s="90" t="s">
+      <c r="F17" s="79" t="s">
         <v>276</v>
       </c>
-      <c r="G17" s="91" t="s">
+      <c r="G17" s="80" t="s">
         <v>277</v>
       </c>
-      <c r="H17" s="90" t="s">
+      <c r="H17" s="79" t="s">
         <v>150</v>
       </c>
-      <c r="I17" s="101" t="s">
+      <c r="I17" s="89" t="s">
         <v>281</v>
       </c>
-      <c r="J17" s="90" t="s">
+      <c r="J17" s="79" t="s">
         <v>278</v>
       </c>
-      <c r="K17" s="79">
+      <c r="K17" s="74">
         <v>1</v>
       </c>
       <c r="L17" s="29">
@@ -4517,34 +4489,34 @@
       </c>
       <c r="M17" s="29"/>
     </row>
-    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="77">
+    <row r="18" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="72">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="147"/>
-      <c r="D18" s="92" t="s">
+      <c r="C18" s="133"/>
+      <c r="D18" s="81" t="s">
         <v>269</v>
       </c>
-      <c r="E18" s="93" t="s">
+      <c r="E18" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="F18" s="92" t="s">
+      <c r="F18" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="G18" s="93" t="s">
+      <c r="G18" s="82" t="s">
         <v>217</v>
       </c>
-      <c r="H18" s="92" t="s">
+      <c r="H18" s="81" t="s">
         <v>152</v>
       </c>
       <c r="I18" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="J18" s="92" t="s">
+      <c r="J18" s="81" t="s">
         <v>184</v>
       </c>
-      <c r="K18" s="100">
+      <c r="K18" s="88">
         <v>1</v>
       </c>
       <c r="L18" s="32">
@@ -4552,34 +4524,34 @@
       </c>
       <c r="M18" s="32"/>
     </row>
-    <row r="19" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="77">
+    <row r="19" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="72">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="148"/>
-      <c r="D19" s="90" t="s">
+      <c r="C19" s="134"/>
+      <c r="D19" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="91" t="s">
+      <c r="E19" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="90" t="s">
+      <c r="F19" s="79" t="s">
         <v>97</v>
       </c>
-      <c r="G19" s="91" t="s">
+      <c r="G19" s="80" t="s">
         <v>134</v>
       </c>
-      <c r="H19" s="90" t="s">
+      <c r="H19" s="79" t="s">
         <v>150</v>
       </c>
       <c r="I19" s="53" t="s">
         <v>218</v>
       </c>
-      <c r="J19" s="90" t="s">
+      <c r="J19" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="K19" s="79">
+      <c r="K19" s="74">
         <v>1</v>
       </c>
       <c r="L19" s="29">
@@ -4587,36 +4559,36 @@
       </c>
       <c r="M19" s="29"/>
     </row>
-    <row r="20" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="77">
+    <row r="20" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="72">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="146" t="s">
+      <c r="C20" s="132" t="s">
         <v>287</v>
       </c>
-      <c r="D20" s="92" t="s">
+      <c r="D20" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="93" t="s">
+      <c r="E20" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="92" t="s">
+      <c r="F20" s="81" t="s">
         <v>202</v>
       </c>
-      <c r="G20" s="93" t="s">
+      <c r="G20" s="82" t="s">
         <v>99</v>
       </c>
-      <c r="H20" s="92" t="s">
+      <c r="H20" s="81" t="s">
         <v>154</v>
       </c>
       <c r="I20" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="J20" s="99" t="s">
+      <c r="J20" s="87" t="s">
         <v>203</v>
       </c>
-      <c r="K20" s="100">
+      <c r="K20" s="88">
         <v>1</v>
       </c>
       <c r="L20" s="32">
@@ -4624,34 +4596,34 @@
       </c>
       <c r="M20" s="32"/>
     </row>
-    <row r="21" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="77">
+    <row r="21" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="72">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="147"/>
-      <c r="D21" s="90" t="s">
+      <c r="C21" s="133"/>
+      <c r="D21" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="91" t="s">
+      <c r="E21" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="F21" s="90" t="s">
+      <c r="F21" s="79" t="s">
         <v>202</v>
       </c>
-      <c r="G21" s="91" t="s">
+      <c r="G21" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="H21" s="90" t="s">
+      <c r="H21" s="79" t="s">
         <v>155</v>
       </c>
       <c r="I21" s="53" t="s">
         <v>220</v>
       </c>
-      <c r="J21" s="94" t="s">
+      <c r="J21" s="83" t="s">
         <v>203</v>
       </c>
-      <c r="K21" s="79">
+      <c r="K21" s="74">
         <v>1</v>
       </c>
       <c r="L21" s="29">
@@ -4659,71 +4631,71 @@
       </c>
       <c r="M21" s="29"/>
     </row>
-    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="77">
+    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="72">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="147"/>
-      <c r="D22" s="105" t="s">
+      <c r="C22" s="133"/>
+      <c r="D22" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="106" t="s">
+      <c r="E22" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="105" t="s">
+      <c r="F22" s="93" t="s">
         <v>202</v>
       </c>
-      <c r="G22" s="106" t="s">
+      <c r="G22" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="H22" s="105" t="s">
+      <c r="H22" s="93" t="s">
         <v>156</v>
       </c>
-      <c r="I22" s="152" t="s">
+      <c r="I22" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="J22" s="108" t="s">
+      <c r="J22" s="96" t="s">
         <v>203</v>
       </c>
-      <c r="K22" s="105">
-        <v>1</v>
-      </c>
-      <c r="L22" s="153">
+      <c r="K22" s="93">
+        <v>1</v>
+      </c>
+      <c r="L22" s="113">
         <v>20</v>
       </c>
-      <c r="M22" s="154" t="s">
+      <c r="M22" s="114" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="23" spans="2:13" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="77">
+    <row r="23" spans="2:13" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="72">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="147"/>
-      <c r="D23" s="90" t="s">
+      <c r="C23" s="133"/>
+      <c r="D23" s="79" t="s">
         <v>19</v>
       </c>
       <c r="E23" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="F23" s="90" t="s">
+      <c r="F23" s="79" t="s">
         <v>202</v>
       </c>
-      <c r="G23" s="91" t="s">
+      <c r="G23" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="H23" s="90" t="s">
+      <c r="H23" s="79" t="s">
         <v>157</v>
       </c>
       <c r="I23" s="53" t="s">
         <v>222</v>
       </c>
-      <c r="J23" s="94" t="s">
+      <c r="J23" s="83" t="s">
         <v>203</v>
       </c>
-      <c r="K23" s="79">
+      <c r="K23" s="74">
         <v>1</v>
       </c>
       <c r="L23" s="29">
@@ -4731,34 +4703,34 @@
       </c>
       <c r="M23" s="29"/>
     </row>
-    <row r="24" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="77">
+    <row r="24" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="72">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="147"/>
-      <c r="D24" s="92" t="s">
+      <c r="C24" s="133"/>
+      <c r="D24" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="93" t="s">
+      <c r="E24" s="82" t="s">
         <v>256</v>
       </c>
-      <c r="F24" s="92" t="s">
+      <c r="F24" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="93" t="s">
+      <c r="G24" s="82" t="s">
         <v>258</v>
       </c>
-      <c r="H24" s="99" t="s">
+      <c r="H24" s="87" t="s">
         <v>260</v>
       </c>
       <c r="I24" s="54" t="s">
         <v>261</v>
       </c>
-      <c r="J24" s="99" t="s">
+      <c r="J24" s="87" t="s">
         <v>203</v>
       </c>
-      <c r="K24" s="100">
+      <c r="K24" s="88">
         <v>1</v>
       </c>
       <c r="L24" s="32">
@@ -4766,34 +4738,34 @@
       </c>
       <c r="M24" s="32"/>
     </row>
-    <row r="25" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="77">
+    <row r="25" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="72">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="147"/>
-      <c r="D25" s="90" t="s">
+      <c r="C25" s="133"/>
+      <c r="D25" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="91" t="s">
+      <c r="E25" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="90" t="s">
+      <c r="F25" s="79" t="s">
         <v>202</v>
       </c>
-      <c r="G25" s="91" t="s">
+      <c r="G25" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="H25" s="90" t="s">
+      <c r="H25" s="79" t="s">
         <v>154</v>
       </c>
       <c r="I25" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="J25" s="94" t="s">
+      <c r="J25" s="83" t="s">
         <v>203</v>
       </c>
-      <c r="K25" s="79">
+      <c r="K25" s="74">
         <v>1</v>
       </c>
       <c r="L25" s="29">
@@ -4801,34 +4773,34 @@
       </c>
       <c r="M25" s="29"/>
     </row>
-    <row r="26" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="77">
+    <row r="26" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="72">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="148"/>
-      <c r="D26" s="92" t="s">
+      <c r="C26" s="134"/>
+      <c r="D26" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="93" t="s">
+      <c r="E26" s="82" t="s">
         <v>257</v>
       </c>
-      <c r="F26" s="92" t="s">
+      <c r="F26" s="81" t="s">
         <v>105</v>
       </c>
-      <c r="G26" s="93" t="s">
+      <c r="G26" s="82" t="s">
         <v>259</v>
       </c>
-      <c r="H26" s="99" t="s">
+      <c r="H26" s="87" t="s">
         <v>260</v>
       </c>
       <c r="I26" s="54" t="s">
         <v>262</v>
       </c>
-      <c r="J26" s="99" t="s">
+      <c r="J26" s="87" t="s">
         <v>203</v>
       </c>
-      <c r="K26" s="100">
+      <c r="K26" s="88">
         <v>1</v>
       </c>
       <c r="L26" s="32">
@@ -4836,36 +4808,36 @@
       </c>
       <c r="M26" s="32"/>
     </row>
-    <row r="27" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="77">
+    <row r="27" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="72">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="146" t="s">
+      <c r="C27" s="132" t="s">
         <v>288</v>
       </c>
-      <c r="D27" s="90" t="s">
+      <c r="D27" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="E27" s="91" t="s">
+      <c r="E27" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="F27" s="90" t="s">
+      <c r="F27" s="79" t="s">
         <v>202</v>
       </c>
-      <c r="G27" s="91" t="s">
+      <c r="G27" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="H27" s="90" t="s">
+      <c r="H27" s="79" t="s">
         <v>153</v>
       </c>
       <c r="I27" s="55" t="s">
         <v>255</v>
       </c>
-      <c r="J27" s="90" t="s">
+      <c r="J27" s="79" t="s">
         <v>186</v>
       </c>
-      <c r="K27" s="79">
+      <c r="K27" s="74">
         <v>1</v>
       </c>
       <c r="L27" s="29">
@@ -4873,34 +4845,34 @@
       </c>
       <c r="M27" s="29"/>
     </row>
-    <row r="28" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="77">
+    <row r="28" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="72">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="147"/>
-      <c r="D28" s="92" t="s">
+      <c r="C28" s="133"/>
+      <c r="D28" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E28" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="92" t="s">
+      <c r="F28" s="81" t="s">
         <v>107</v>
       </c>
-      <c r="G28" s="93" t="s">
+      <c r="G28" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="H28" s="92" t="s">
+      <c r="H28" s="81" t="s">
         <v>158</v>
       </c>
       <c r="I28" s="54" t="s">
         <v>224</v>
       </c>
-      <c r="J28" s="92" t="s">
+      <c r="J28" s="81" t="s">
         <v>187</v>
       </c>
-      <c r="K28" s="100">
+      <c r="K28" s="88">
         <v>1</v>
       </c>
       <c r="L28" s="32">
@@ -4908,34 +4880,34 @@
       </c>
       <c r="M28" s="32"/>
     </row>
-    <row r="29" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="77">
+    <row r="29" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="72">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="147"/>
-      <c r="D29" s="90" t="s">
+      <c r="C29" s="133"/>
+      <c r="D29" s="79" t="s">
         <v>27</v>
       </c>
       <c r="E29" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="F29" s="90" t="s">
+      <c r="F29" s="79" t="s">
         <v>202</v>
       </c>
-      <c r="G29" s="91" t="s">
+      <c r="G29" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="H29" s="90" t="s">
+      <c r="H29" s="79" t="s">
         <v>159</v>
       </c>
       <c r="I29" s="53" t="s">
         <v>225</v>
       </c>
-      <c r="J29" s="90" t="s">
+      <c r="J29" s="79" t="s">
         <v>188</v>
       </c>
-      <c r="K29" s="79">
+      <c r="K29" s="74">
         <v>1</v>
       </c>
       <c r="L29" s="29">
@@ -4943,34 +4915,34 @@
       </c>
       <c r="M29" s="29"/>
     </row>
-    <row r="30" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="77">
+    <row r="30" spans="2:13" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="72">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="147"/>
-      <c r="D30" s="92" t="s">
+      <c r="C30" s="133"/>
+      <c r="D30" s="81" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="F30" s="92" t="s">
+      <c r="F30" s="81" t="s">
         <v>109</v>
       </c>
-      <c r="G30" s="93" t="s">
+      <c r="G30" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="H30" s="92" t="s">
+      <c r="H30" s="81" t="s">
         <v>150</v>
       </c>
       <c r="I30" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="J30" s="92" t="s">
+      <c r="J30" s="81" t="s">
         <v>189</v>
       </c>
-      <c r="K30" s="100">
+      <c r="K30" s="88">
         <v>1</v>
       </c>
       <c r="L30" s="32">
@@ -4978,34 +4950,34 @@
       </c>
       <c r="M30" s="32"/>
     </row>
-    <row r="31" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="77">
+    <row r="31" spans="2:13" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="72">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="147"/>
-      <c r="D31" s="90" t="s">
+      <c r="C31" s="133"/>
+      <c r="D31" s="79" t="s">
         <v>29</v>
       </c>
       <c r="E31" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="F31" s="90" t="s">
+      <c r="F31" s="79" t="s">
         <v>109</v>
       </c>
-      <c r="G31" s="91" t="s">
+      <c r="G31" s="80" t="s">
         <v>137</v>
       </c>
-      <c r="H31" s="90" t="s">
+      <c r="H31" s="79" t="s">
         <v>150</v>
       </c>
       <c r="I31" s="53" t="s">
         <v>228</v>
       </c>
-      <c r="J31" s="94" t="s">
+      <c r="J31" s="83" t="s">
         <v>204</v>
       </c>
-      <c r="K31" s="79">
+      <c r="K31" s="74">
         <v>1</v>
       </c>
       <c r="L31" s="29">
@@ -5013,34 +4985,34 @@
       </c>
       <c r="M31" s="29"/>
     </row>
-    <row r="32" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="77">
+    <row r="32" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="72">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="148"/>
-      <c r="D32" s="92" t="s">
+      <c r="C32" s="134"/>
+      <c r="D32" s="81" t="s">
         <v>30</v>
       </c>
       <c r="E32" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="F32" s="92" t="s">
+      <c r="F32" s="81" t="s">
         <v>202</v>
       </c>
-      <c r="G32" s="93" t="s">
+      <c r="G32" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="H32" s="92" t="s">
+      <c r="H32" s="81" t="s">
         <v>160</v>
       </c>
       <c r="I32" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="J32" s="92" t="s">
+      <c r="J32" s="81" t="s">
         <v>190</v>
       </c>
-      <c r="K32" s="100">
+      <c r="K32" s="88">
         <v>1</v>
       </c>
       <c r="L32" s="32">
@@ -5048,36 +5020,36 @@
       </c>
       <c r="M32" s="32"/>
     </row>
-    <row r="33" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="77">
+    <row r="33" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="72">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="146" t="s">
+      <c r="C33" s="132" t="s">
         <v>289</v>
       </c>
-      <c r="D33" s="90" t="s">
+      <c r="D33" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="E33" s="91" t="s">
+      <c r="E33" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="90" t="s">
+      <c r="F33" s="79" t="s">
         <v>111</v>
       </c>
       <c r="G33" s="44" t="s">
         <v>229</v>
       </c>
-      <c r="H33" s="90" t="s">
+      <c r="H33" s="79" t="s">
         <v>161</v>
       </c>
       <c r="I33" s="53" t="s">
         <v>230</v>
       </c>
-      <c r="J33" s="94" t="s">
+      <c r="J33" s="83" t="s">
         <v>204</v>
       </c>
-      <c r="K33" s="79">
+      <c r="K33" s="74">
         <v>2</v>
       </c>
       <c r="L33" s="29">
@@ -5085,34 +5057,34 @@
       </c>
       <c r="M33" s="29"/>
     </row>
-    <row r="34" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="77">
+    <row r="34" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="72">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="148"/>
-      <c r="D34" s="92" t="s">
+      <c r="C34" s="134"/>
+      <c r="D34" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="E34" s="93" t="s">
+      <c r="E34" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="F34" s="92" t="s">
+      <c r="F34" s="81" t="s">
         <v>111</v>
       </c>
       <c r="G34" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="H34" s="92" t="s">
+      <c r="H34" s="81" t="s">
         <v>161</v>
       </c>
       <c r="I34" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="J34" s="99" t="s">
+      <c r="J34" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="K34" s="100">
+      <c r="K34" s="88">
         <v>1</v>
       </c>
       <c r="L34" s="32">
@@ -5120,36 +5092,36 @@
       </c>
       <c r="M34" s="32"/>
     </row>
-    <row r="35" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="77">
+    <row r="35" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="72">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="146" t="s">
+      <c r="C35" s="132" t="s">
         <v>290</v>
       </c>
-      <c r="D35" s="90" t="s">
+      <c r="D35" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="95" t="s">
+      <c r="E35" s="84" t="s">
         <v>264</v>
       </c>
-      <c r="F35" s="90" t="s">
+      <c r="F35" s="79" t="s">
         <v>265</v>
       </c>
-      <c r="G35" s="91" t="s">
+      <c r="G35" s="80" t="s">
         <v>266</v>
       </c>
-      <c r="H35" s="90" t="s">
+      <c r="H35" s="79" t="s">
         <v>267</v>
       </c>
       <c r="I35" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="J35" s="90" t="s">
+      <c r="J35" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="K35" s="79">
+      <c r="K35" s="74">
         <v>1</v>
       </c>
       <c r="L35" s="29">
@@ -5157,34 +5129,34 @@
       </c>
       <c r="M35" s="29"/>
     </row>
-    <row r="36" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="77">
+    <row r="36" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="72">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="147"/>
-      <c r="D36" s="92" t="s">
+      <c r="C36" s="133"/>
+      <c r="D36" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="96" t="s">
+      <c r="E36" s="85" t="s">
         <v>253</v>
       </c>
-      <c r="F36" s="92" t="s">
+      <c r="F36" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="G36" s="96" t="s">
+      <c r="G36" s="85" t="s">
         <v>252</v>
       </c>
-      <c r="H36" s="97" t="s">
+      <c r="H36" s="86" t="s">
         <v>152</v>
       </c>
       <c r="I36" s="54" t="s">
         <v>251</v>
       </c>
-      <c r="J36" s="92" t="s">
+      <c r="J36" s="81" t="s">
         <v>192</v>
       </c>
-      <c r="K36" s="100">
+      <c r="K36" s="88">
         <v>4</v>
       </c>
       <c r="L36" s="32">
@@ -5192,34 +5164,34 @@
       </c>
       <c r="M36" s="32"/>
     </row>
-    <row r="37" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="77">
+    <row r="37" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="72">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="147"/>
+      <c r="C37" s="133"/>
       <c r="D37" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="91" t="s">
+      <c r="E37" s="80" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="90" t="s">
+      <c r="F37" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="G37" s="91" t="s">
+      <c r="G37" s="80" t="s">
         <v>138</v>
       </c>
-      <c r="H37" s="90" t="s">
+      <c r="H37" s="79" t="s">
         <v>152</v>
       </c>
       <c r="I37" s="53" t="s">
         <v>233</v>
       </c>
-      <c r="J37" s="90" t="s">
+      <c r="J37" s="79" t="s">
         <v>193</v>
       </c>
-      <c r="K37" s="79">
+      <c r="K37" s="74">
         <v>10</v>
       </c>
       <c r="L37" s="29">
@@ -5227,34 +5199,34 @@
       </c>
       <c r="M37" s="29"/>
     </row>
-    <row r="38" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="77">
+    <row r="38" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="72">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="147"/>
-      <c r="D38" s="92" t="s">
+      <c r="C38" s="133"/>
+      <c r="D38" s="81" t="s">
         <v>279</v>
       </c>
-      <c r="E38" s="93" t="s">
+      <c r="E38" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="F38" s="92" t="s">
+      <c r="F38" s="81" t="s">
         <v>113</v>
       </c>
       <c r="G38" s="45" t="s">
         <v>236</v>
       </c>
-      <c r="H38" s="92" t="s">
+      <c r="H38" s="81" t="s">
         <v>163</v>
       </c>
       <c r="I38" s="54" t="s">
         <v>237</v>
       </c>
-      <c r="J38" s="92" t="s">
+      <c r="J38" s="81" t="s">
         <v>195</v>
       </c>
-      <c r="K38" s="100">
+      <c r="K38" s="88">
         <v>8</v>
       </c>
       <c r="L38" s="32">
@@ -5262,34 +5234,34 @@
       </c>
       <c r="M38" s="32"/>
     </row>
-    <row r="39" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="77">
+    <row r="39" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="72">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="147"/>
-      <c r="D39" s="90" t="s">
+      <c r="C39" s="133"/>
+      <c r="D39" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="E39" s="91" t="s">
+      <c r="E39" s="80" t="s">
         <v>79</v>
       </c>
-      <c r="F39" s="90" t="s">
+      <c r="F39" s="79" t="s">
         <v>113</v>
       </c>
       <c r="G39" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="H39" s="90" t="s">
+      <c r="H39" s="79" t="s">
         <v>163</v>
       </c>
       <c r="I39" s="53" t="s">
         <v>239</v>
       </c>
-      <c r="J39" s="90" t="s">
+      <c r="J39" s="79" t="s">
         <v>196</v>
       </c>
-      <c r="K39" s="79">
+      <c r="K39" s="74">
         <v>2</v>
       </c>
       <c r="L39" s="29">
@@ -5297,34 +5269,34 @@
       </c>
       <c r="M39" s="29"/>
     </row>
-    <row r="40" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="77">
+    <row r="40" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="72">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="147"/>
-      <c r="D40" s="92" t="s">
+      <c r="C40" s="133"/>
+      <c r="D40" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="E40" s="93" t="s">
+      <c r="E40" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="F40" s="92" t="s">
+      <c r="F40" s="81" t="s">
         <v>112</v>
       </c>
       <c r="G40" s="45" t="s">
         <v>240</v>
       </c>
-      <c r="H40" s="92" t="s">
+      <c r="H40" s="81" t="s">
         <v>164</v>
       </c>
       <c r="I40" s="54" t="s">
         <v>241</v>
       </c>
-      <c r="J40" s="92" t="s">
+      <c r="J40" s="81" t="s">
         <v>197</v>
       </c>
-      <c r="K40" s="100">
+      <c r="K40" s="88">
         <v>2</v>
       </c>
       <c r="L40" s="32">
@@ -5332,34 +5304,34 @@
       </c>
       <c r="M40" s="32"/>
     </row>
-    <row r="41" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="77">
+    <row r="41" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="72">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="148"/>
-      <c r="D41" s="90" t="s">
+      <c r="C41" s="134"/>
+      <c r="D41" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="E41" s="91" t="s">
+      <c r="E41" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="F41" s="90" t="s">
+      <c r="F41" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="G41" s="91" t="s">
+      <c r="G41" s="80" t="s">
         <v>140</v>
       </c>
-      <c r="H41" s="90" t="s">
+      <c r="H41" s="79" t="s">
         <v>152</v>
       </c>
       <c r="I41" s="53" t="s">
         <v>235</v>
       </c>
-      <c r="J41" s="90" t="s">
+      <c r="J41" s="79" t="s">
         <v>198</v>
       </c>
-      <c r="K41" s="79">
+      <c r="K41" s="74">
         <v>1</v>
       </c>
       <c r="L41" s="29">
@@ -5367,75 +5339,75 @@
       </c>
       <c r="M41" s="29"/>
     </row>
-    <row r="42" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="77">
+    <row r="42" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="72">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="150" t="s">
+      <c r="C42" s="110" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="105" t="s">
+      <c r="D42" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="E42" s="106" t="s">
+      <c r="E42" s="94" t="s">
         <v>82</v>
       </c>
-      <c r="F42" s="105" t="s">
+      <c r="F42" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="G42" s="107" t="s">
+      <c r="G42" s="95" t="s">
         <v>204</v>
       </c>
-      <c r="H42" s="108" t="s">
+      <c r="H42" s="96" t="s">
         <v>204</v>
       </c>
-      <c r="I42" s="109" t="s">
+      <c r="I42" s="97" t="s">
         <v>254</v>
       </c>
-      <c r="J42" s="108" t="s">
+      <c r="J42" s="96" t="s">
         <v>204</v>
       </c>
-      <c r="K42" s="105">
+      <c r="K42" s="93">
         <v>3</v>
       </c>
-      <c r="L42" s="110" t="s">
+      <c r="L42" s="98" t="s">
         <v>203</v>
       </c>
-      <c r="M42" s="111" t="s">
+      <c r="M42" s="99" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="77">
+    <row r="43" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="72">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="151" t="s">
+      <c r="C43" s="111" t="s">
         <v>291</v>
       </c>
-      <c r="D43" s="90" t="s">
+      <c r="D43" s="79" t="s">
         <v>280</v>
       </c>
       <c r="E43" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="F43" s="90" t="s">
+      <c r="F43" s="79" t="s">
         <v>202</v>
       </c>
-      <c r="G43" s="91" t="s">
+      <c r="G43" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="H43" s="90" t="s">
+      <c r="H43" s="79" t="s">
         <v>165</v>
       </c>
       <c r="I43" s="53" t="s">
         <v>242</v>
       </c>
-      <c r="J43" s="94" t="s">
+      <c r="J43" s="83" t="s">
         <v>204</v>
       </c>
-      <c r="K43" s="79">
+      <c r="K43" s="74">
         <v>2</v>
       </c>
       <c r="L43" s="29">
@@ -5443,36 +5415,36 @@
       </c>
       <c r="M43" s="29"/>
     </row>
-    <row r="44" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="77">
+    <row r="44" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="72">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="146" t="s">
+      <c r="C44" s="132" t="s">
         <v>292</v>
       </c>
-      <c r="D44" s="92" t="s">
+      <c r="D44" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="E44" s="93" t="s">
+      <c r="E44" s="82" t="s">
         <v>84</v>
       </c>
-      <c r="F44" s="92" t="s">
+      <c r="F44" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="G44" s="93" t="s">
+      <c r="G44" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="H44" s="92" t="s">
+      <c r="H44" s="81" t="s">
         <v>166</v>
       </c>
       <c r="I44" s="57" t="s">
         <v>254</v>
       </c>
-      <c r="J44" s="99" t="s">
+      <c r="J44" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="K44" s="100">
+      <c r="K44" s="88">
         <v>1</v>
       </c>
       <c r="L44" s="32">
@@ -5480,34 +5452,34 @@
       </c>
       <c r="M44" s="32"/>
     </row>
-    <row r="45" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="77">
+    <row r="45" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="72">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="147"/>
-      <c r="D45" s="90" t="s">
+      <c r="C45" s="133"/>
+      <c r="D45" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="91" t="s">
+      <c r="E45" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="F45" s="90" t="s">
+      <c r="F45" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="G45" s="91" t="s">
+      <c r="G45" s="80" t="s">
         <v>142</v>
       </c>
-      <c r="H45" s="90" t="s">
+      <c r="H45" s="79" t="s">
         <v>167</v>
       </c>
       <c r="I45" s="53" t="s">
         <v>243</v>
       </c>
-      <c r="J45" s="94" t="s">
+      <c r="J45" s="83" t="s">
         <v>204</v>
       </c>
-      <c r="K45" s="79">
+      <c r="K45" s="74">
         <v>1</v>
       </c>
       <c r="L45" s="29">
@@ -5515,34 +5487,34 @@
       </c>
       <c r="M45" s="29"/>
     </row>
-    <row r="46" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="77">
+    <row r="46" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="72">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="147"/>
-      <c r="D46" s="92" t="s">
+      <c r="C46" s="133"/>
+      <c r="D46" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="E46" s="93" t="s">
+      <c r="E46" s="82" t="s">
         <v>86</v>
       </c>
-      <c r="F46" s="92" t="s">
+      <c r="F46" s="81" t="s">
         <v>118</v>
       </c>
-      <c r="G46" s="93" t="s">
+      <c r="G46" s="82" t="s">
         <v>143</v>
       </c>
-      <c r="H46" s="92" t="s">
+      <c r="H46" s="81" t="s">
         <v>168</v>
       </c>
       <c r="I46" s="57" t="s">
         <v>254</v>
       </c>
-      <c r="J46" s="99" t="s">
+      <c r="J46" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="K46" s="100">
+      <c r="K46" s="88">
         <v>1</v>
       </c>
       <c r="L46" s="32">
@@ -5550,34 +5522,34 @@
       </c>
       <c r="M46" s="32"/>
     </row>
-    <row r="47" spans="2:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="77">
+    <row r="47" spans="2:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="72">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="147"/>
-      <c r="D47" s="90" t="s">
+      <c r="C47" s="133"/>
+      <c r="D47" s="79" t="s">
         <v>46</v>
       </c>
       <c r="E47" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="F47" s="90" t="s">
+      <c r="F47" s="79" t="s">
         <v>119</v>
       </c>
-      <c r="G47" s="91" t="s">
+      <c r="G47" s="80" t="s">
         <v>144</v>
       </c>
-      <c r="H47" s="90" t="s">
+      <c r="H47" s="79" t="s">
         <v>169</v>
       </c>
       <c r="I47" s="53" t="s">
         <v>244</v>
       </c>
-      <c r="J47" s="94" t="s">
+      <c r="J47" s="83" t="s">
         <v>204</v>
       </c>
-      <c r="K47" s="79">
+      <c r="K47" s="74">
         <v>1</v>
       </c>
       <c r="L47" s="29">
@@ -5585,34 +5557,34 @@
       </c>
       <c r="M47" s="29"/>
     </row>
-    <row r="48" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="77">
+    <row r="48" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="72">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="147"/>
-      <c r="D48" s="92" t="s">
+      <c r="C48" s="133"/>
+      <c r="D48" s="81" t="s">
         <v>47</v>
       </c>
       <c r="E48" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="F48" s="92" t="s">
+      <c r="F48" s="81" t="s">
         <v>120</v>
       </c>
-      <c r="G48" s="93" t="s">
+      <c r="G48" s="82" t="s">
         <v>145</v>
       </c>
-      <c r="H48" s="92" t="s">
+      <c r="H48" s="81" t="s">
         <v>170</v>
       </c>
       <c r="I48" s="57" t="s">
         <v>203</v>
       </c>
-      <c r="J48" s="99" t="s">
+      <c r="J48" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="K48" s="100">
+      <c r="K48" s="88">
         <v>1</v>
       </c>
       <c r="L48" s="32">
@@ -5620,34 +5592,34 @@
       </c>
       <c r="M48" s="32"/>
     </row>
-    <row r="49" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="77">
+    <row r="49" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="72">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="147"/>
-      <c r="D49" s="90" t="s">
+      <c r="C49" s="133"/>
+      <c r="D49" s="79" t="s">
         <v>48</v>
       </c>
       <c r="E49" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="F49" s="90" t="s">
+      <c r="F49" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="G49" s="91" t="s">
+      <c r="G49" s="80" t="s">
         <v>146</v>
       </c>
-      <c r="H49" s="90" t="s">
+      <c r="H49" s="79" t="s">
         <v>171</v>
       </c>
       <c r="I49" s="53" t="s">
         <v>245</v>
       </c>
-      <c r="J49" s="94" t="s">
+      <c r="J49" s="83" t="s">
         <v>204</v>
       </c>
-      <c r="K49" s="79">
+      <c r="K49" s="74">
         <v>1</v>
       </c>
       <c r="L49" s="29">
@@ -5655,34 +5627,34 @@
       </c>
       <c r="M49" s="29"/>
     </row>
-    <row r="50" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="77">
+    <row r="50" spans="2:13" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="72">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="147"/>
-      <c r="D50" s="92" t="s">
+      <c r="C50" s="133"/>
+      <c r="D50" s="81" t="s">
         <v>49</v>
       </c>
       <c r="E50" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="F50" s="92" t="s">
+      <c r="F50" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="G50" s="93" t="s">
+      <c r="G50" s="82" t="s">
         <v>147</v>
       </c>
-      <c r="H50" s="92" t="s">
+      <c r="H50" s="81" t="s">
         <v>172</v>
       </c>
       <c r="I50" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="J50" s="99" t="s">
+      <c r="J50" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="K50" s="100">
+      <c r="K50" s="88">
         <v>1</v>
       </c>
       <c r="L50" s="32">
@@ -5690,34 +5662,34 @@
       </c>
       <c r="M50" s="32"/>
     </row>
-    <row r="51" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="77">
+    <row r="51" spans="2:13" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="72">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="148"/>
-      <c r="D51" s="90" t="s">
+      <c r="C51" s="134"/>
+      <c r="D51" s="79" t="s">
         <v>50</v>
       </c>
       <c r="E51" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="F51" s="90" t="s">
+      <c r="F51" s="79" t="s">
         <v>123</v>
       </c>
-      <c r="G51" s="91" t="s">
+      <c r="G51" s="80" t="s">
         <v>148</v>
       </c>
-      <c r="H51" s="90" t="s">
+      <c r="H51" s="79" t="s">
         <v>173</v>
       </c>
       <c r="I51" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="J51" s="94" t="s">
+      <c r="J51" s="83" t="s">
         <v>204</v>
       </c>
-      <c r="K51" s="79">
+      <c r="K51" s="74">
         <v>1</v>
       </c>
       <c r="L51" s="29">
@@ -5725,36 +5697,36 @@
       </c>
       <c r="M51" s="29"/>
     </row>
-    <row r="52" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="77">
+    <row r="52" spans="2:13" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="72">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="145" t="s">
+      <c r="C52" s="135" t="s">
         <v>293</v>
       </c>
-      <c r="D52" s="92" t="s">
+      <c r="D52" s="81" t="s">
         <v>51</v>
       </c>
       <c r="E52" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="F52" s="92" t="s">
+      <c r="F52" s="81" t="s">
         <v>202</v>
       </c>
-      <c r="G52" s="93" t="s">
+      <c r="G52" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="H52" s="92" t="s">
+      <c r="H52" s="81" t="s">
         <v>174</v>
       </c>
       <c r="I52" s="54" t="s">
         <v>248</v>
       </c>
-      <c r="J52" s="92" t="s">
+      <c r="J52" s="81" t="s">
         <v>199</v>
       </c>
-      <c r="K52" s="100">
+      <c r="K52" s="88">
         <v>2</v>
       </c>
       <c r="L52" s="32">
@@ -5762,34 +5734,34 @@
       </c>
       <c r="M52" s="32"/>
     </row>
-    <row r="53" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="77">
+    <row r="53" spans="2:13" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="72">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="144"/>
-      <c r="D53" s="90" t="s">
+      <c r="C53" s="136"/>
+      <c r="D53" s="79" t="s">
         <v>52</v>
       </c>
       <c r="E53" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="F53" s="90" t="s">
+      <c r="F53" s="79" t="s">
         <v>202</v>
       </c>
-      <c r="G53" s="91" t="s">
+      <c r="G53" s="80" t="s">
         <v>125</v>
       </c>
-      <c r="H53" s="90" t="s">
+      <c r="H53" s="79" t="s">
         <v>174</v>
       </c>
       <c r="I53" s="53" t="s">
         <v>249</v>
       </c>
-      <c r="J53" s="90" t="s">
+      <c r="J53" s="79" t="s">
         <v>200</v>
       </c>
-      <c r="K53" s="79">
+      <c r="K53" s="74">
         <v>1</v>
       </c>
       <c r="L53" s="29">
@@ -5797,72 +5769,72 @@
       </c>
       <c r="M53" s="29"/>
     </row>
-    <row r="54" spans="2:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="117">
+    <row r="54" spans="2:13" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="100">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="149"/>
-      <c r="D54" s="118" t="s">
+      <c r="C54" s="137"/>
+      <c r="D54" s="101" t="s">
         <v>53</v>
       </c>
-      <c r="E54" s="102" t="s">
+      <c r="E54" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="F54" s="118" t="s">
+      <c r="F54" s="101" t="s">
         <v>202</v>
       </c>
-      <c r="G54" s="103" t="s">
+      <c r="G54" s="91" t="s">
         <v>126</v>
       </c>
-      <c r="H54" s="118" t="s">
+      <c r="H54" s="101" t="s">
         <v>175</v>
       </c>
-      <c r="I54" s="102" t="s">
+      <c r="I54" s="90" t="s">
         <v>250</v>
       </c>
-      <c r="J54" s="118" t="s">
+      <c r="J54" s="101" t="s">
         <v>201</v>
       </c>
-      <c r="K54" s="119">
-        <v>1</v>
-      </c>
-      <c r="L54" s="104">
+      <c r="K54" s="102">
+        <v>1</v>
+      </c>
+      <c r="L54" s="92">
         <v>10</v>
       </c>
-      <c r="M54" s="104"/>
-    </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B55" s="81"/>
-      <c r="C55" s="142"/>
-      <c r="D55" s="82" t="s">
+      <c r="M54" s="92"/>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B55" s="39"/>
+      <c r="C55" s="108"/>
+      <c r="D55" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="83"/>
+      <c r="E55" s="41"/>
       <c r="F55" s="42"/>
-      <c r="G55" s="133"/>
-      <c r="H55" s="133"/>
-      <c r="I55" s="133"/>
-      <c r="J55" s="133"/>
-      <c r="K55" s="133"/>
-      <c r="L55" s="133"/>
-      <c r="M55" s="134"/>
-    </row>
-    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="84"/>
-      <c r="C56" s="143"/>
-      <c r="D56" s="85" t="s">
+      <c r="G55" s="128"/>
+      <c r="H55" s="128"/>
+      <c r="I55" s="128"/>
+      <c r="J55" s="128"/>
+      <c r="K55" s="128"/>
+      <c r="L55" s="128"/>
+      <c r="M55" s="129"/>
+    </row>
+    <row r="56" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="22"/>
+      <c r="C56" s="109"/>
+      <c r="D56" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E56" s="86"/>
-      <c r="F56" s="86"/>
-      <c r="G56" s="135"/>
-      <c r="H56" s="135"/>
-      <c r="I56" s="135"/>
-      <c r="J56" s="135"/>
-      <c r="K56" s="135"/>
-      <c r="L56" s="135"/>
-      <c r="M56" s="136"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="130"/>
+      <c r="H56" s="130"/>
+      <c r="I56" s="130"/>
+      <c r="J56" s="130"/>
+      <c r="K56" s="130"/>
+      <c r="L56" s="130"/>
+      <c r="M56" s="131"/>
     </row>
   </sheetData>
   <mergeCells count="10">
